--- a/data/google_news_dedup_07_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_07_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,12 +655,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Heavy traffic surrounding designer village just off the M5 - The Worcester News</t>
+          <t>Heavy traffic surrounding designer village just off the M5 - worcesternews.co.uk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Heavy traffic surrounding designer village just off the M5 - The Worcester News</t>
+          <t>Heavy traffic surrounding designer village just off the M5 - worcesternews.co.uk</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Driver caught speeding at 112mph on motorway - bicesteradvertiser.net</t>
+          <t>Driver caught speeding at 112mph on motorway - Bicester Advertiser</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Driver caught speeding at 112mph on motorway - bicesteradvertiser.net</t>
+          <t>Driver caught speeding at 112mph on motorway - Bicester Advertiser</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -930,22 +930,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amazon rides on new logistics and delivery innovations: What's ahead? - MSN</t>
+          <t>Amazon reaches delivery agreement with U.S. Postal Service - Investing.com UK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Amazon rides on new logistics and delivery innovations: What's ahead? - MSN</t>
+          <t>Amazon reaches delivery agreement with U.S. Postal Service - Investing.com UK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 22:58:12 GMT</t>
+          <t>Mon, 06 Apr 2026 19:39:21 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN0xrNEcwT2FCNEJSTEh1OTFJWHpscDc1ckgxVDk1eWRtY2lvSzZtdjhyaGR3dnQxUEhjTHlCT3h2VE50WTBjYkxHN2EwMjdvdWptNnlYa0tzN05xdDJCLW1qQzQ5cU1ZelM5c0dMZGRFZkxBdDVjNUxsMDZzM04wNjAwVkZvYTJ6MkU3SHBPTGdsN0lUWjlZV3lFdlNQUXJjdnBOVnhUN184SGM1b05xU2lmUWdXWTZOMFBmWUln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPVlVZaXRUeGtJaXZKNDVLWHhXcXhwVDBTQ3R4dDN4WnZyU1ZjOEgwYWJ1eHlQQktaalJPS2VNUDRnQmx5R2duamFyZWVScnZ4R0k5Q1ptay03eWVzdDhqOVpMTnRNNU1fXzZ2aWpSQ1NXb2dXaUFxM2RtS09SVzdRelVVM3VEeHl4ZnNLMWh5UDJaaVplUjd2MUNLbWNueTI3ZElyWGtUbVR6Y0o0RUpvZGNLajUtUEVWRWEzczZKUmtGWWtGNVJ6eQ?oc=5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46118.95708333333</v>
+        <v>46118.81899305555</v>
       </c>
     </row>
     <row r="11">
@@ -985,22 +985,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amazon reaches delivery agreement with U.S. Postal Service - Investing.com UK</t>
+          <t>Exclusive | Amazon and U.S. Postal Service Reach Delivery Deal - WSJ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Amazon reaches delivery agreement with U.S. Postal Service - Investing.com UK</t>
+          <t>Exclusive | Amazon and U.S. Postal Service Reach Delivery Deal - WSJ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 19:39:21 GMT</t>
+          <t>Mon, 06 Apr 2026 19:50:00 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPVlVZaXRUeGtJaXZKNDVLWHhXcXhwVDBTQ3R4dDN4WnZyU1ZjOEgwYWJ1eHlQQktaalJPS2VNUDRnQmx5R2duamFyZWVScnZ4R0k5Q1ptay03eWVzdDhqOVpMTnRNNU1fXzZ2aWpSQ1NXb2dXaUFxM2RtS09SVzdRelVVM3VEeHl4ZnNLMWh5UDJaaVplUjd2MUNLbWNueTI3ZElyWGtUbVR6Y0o0RUpvZGNLajUtUEVWRWEzczZKUmtGWWtGNVJ6eQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowNBVV95cUxON1V4aml1UWs0MmFTbUYxT2VsVEFBRUwyQjVOOGZpR3lMVW9TR2tRUk42d2p1WmZya0xIaTdJMFc4QjN2YTN4bzc1elRVVE9vZnM0X0dpWWtHLTRMNmZ5aU56OTRnakZDR3E5UmtkUlFIMnhmZTRhclUxVVUxR0VvaDFzV2cxa3BnakN4WWZKZHA0aHNWZmlBOEJEX2VDQ1lRZzhtODV2RkxhaFdDeWdYRkwxYXZZSmZXaXFGU0ZjMmtWQk1CRTFEZlZRc2xielhNRVE1ZjkxMWdFRENwc25QOV9QaExRV1c1aXdNM2c1NmZXVnFBaVRJZmJuQ25Zc3hUbk5KaUs5UFhCSjRDRzFYU0pGSWdDS0RKeTRfRVpvU3JLdlFGbmRLN2RMbmNFalh5YkRtdU0wdkhvQ0JjZHhtajJ5dzR1MG1xU1hMMkJsSDh3YlZvRGo2aGtiNjZ2MWoySENCdk82cm5iajZvcmFaYkRrUEpkY3ZESzhIVlRXNEFMMnJ0M1I5SzdvVkJyb0RUck0xUUxLY3NoZTdqQThyc2dLMA?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46118.81899305555</v>
+        <v>46118.82638888889</v>
       </c>
     </row>
     <row r="12">
@@ -1040,22 +1040,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Exclusive | Amazon and U.S. Postal Service Reach Delivery Deal - WSJ</t>
+          <t>Amazon’s 3.5% fuel surcharge indicates a lasting disruption in the energy market is becoming entrenched - Bitget</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Exclusive | Amazon and U.S. Postal Service Reach Delivery Deal - WSJ</t>
+          <t>Amazon’s 3.5% fuel surcharge indicates a lasting disruption in the energy market is becoming entrenched - Bitget</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 19:50:00 GMT</t>
+          <t>Mon, 06 Apr 2026 23:15:00 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowNBVV95cUxONUo2T0g4eTB1d2c1MVlmSGxLVjNzYWhMZjRRNXBrTUptVlR5T0lHel9hNGNLRzJDSG1WWTExd0hwTGthZzI4c0dIamJKNDEtWGlad21Fblp3WnEyNTg3emtUak0za3UwNDFaSktXTkxZYVJjaVVTcExUZ3ByaFFMVExLYTQ3ZFRuM0NxUkdnM2QxLVdoR1JGcmtDWWZVVUhSWFFJTXFJX0pJaFFZa0NCRU52aGE1YXRQN0U1V2plQ21Qa0tZTWRuZHpPRUVOQXRGUFhoSFZvWlY1eTlNRVJXYXo5SmFrX1RYckpxaldRSlBWZHdxOTc4VXpLTUdvVnFYWVV0TG1kSmdsMXN1d0JRRzRkd2hUaHZsSUlJUjRqMXVpWmZOenZuTkszbHRhajN3UUZWSW80UndYeG5zT3FwNzl2RHdwTnNGc0Q2T0hsNkZpX3RxX2g4WGk5bXgwYVJVcERVOFV2TnpfVW5MUjJwMk1Md2V4REh6Snl4clFBVXV3UWhpcWFGTXZ4M25zRk85SXVlb25RcVR5SjV6bWY1cHNCQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBnRXl1NjhUajRxdmZERUNWZzVtTmlUcmJXb05HeVA3TUxITDJYWThhZlhOWk5fdGh0TGVpQi1kcDlKaGxTazd6Y1p0OTM4N29tVmZzRjNvVy1CQlluQjkxQnpka9IBY0FVX3lxTFBnRXl1NjhUajRxdmZERUNWZzVtTmlUcmJXb05HeVA3TUxITDJYWThhZlhOWk5fdGh0TGVpQi1kcDlKaGxTazd6Y1p0OTM4N29tVmZzRjNvVy1CQlluQjkxQnpkaw?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46118.82638888889</v>
+        <v>46118.96875</v>
       </c>
     </row>
     <row r="13">
@@ -1095,22 +1095,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amazon’s 3.5% fuel surcharge indicates a lasting disruption in the energy market is becoming entrenched - Bitget</t>
+          <t>How UPS is using AI, from shipper pricing to customs clearance - supplychaindive.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Amazon’s 3.5% fuel surcharge indicates a lasting disruption in the energy market is becoming entrenched - Bitget</t>
+          <t>How UPS is using AI, from shipper pricing to customs clearance - supplychaindive.com</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 23:15:00 GMT</t>
+          <t>Mon, 06 Apr 2026 20:18:50 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBnRXl1NjhUajRxdmZERUNWZzVtTmlUcmJXb05HeVA3TUxITDJYWThhZlhOWk5fdGh0TGVpQi1kcDlKaGxTazd6Y1p0OTM4N29tVmZzRjNvVy1CQlluQjkxQnpka9IBY0FVX3lxTFBnRXl1NjhUajRxdmZERUNWZzVtTmlUcmJXb05HeVA3TUxITDJYWThhZlhOWk5fdGh0TGVpQi1kcDlKaGxTazd6Y1p0OTM4N29tVmZzRjNvVy1CQlluQjkxQnpkaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQ3RpV3ZyRjhKSzAyVGw3VG4yTnZmUzRxUjJzVk03QmVJM1l4QmlRTllQcWVsTEJZanRxVUJTYWpVSVVMM2x0MnZMb1dMNV9FME1TemVDbDA5dEQ5QnJib3doWlpqNndLOFdfNnFxenZvWWYxZEhCYlJBdlB1eXZtVVJrNmItUC1EYzJRbUZOTTE?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46118.96875</v>
+        <v>46118.84641203703</v>
       </c>
     </row>
     <row r="14">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikANBVV95cUxPVWtOLXN0ZGlQNFRVYkNnUTdhaTNDRVZ0ZmRkVHVJNVhJSUpQaFEzT2VPYVpaVHQ5MDU4N3VzcFgtbEFZZ3VBMVRCdWV4SGo4Mk5Od2s2dGE1MHJEZ3hLMDdHU3JUTzhzRkZIRUw0d0hfcHVzQnhYeUNuSU9ENUh6UVdjMmxQVVpEb21fOFZzLUMyMlk4dGJlUm42N3pWY3FlZFhUYjRCaHI1WkxWdjBqM0RpTk9XS3NZWXBNQWxwQXVEbkx6VGRWTFRlTWo0XzZ5cnZqNlRuLUlDNkdCNDJRUGNua3BIT2gxZ0RlWFVKakhjMFlnTFY4V2lxbjZwNE1ELWVnRzlWXzkzajdSUDU5U0d6bnZmU0lvazloUVlkYUJfSWQ0R0F2WTYxc2RWVmpPOTJGaUZTX2NyNmFQQ0dwM09QOFM0bTExR0JQTjZXMFBEVXRac2o5NHl0aWZET2hwQUtYUGxIUklhQzhYX09jcG03SHFqNGc2V1BKLW5mRnc4em9YWEQ4TlN4MUppOEhT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikANBVV95cUxQQy1GRlN6U3hjQkxhQmVqVkxtSEFMRHgwRGZvQVUzcXFCeWVEazlySlVxTnJHcEVIZnljUlFOYzFmZ0hzMU5hZlB4SC1OZUVQN0g0QlRZb2hwOUdFUmd3aUc2eml0Qkx3SHJQVGY3X2tUdm9LWld6QTRWbmtISm9MSVNILUtrUHBxemViaXEyS0MyXzlOczY5QWxvTHI5cWp0dTBpT21jbV9YMHBBSU42SU1peTlIdzU1RV9xcGFhV1RRNUxqdXd0cXNJNnpudDA3WTQ0bVFiMkxSLVhJWTZvdERsQUF1dmVpSjJ1aE5WcWVTNFo3RWZWb1BGUkR5V283NXE0Ykt5dThlZnRGNWRBV0RxTEpObVMtb0dsZlJoX0NQVkFmcUY4TGZwNWU4SjRhOWV6NzQ0WTQtcHlINURGSVNJZ0JfeDBELWNfZUZmUkRWR3hUSFhURkNMLVI3Uk1Pa0dPbHotSms3Mk5HT1ZFVTdYSTRMUEtaOVlUdmtwLXhoMlVFUXZkWXN5ZmZTZTRq?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1205,22 +1205,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How UPS is using AI, from shipper pricing to customs clearance - supplychaindive.com</t>
+          <t>US city to close loophole on Amazon’s ‘dangerous’ delivery scheme - the-sun.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>How UPS is using AI, from shipper pricing to customs clearance - supplychaindive.com</t>
+          <t>US city to close loophole on Amazon’s ‘dangerous’ delivery scheme - the-sun.com</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 20:18:50 GMT</t>
+          <t>Mon, 06 Apr 2026 20:14:24 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQ3RpV3ZyRjhKSzAyVGw3VG4yTnZmUzRxUjJzVk03QmVJM1l4QmlRTllQcWVsTEJZanRxVUJTYWpVSVVMM2x0MnZMb1dMNV9FME1TemVDbDA5dEQ5QnJib3doWlpqNndLOFdfNnFxenZvWWYxZEhCYlJBdlB1eXZtVVJrNmItUC1EYzJRbUZOTTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOTjdiMmZEdXhwSFItdmhHYlFzN2V3NHVlRGtBdFFwcXc2WFhNTy1ReWx4aHBWVHBqRXJYNWRJNW0yVWZIM29jOFhrUzZzSS1qbnU0cmlSaFJROENGUW5KcjlQZHRtQU9zTjFhcHlncUQwZnBIZGlaUms5WmxqVEF2QXJRRkdOc0VVN1BGZTAxQXFEUHJtUW9mNjhtZUJIazFC?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46118.84641203703</v>
+        <v>46118.84333333333</v>
       </c>
     </row>
     <row r="16">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US city to close loophole on Amazon’s ‘dangerous’ delivery scheme - the-sun.com</t>
+          <t>Why you might want to check your Amazon 'delivery instructions' | Money newsletter - Fosse 107</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>US city to close loophole on Amazon’s ‘dangerous’ delivery scheme - the-sun.com</t>
+          <t>Why you might want to check your Amazon 'delivery instructions' | Money newsletter - Fosse 107</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 20:14:24 GMT</t>
+          <t>Mon, 06 Apr 2026 08:28:00 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOTjdiMmZEdXhwSFItdmhHYlFzN2V3NHVlRGtBdFFwcXc2WFhNTy1ReWx4aHBWVHBqRXJYNWRJNW0yVWZIM29jOFhrUzZzSS1qbnU0cmlSaFJROENGUW5KcjlQZHRtQU9zTjFhcHlncUQwZnBIZGlaUms5WmxqVEF2QXJRRkdOc0VVN1BGZTAxQXFEUHJtUW9mNjhtZUJIazFC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTXowMzEtc1RfMWpDRTJSeU54cXRfcHN4S2tzTTQxclBNU3o0eXlVdy1ydFRXbTlpdDg5U1dFZ19nOWU0bk5xZ3Q1LUplSjA3bUdUajNiQUNmZzg5bXNzVDhaN0l6dG5SQTNKZ0JFQVpkbUVFV3NtWHgxdGpKTkZ2TkJBUzJEeGQyWFQ2Nk12QmVqbkE3czZUMU9wdElrbkstenpBV1RYYlpJMHBBYVFydWNrRXdUNFVQRkg2Uk03ZUFvaHM?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46118.84333333333</v>
+        <v>46118.35277777778</v>
       </c>
     </row>
     <row r="17">
@@ -1315,22 +1315,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Why you might want to check your Amazon 'delivery instructions' | Money newsletter - Fosse 107</t>
+          <t>War in Iran: Amazon, UPS, FedEx, USPS add temporary fuel surcharges to offset extra costs - ABC7 San Francisco</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Why you might want to check your Amazon 'delivery instructions' | Money newsletter - Fosse 107</t>
+          <t>War in Iran: Amazon, UPS, FedEx, USPS add temporary fuel surcharges to offset extra costs - ABC7 San Francisco</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 08:28:00 GMT</t>
+          <t>Mon, 06 Apr 2026 13:29:33 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTXowMzEtc1RfMWpDRTJSeU54cXRfcHN4S2tzTTQxclBNU3o0eXlVdy1ydFRXbTlpdDg5U1dFZ19nOWU0bk5xZ3Q1LUplSjA3bUdUajNiQUNmZzg5bXNzVDhaN0l6dG5SQTNKZ0JFQVpkbUVFV3NtWHgxdGpKTkZ2TkJBUzJEeGQyWFQ2Nk12QmVqbkE3czZUMU9wdElrbkstenpBV1RYYlpJMHBBYVFydWNrRXdUNFVQRkg2Uk03ZUFvaHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPSkx4UGpPMEdmYWxqQ09OYlRTQ3Z4SEdIUGhOT0hOajJ0Q0JEYUcweVBfdG96bkZibUtxMTRBTjU0eGJYRVRtZ2g2Z2Ywakh5QUg0TV9zSHBVcWhXRGk1eGxNMm85RkFzNGR6ZlhQbnVmSzdpa0N6Um4tclBSNGNpVm9XWVFvSGFjS2kzSW1HbExzZ01femEzVHFfOXRnMlYwQm1LUFpDUVp0WGpYUVE0UjlITXZmd9IBuwFBVV95cUxPck5yWXE0ZW02NkdENEV1dHA4M2l4RGtpcExtZHVXb3V0MkhTZE1MQkpjVDNnU3lnbGdaYU9Zb3k0YWMxT3RnbGxGWkdXRjdqSEZjTWEtQmQ5T1MwV1RLT3ZyZVFUWlhHMGhJdWVfQ0dFeWZlMVVkazFzc0xDVURuMVFhVVJmWHZHM1BQVnBwWU9YcnRuMEF4eFBVdDRCWlpBS0UxOTF3djNyMEN4a0pfc1F6ZjY1cDVHMGdn?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46118.35277777778</v>
+        <v>46118.5621875</v>
       </c>
     </row>
     <row r="18">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>War in Iran: Amazon, UPS, FedEx, USPS add temporary fuel surcharges to offset extra costs - ABC7 San Francisco</t>
+          <t>How DHL tackled mail and parcel boom during peak Easter season - FreightWaves</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>War in Iran: Amazon, UPS, FedEx, USPS add temporary fuel surcharges to offset extra costs - ABC7 San Francisco</t>
+          <t>How DHL tackled mail and parcel boom during peak Easter season - FreightWaves</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 13:29:33 GMT</t>
+          <t>Mon, 06 Apr 2026 14:26:43 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPSkx4UGpPMEdmYWxqQ09OYlRTQ3Z4SEdIUGhOT0hOajJ0Q0JEYUcweVBfdG96bkZibUtxMTRBTjU0eGJYRVRtZ2g2Z2Ywakh5QUg0TV9zSHBVcWhXRGk1eGxNMm85RkFzNGR6ZlhQbnVmSzdpa0N6Um4tclBSNGNpVm9XWVFvSGFjS2kzSW1HbExzZ01femEzVHFfOXRnMlYwQm1LUFpDUVp0WGpYUVE0UjlITXZmd9IBuwFBVV95cUxPck5yWXE0ZW02NkdENEV1dHA4M2l4RGtpcExtZHVXb3V0MkhTZE1MQkpjVDNnU3lnbGdaYU9Zb3k0YWMxT3RnbGxGWkdXRjdqSEZjTWEtQmQ5T1MwV1RLT3ZyZVFUWlhHMGhJdWVfQ0dFeWZlMVVkazFzc0xDVURuMVFhVVJmWHZHM1BQVnBwWU9YcnRuMEF4eFBVdDRCWlpBS0UxOTF3djNyMEN4a0pfc1F6ZjY1cDVHMGdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNa1NLZ3lKNUdEXzBSQ1R5blk2SUd6SVhRSE1feGVVVVlTZnIwc3hlcG01dlY0VTZfQWdhNk1FcTVacjJ2Y3RQU1NVa2Q0M24tM2owYTlURFBtY25mc2hNUjJEX3pyTnRCc3lGc3ZoWnRoUlVTZC1oWWF5aUJ2SXoxRGZNUnY0OC0tVWhXaWVVbDhSUXJjc05jS0JZZXg?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46118.5621875</v>
+        <v>46118.60188657408</v>
       </c>
     </row>
     <row r="19">
@@ -1425,22 +1425,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How DHL tackled mail and parcel boom during peak Easter season - FreightWaves</t>
+          <t>Will I get mail on Good Friday? USPS, UPS and FedEx delivery schedules on Easter weekend - AOL.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>How DHL tackled mail and parcel boom during peak Easter season - FreightWaves</t>
+          <t>Will I get mail on Good Friday? USPS, UPS and FedEx delivery schedules on Easter weekend - AOL.com</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 14:26:43 GMT</t>
+          <t>Mon, 06 Apr 2026 19:23:09 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNa1NLZ3lKNUdEXzBSQ1R5blk2SUd6SVhRSE1feGVVVVlTZnIwc3hlcG01dlY0VTZfQWdhNk1FcTVacjJ2Y3RQU1NVa2Q0M24tM2owYTlURFBtY25mc2hNUjJEX3pyTnRCc3lGc3ZoWnRoUlVTZC1oWWF5aUJ2SXoxRGZNUnY0OC0tVWhXaWVVbDhSUXJjc05jS0JZZXg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1ZN2I2bzVQUlNPT0VSb3diRk90WTFIemVZOWdCOWhjR3g1RzNCQUppNVZCS1NyMDlqSk5oVGNlSnFidDdJMk1hN1o2b3hlY0gwVzBxdm1YUWZRX2hFV3JIaTJCUkZUOE82eEN2Zg?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46118.60188657408</v>
+        <v>46118.80774305556</v>
       </c>
     </row>
     <row r="20">
@@ -1480,22 +1480,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Will I get mail on Good Friday? USPS, UPS and FedEx delivery schedules on Easter weekend - AOL.com</t>
+          <t>Amazon is hiring independent delivery drivers — Is Amazon Flex worth it? - ConsumerAffairs</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Will I get mail on Good Friday? USPS, UPS and FedEx delivery schedules on Easter weekend - AOL.com</t>
+          <t>Amazon is hiring independent delivery drivers — Is Amazon Flex worth it? - ConsumerAffairs</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 19:23:09 GMT</t>
+          <t>Mon, 06 Apr 2026 18:05:43 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1ZN2I2bzVQUlNPT0VSb3diRk90WTFIemVZOWdCOWhjR3g1RzNCQUppNVZCS1NyMDlqSk5oVGNlSnFidDdJMk1hN1o2b3hlY0gwVzBxdm1YUWZRX2hFV3JIaTJCUkZUOE82eEN2Zg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNZnpwYzRXSXVUS3pOMDhPVVo0U294TDlfX2pxSVM2TFF3ZkpyOTVuMWlxLXpidW8wTXdhTklOa3dtRGtrVlZlcjl1Qzl1S0NOeFdCaU4wU3ZyaVhqQlREVG5KSTJ2TFZ6WFQxRVVWb1M1M1NLMTF4Q0tiRWVLcFZIVzRGbDdFNWhzal9MbFR2Nkh6bFpRR3RZQzlPRFZLT0lQb3hkWlFaM3N0OURqamhtcS01UWFHa2ktd2c?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46118.80774305556</v>
+        <v>46118.7539699074</v>
       </c>
     </row>
     <row r="21">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amazon is hiring independent delivery drivers — Is Amazon Flex worth it? - ConsumerAffairs</t>
+          <t>Amazon launches Prime Air drone delivery in Ruskin, first site in Florida - MSN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Amazon is hiring independent delivery drivers — Is Amazon Flex worth it? - ConsumerAffairs</t>
+          <t>Amazon launches Prime Air drone delivery in Ruskin, first site in Florida - MSN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:05:43 GMT</t>
+          <t>Mon, 06 Apr 2026 16:11:51 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNZnpwYzRXSXVUS3pOMDhPVVo0U294TDlfX2pxSVM2TFF3ZkpyOTVuMWlxLXpidW8wTXdhTklOa3dtRGtrVlZlcjl1Qzl1S0NOeFdCaU4wU3ZyaVhqQlREVG5KSTJ2TFZ6WFQxRVVWb1M1M1NLMTF4Q0tiRWVLcFZIVzRGbDdFNWhzal9MbFR2Nkh6bFpRR3RZQzlPRFZLT0lQb3hkWlFaM3N0OURqamhtcS01UWFHa2ktd2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wJBVV95cUxPZ3EyZGt2ZkVDTWpoTWNfLXpZWHVQaklhQjdYU0hDQnN4WWo5cEY5YWl3YVpQWUYwU0ZMNExvcFh1a3FhejAyMTl4SHZHb3FTWEtKQkdVbGoxZ1lvTXVZengzWlgyQ0IxMGFlYkxMUU9NNFk5TnRHcXJUdmhkNWhPajZneXN5N1YxRVdQZ3lkajBJdUo3UlRjaUM5UlFSMll6UEJWY3JwR1B4b0Z3eUk2MmNCZWdTY1FiSVhzOUxtZTRRTUdiTlA2VWExZlNLUnVZZ3hrNDVqUV9FU2w3NVpwQmJNLU1ONWY5TXR2UV9Bbi1wa3J2akd6bzNtcFdRd1V1MkJHam83NHNIMlMxc1Vha21LZ2xGelh3VUo3OHRrNW1JeWhOcThOOGkyazJVY3JZWGFBWGhPNlN0Rk5VQ0xjRXMwb1U5dWZidFRkSGl1elFDMzNBT1RlRE80NA?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46118.7539699074</v>
+        <v>46118.67489583333</v>
       </c>
     </row>
     <row r="22">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FedEx, Amazon up race for faster delivery - MSN</t>
+          <t>Amazon launches new way to order UberEats, Grubhub with Alexa: ‘Same way you would with a waiter’ - New York Post</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FedEx, Amazon up race for faster delivery - MSN</t>
+          <t>Amazon launches new way to order UberEats, Grubhub with Alexa: ‘Same way you would with a waiter’ - New York Post</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 14:25:47 GMT</t>
+          <t>Mon, 06 Apr 2026 17:57:00 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPNndiT3dfX3VEODhzY2Y1dURQUy0wN21GVTBqMmdsa3A4LXY3U2Rud3ZSUEM1T1Rtd2VWSFVPcW1YMmx3enN4WHdwUnJVY1RIOXB3eG1rdFc3VnRyNXo4aTFGR190bTNCVGZfNHR2WDZySzYwc2lCMkJXTVotd3NoVTg1b2lQMVpSVk5TRGdmV1ZEbnVJNzZvRU13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPcktESmozd0RSZ0FUeTFqaHlPVUtVX1lOeFY2YWVzTTBqZnliUzNGcHZLb3VBejd1cV85VnIyelVwRXdBWVh3VktHNThzbEd4QWJBOGxrT21scVRHSWRUaGd6bEh2VzFGZExDRkN1Z0xCclBoTkxCWE5ZOV9FMXVScXNkeUREMGEzOXJRMmc4WHkzeW9Vakpndk1mV0hxUDRrdWN1U2NpZGoxWkJ0RGgxYWphNEZOd1FEOWZXOTNQMkh2cXlvcndCaGFKeEtOaDNfQzlB?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46118.60123842592</v>
+        <v>46118.74791666667</v>
       </c>
     </row>
     <row r="23">
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Amazon launches new way to order UberEats, Grubhub with Alexa: ‘Same way you would with a waiter’ - New York Post</t>
+          <t>Amazon delivery partner in Weston shuts down - WXPR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Amazon launches new way to order UberEats, Grubhub with Alexa: ‘Same way you would with a waiter’ - New York Post</t>
+          <t>Amazon delivery partner in Weston shuts down - WXPR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 17:57:00 GMT</t>
+          <t>Mon, 06 Apr 2026 12:03:00 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPcktESmozd0RSZ0FUeTFqaHlPVUtVX1lOeFY2YWVzTTBqZnliUzNGcHZLb3VBejd1cV85VnIyelVwRXdBWVh3VktHNThzbEd4QWJBOGxrT21scVRHSWRUaGd6bEh2VzFGZExDRkN1Z0xCclBoTkxCWE5ZOV9FMXVScXNkeUREMGEzOXJRMmc4WHkzeW9Vakpndk1mV0hxUDRrdWN1U2NpZGoxWkJ0RGgxYWphNEZOd1FEOWZXOTNQMkh2cXlvcndCaGFKeEtOaDNfQzlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQR0tuOWJSU0tyWnhlZ3hCMDdvTF9Rdm9NYi1INzd1TXFPLXBOWk9LbmZfV3NjbWQxN0cxdktLUDdsQzUwMFR1TlRKRW1WNkVRbjhPRVdxWmJuakdSRFFMbmFBbEdjYlNIbTNQODJEcXFaY3ZkeG04cW1mRnkzeHFyYTdnOGx5U0VoSUdTRGdIT0xOOVpSVVBvQzh6TQ?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46118.74791666667</v>
+        <v>46118.50208333333</v>
       </c>
     </row>
     <row r="24">
@@ -1700,22 +1700,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Amazon delivery partner in Weston shuts down - WXPR</t>
+          <t>FedEx's same-day delivery rollout is more about optionality than speed - MSN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Amazon delivery partner in Weston shuts down - WXPR</t>
+          <t>FedEx's same-day delivery rollout is more about optionality than speed - MSN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 12:03:00 GMT</t>
+          <t>Sun, 05 Apr 2026 12:12:38 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQR0tuOWJSU0tyWnhlZ3hCMDdvTF9Rdm9NYi1INzd1TXFPLXBOWk9LbmZfV3NjbWQxN0cxdktLUDdsQzUwMFR1TlRKRW1WNkVRbjhPRVdxWmJuakdSRFFMbmFBbEdjYlNIbTNQODJEcXFaY3ZkeG04cW1mRnkzeHFyYTdnOGx5U0VoSUdTRGdIT0xOOVpSVVBvQzh6TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNMzhWcVlwQUk5RlUzTEx6anZabHBhM0hFNjlyOGg0RFRhV3NQV0c0N2xwbXlvbVU1UC1DSXBCS0Y2WUVNOXdWZnlFNk45R3I5bGdQVENLbzYycUZGcFhMWmp5alZsV2RRMDEyUHFjNUpEY01jZ3NPWDZ1QkF6VFlTeVVncHZtUlh3dW94bWlLWC1hUExGdnJ4VnFtQzRMTzRLWmg3ZlRDdkpWQjk4LTQtTEtjVUhnRkc1WktBNENRQTE5QQ?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46118.50208333333</v>
+        <v>46117.50877314815</v>
       </c>
     </row>
     <row r="25">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Is Easter Monday a federal holiday? Will mail get delivered? What to know - The Courier-Journal</t>
+          <t>New York Is Closing In on Amazon’s Shady Delivery System - Jacobin</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Is Easter Monday a federal holiday? Will mail get delivered? What to know - The Courier-Journal</t>
+          <t>New York Is Closing In on Amazon’s Shady Delivery System - Jacobin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 09:09:00 GMT</t>
+          <t>Sun, 05 Apr 2026 16:55:48 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOWUVPVWlfWHB2elc5X0U4eGdQMDNPc2FNMVZQbXpLTUJfdVg1bEFSV09LRDhJbkhGb3pySWhKOU5uU3Z0QzlNc2hTc29aRUwzZnBIakJjY0FYTXA4Z3VmQWFObjBONHNZTnVCUXRYOTh5NE9qU01yc0NMN3VyQU9LYUE1LUsyQ2lkSXNkV0t5ZU80WGwxd2x0N0xLVm9RZGFWYkNNeFp2dVMxRDFLU3FMMVV1bWd4VW9CZnh6aG9zRDVGV1hQOTVRbzEzbno5N3hI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9aeHJsTmNIWUgxOFhGS19MSTJlX1BfbVVRaHhXcmhtRUVYZXNFX2E0UXROTWllSldlVTV5OTRWZ2FrMFl1b2xZVkRBWFFKM0loYVpyOUNZdUtYaFZwN3RZc3lram9UbjZTdU01b2VhSHE2M2N4aUttRWtOREpuQQ?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46118.38125</v>
+        <v>46117.70541666666</v>
       </c>
     </row>
     <row r="27">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York Is Closing In on Amazon’s Shady Delivery System - Jacobin</t>
+          <t>UPS sets limits on driver buyouts in deal with Teamsters union - supplychaindive.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>New York Is Closing In on Amazon’s Shady Delivery System - Jacobin</t>
+          <t>UPS sets limits on driver buyouts in deal with Teamsters union - supplychaindive.com</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 16:55:48 GMT</t>
+          <t>Mon, 06 Apr 2026 14:54:19 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9aeHJsTmNIWUgxOFhGS19MSTJlX1BfbVVRaHhXcmhtRUVYZXNFX2E0UXROTWllSldlVTV5OTRWZ2FrMFl1b2xZVkRBWFFKM0loYVpyOUNZdUtYaFZwN3RZc3lram9UbjZTdU01b2VhSHE2M2N4aUttRWtOREpuQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbTM5NzQ4XzdsNUF1cW9EaFB1XzZrYUl5ZU1HUDlZem9Jd2FHWGFlSFRhdWVPQ1FpeWxYRnplUDZaTkwzSFRRRGF5RHowMnFXWmJEVTA5X1U5V3BGejRWZncyLXNaOVhYVk5yTlhPWEFrTVc5R2h5clZnbWhZZDFpUnVpX1BTYmx0eWpSY0phejZUd09XZEoyVEIzdw?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46117.70541666666</v>
+        <v>46118.62105324074</v>
       </c>
     </row>
     <row r="29">
@@ -1975,22 +1975,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UPS sets limits on driver buyouts in deal with Teamsters union - supplychaindive.com</t>
+          <t>Is Easter Monday a federal holiday? Will mail get delivered? What to know - The Courier-Journal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UPS sets limits on driver buyouts in deal with Teamsters union - supplychaindive.com</t>
+          <t>Is Easter Monday a federal holiday? Will mail get delivered? What to know - The Courier-Journal</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 14:54:19 GMT</t>
+          <t>Mon, 06 Apr 2026 09:09:00 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbTM5NzQ4XzdsNUF1cW9EaFB1XzZrYUl5ZU1HUDlZem9Jd2FHWGFlSFRhdWVPQ1FpeWxYRnplUDZaTkwzSFRRRGF5RHowMnFXWmJEVTA5X1U5V3BGejRWZncyLXNaOVhYVk5yTlhPWEFrTVc5R2h5clZnbWhZZDFpUnVpX1BTYmx0eWpSY0phejZUd09XZEoyVEIzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOWUVPVWlfWHB2elc5X0U4eGdQMDNPc2FNMVZQbXpLTUJfdVg1bEFSV09LRDhJbkhGb3pySWhKOU5uU3Z0QzlNc2hTc29aRUwzZnBIakJjY0FYTXA4Z3VmQWFObjBONHNZTnVCUXRYOTh5NE9qU01yc0NMN3VyQU9LYUE1LUsyQ2lkSXNkV0t5ZU80WGwxd2x0N0xLVm9RZGFWYkNNeFp2dVMxRDFLU3FMMVV1bWd4VW9CZnh6aG9zRDVGV1hQOTVRbzEzbno5N3hI?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2014,38 +2014,38 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46118.62105324074</v>
+        <v>46118.38125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>XR JSO Village Search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Extinction Rebellion" OR "Just Stop Oil" OR "climate protest" OR "environmental protest") AND ("Ingolstadt" OR "Kildare" OR "Vallee" OR "Bicester" OR "Wertheim" OR "Las Rozas" OR "La Roca" OR "Fidenza" OR "Maasmechelen")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Protest outside Leinster House calling for action to protect Irish seas - wlrfm.com</t>
+          <t>Amazon–USPS deal averts major blow, postal service retains 80% of delivery business - Firstpost</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Protest outside Leinster House calling for action to protect Irish seas - wlrfm.com</t>
+          <t>Amazon–USPS deal averts major blow, postal service retains 80% of delivery business - Firstpost</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 04:56:21 GMT</t>
+          <t>Tue, 07 Apr 2026 02:58:32 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOaUpEMGp4S2hyb3drXzhHMF84SDU2S1lPY20yNDJYTWlseVpEWmMzZ0VqekRBTmJPZWF2LV9UOG1maFU3TmVCYmFLMmlPN0NTQTJ1MjVWZngwdUZqTW9iY1ptMU53eXIzZDY1bjVRNmFlOFRBR0xvSU5INW4tWV9CYkJJZDgzTlpPTnVMUkg2RHJEM3I0WTdaWG90ZnFxZFpWLThLNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxORV9zZGVCQzFlZWZQTWdhUi1SaTBTd2FEZUFHLVZ1dlRWcHBwb2tuZ3psWkxPc1NkY2RCUHRoR2Y2b2lLeTc4dUhERlRkY0Fid1BvdXNJZGtPU3Y5R002Q2VfN1o5QURmaEx5NmotalhieXFIMWFuamNfOVFQTFQyT3pOWTJKUUJuRURfX2dpZG1QTno0MS1KRjl3NzR3eE5yZVJnVXlQOEZnQVoydFdqc3hUYWVEUlh2YTVXRVlFc0haNUZDcWFwWWRnRURPY1gt0gHWAUFVX3lxTFB2NWlhZ3k5RXl4d1pIR182MDFBRlo2ejlNNU1OdzNLUFh5Tmc5RTNpZWhtRWNsWkdGQjJKelFuWUxVazhpRmRiMHVnaDZ0X1BWM1V1TF9FRmVrVVNLZFVGUzAycnExTXY1TlROYjdNOFpoeWJJWGw2R0Fwa1lMWElmTk5adVVQaGVhTnc3R19hYmYzT0dFRkQ3dEhwUkVLazdRU3Q0X3JyazRZMERkMVJrbkhLSnNjcW1KdVNMa3A1Rnp0SGlRLWI1dWJoSmpKR0thSEJCUFE?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2069,38 +2069,38 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46118.20579861111</v>
+        <v>46119.12398148148</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>XR JSO Village Search</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("shoplifting" OR "retail theft" OR "retail crime" OR "shop theft" OR "pickpocket") AND ("UK" OR "England" OR "Britain") AND ("gang" OR "organised" OR "trend" OR "rise" OR "survey" OR "report")</t>
+          <t>("Extinction Rebellion" OR "Just Stop Oil" OR "climate protest" OR "environmental protest") AND ("Ingolstadt" OR "Kildare" OR "Vallee" OR "Bicester" OR "Wertheim" OR "Las Rozas" OR "La Roca" OR "Fidenza" OR "Maasmechelen")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>London shops struggle with daily theft as Met reports success on shoplifting - BBC</t>
+          <t>Protest outside Leinster House calling for action to protect Irish seas - wlrfm.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>London shops struggle with daily theft as Met reports success on shoplifting - BBC</t>
+          <t>Protest outside Leinster House calling for action to protect Irish seas - wlrfm.com</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 07:47:50 GMT</t>
+          <t>Mon, 06 Apr 2026 04:56:21 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1JUVNMVlVTNk0wV21nemxPRVdYT0o5dHFSZ2Nqalp3MmtTNkNSbEY2d1FqZVk4X0VneE1TdkpqZ0lNcU91ZTNlMkpUY2IwZGpaX0kwdkJ2N3ktdlBM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOaUpEMGp4S2hyb3drXzhHMF84SDU2S1lPY20yNDJYTWlseVpEWmMzZ0VqekRBTmJPZWF2LV9UOG1maFU3TmVCYmFLMmlPN0NTQTJ1MjVWZngwdUZqTW9iY1ptMU53eXIzZDY1bjVRNmFlOFRBR0xvSU5INW4tWV9CYkJJZDgzTlpPTnVMUkg2RHJEM3I0WTdaWG90ZnFxZFpWLThLNg?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46115.32488425926</v>
+        <v>46118.20579861111</v>
       </c>
     </row>
     <row r="32">
@@ -2140,22 +2140,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M&amp;S calls for crackdown on ‘brazen, organised, aggressive’ retail crime | Marks &amp; Spencer - The Guardian</t>
+          <t>London shops struggle with daily theft as Met reports success on shoplifting - BBC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>M&amp;S calls for crackdown on ‘brazen, organised, aggressive’ retail crime | Marks &amp; Spencer - The Guardian</t>
+          <t>London shops struggle with daily theft as Met reports success on shoplifting - BBC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sat, 04 Apr 2026 01:30:00 GMT</t>
+          <t>Fri, 03 Apr 2026 07:47:50 GMT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQZWRtNlo4TkJJYy1pVF83enhHZ2FFWUtyZnF4MXE5a3diNEc1YTU2S0l5UFByZUtXRUVnTkhnUVJQbENTNDQyYzF0ckljcTZfUVBqNk9lM1BjeHQtbVpBbnB4bS1hZHJsTHNDUjVOQXktTnNIcjBoaDBWZVl0aEZEbVZhSk8xRmZtNFNqLTU2aUJDYXZnSXlwZGpLRmlDRUtT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1JUVNMVlVTNk0wV21nemxPRVdYT0o5dHFSZ2Nqalp3MmtTNkNSbEY2d1FqZVk4X0VneE1TdkpqZ0lNcU91ZTNlMkpUY2IwZGpaX0kwdkJ2N3ktdlBM?oc=5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2179,38 +2179,38 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46116.0625</v>
+        <v>46115.32488425926</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("shoplifting" OR "retail theft" OR "retail crime" OR "shop theft" OR "pickpocket") AND ("UK" OR "England" OR "Britain") AND ("gang" OR "organised" OR "trend" OR "rise" OR "survey" OR "report")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Man in levensgevaar na steekpartij in stationsbuurt Antwerpen - VRT</t>
+          <t>M&amp;S calls for crackdown on ‘brazen, organised, aggressive’ retail crime | Marks &amp; Spencer - The Guardian</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Man in danger of life after stabbing in Antwerp station area - VRT</t>
+          <t>M&amp;S calls for crackdown on ‘brazen, organised, aggressive’ retail crime | Marks &amp; Spencer - The Guardian</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:35:05 GMT</t>
+          <t>Sat, 04 Apr 2026 01:30:00 GMT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNS1dIeGtRVjRoU1BUaDhuVmFVbzIwSmtoX0VFd1p6dVI2MWNxbXc0VE81TU8tSlVzdWc5MnNka0ItdzRHcTVORTFUQUk5NE5sVThJZGxvU3pMVnEyeUZqWlpDUnRGTXhSWTJucTI4dE5qdERjZXVPbmg1YXI5UDhWNEtaZlFnTmplcmlHd1k4b3lqajluOXBQbDltc1FKM3FhQ2hBSHNSamU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQZWRtNlo4TkJJYy1pVF83enhHZ2FFWUtyZnF4MXE5a3diNEc1YTU2S0l5UFByZUtXRUVnTkhnUVJQbENTNDQyYzF0ckljcTZfUVBqNk9lM1BjeHQtbVpBbnB4bS1hZHJsTHNDUjVOQXktTnNIcjBoaDBWZVl0aEZEbVZhSk8xRmZtNFNqLTU2aUJDYXZnSXlwZGpLRmlDRUtT?oc=5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2220,52 +2220,52 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46118.6910300926</v>
+        <v>46116.0625</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("shoplifting" OR "retail theft" OR "retail crime" OR "shop theft" OR "pickpocket") AND ("UK" OR "England" OR "Britain") AND ("gang" OR "organised" OR "trend" OR "rise" OR "survey" OR "report")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Twee jongeren worden betrapt terwijl ze een bromfiets aan het stelen zijn - Nieuwsblad</t>
+          <t>M&amp;S boss calls for more action on crime and abuse of staff - BBC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Two young people are caught stealing a moped - Nieuwsblad</t>
+          <t>M&amp;S boss calls for more action on crime and abuse of staff - BBC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:35:15 GMT</t>
+          <t>Fri, 03 Apr 2026 05:40:00 GMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOb0ExZ0VzR0pUTkZQclpnLWRiRG5kMDk0Rzd4djFSQ0xKSEVTRVZBMk1hRTlmMkRySWxhZHJpSUN4RXdlY1BoVVVjV3FFMGJnZncxQ25JbzFhZ29OMUlhdFFTU2tHOGFHUnNjYjFtQmRYeGJwU012R3dzZlA2dlktd25zMW4wU05ORmoyUTNZb0hQMDlGTmg5R3NGcTI5V0RadkdwQ2oxa2xreF9RdFhERjNKRjljZ1BGVVBGNFc5QXJoOW5xN1pEZ1ZxN2k3VXhQaXpVRTc5OE5VUVFtNkZLaml2NlhxV0NnVzRMcjFqNW85QWtYVk9KR25zcmFmM1BUbURGdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9VWEZDeFR6emRrMndEYXFUY2xqY3J1T3JxX1B5TnVVZkZIYVVuclpzOEtKZlNLeXdMdHdmVUM2cWw3Y1NQUkZqOWNFZVl0X2Z6N09JMnVfd1E1Smdq?oc=5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2275,21 +2275,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46118.77447916667</v>
+        <v>46115.23611111111</v>
       </c>
     </row>
     <row r="35">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eén van veroordeelden aanslagen 22 maart na tien jaar vrij - HLN</t>
+          <t>Man in levensgevaar na steekpartij in stationsbuurt Antwerpen - VRT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>One of those convicted of attacks on March 22 is released after ten years - HLN</t>
+          <t>Man in danger of life after stabbing in Antwerp station area - VRT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 17:38:45 GMT</t>
+          <t>Mon, 06 Apr 2026 16:35:05 GMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOd3NfbFBleDhZcE5oc1JBMmdVUEpsR09ORU1ZdTRyallMWS1Od21DN1p5a0dMME5HQ3FQMUpxMkJaYjBiejlQeVIzLXVYUUp1eGdxTWU2NFJoN2JUN2p2eVUtOVBjNWI4ekw3VEl1NkstcUUzNl9jbkxrWm41SjZTMjFFZzBQLXdNQmNHVXpTanZ6SUxMU0JJQTFfZ2hYMXkxRTAxNFJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNS1dIeGtRVjRoU1BUaDhuVmFVbzIwSmtoX0VFd1p6dVI2MWNxbXc0VE81TU8tSlVzdWc5MnNka0ItdzRHcTVORTFUQUk5NE5sVThJZGxvU3pMVnEyeUZqWlpDUnRGTXhSWTJucTI4dE5qdERjZXVPbmg1YXI5UDhWNEtaZlFnTmplcmlHd1k4b3lqajluOXBQbDltc1FKM3FhQ2hBSHNSamU?oc=5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46118.73524305555</v>
+        <v>46118.6910300926</v>
       </c>
     </row>
     <row r="36">
@@ -2360,22 +2360,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Twee jaar na alle commotie haalt ‘Klopjacht’ het scherm, deelnemer Yahya dan toch niet geschrapt - Nieuwsblad</t>
+          <t>Twee jongeren worden betrapt terwijl ze een bromfiets aan het stelen zijn - Nieuwsblad</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Two years after all the commotion, 'Manhunt' makes it to the screen, participant Yahya is not deleted after all - Nieuwsblad</t>
+          <t>Two young people are caught stealing a moped - Nieuwsblad</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:15:54 GMT</t>
+          <t>Mon, 06 Apr 2026 18:35:15 GMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPRXp1S1JuZ3FQZmJIZzJFeXUwcllxY21yR05pSW1Bd3BmMHRtMEl3VUI1b09QTGV5WXNYY0ozT242bGNZM0NSQy1tLVhNSllTRnVjQlRXWkF6SHlaS1RYb01aVlMyWG83c01zd283RlVydjMtX25TS0xPMUFVVzdzQmVXM0JaeVo5b2hVV25MSURwdHZFYnRHUklYRnpyejcyUkVkd0ZNSWdNNjVoMHU1eTdUc0NQYlctM0ZaT1EyM1RJTUlCalNEaGhMN0VfLWFBWlh0UXV3TDlqdWhuOWszV0hCSXRDUnRSTXdXdExDZG40b3ctdmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOb0ExZ0VzR0pUTkZQclpnLWRiRG5kMDk0Rzd4djFSQ0xKSEVTRVZBMk1hRTlmMkRySWxhZHJpSUN4RXdlY1BoVVVjV3FFMGJnZncxQ25JbzFhZ29OMUlhdFFTU2tHOGFHUnNjYjFtQmRYeGJwU012R3dzZlA2dlktd25zMW4wU05ORmoyUTNZb0hQMDlGTmg5R3NGcTI5V0RadkdwQ2oxa2xreF9RdFhERjNKRjljZ1BGVVBGNFc5QXJoOW5xN1pEZ1ZxN2k3VXhQaXpVRTc5OE5VUVFtNkZLaml2NlhxV0NnVzRMcjFqNW85QWtYVk9KR25zcmFmM1BUbURGdw?oc=5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46118.67770833334</v>
+        <v>46118.77447916667</v>
       </c>
     </row>
     <row r="37">
@@ -2415,22 +2415,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pro-Iraanse beweging Hayi zet video explosie Nederlands Israëlcentrum online - HLN</t>
+          <t>Eén van veroordeelden aanslagen 22 maart na tien jaar vrij - HLN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pro-Iranian movement Hayi puts video explosion Dutch Israel Center online - HLN</t>
+          <t>One of those convicted of attacks on March 22 is released after ten years - HLN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 13:20:30 GMT</t>
+          <t>Mon, 06 Apr 2026 17:38:45 GMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNZklTVXFTd3hHRXlDZ1c0SU9aanFUNk9TRS01RDN2NmNPUlpZTVVGTnpJZGVEbXQybTI3S3JHN01JRVdmeUhqNFNrQ2NPN2N6aEh5Q0QyLVFubzc1OEp3MnVVQnRyQWI1Sk5QM0xMOW9NY0JuWTdRS0xjQjVVcTFSR1R6Umhhckg2aFQwWXFEOVlTdU9nMnVVLUtsYnNWVDRmZFRUekJwelNSM08wZGRCNjdWR2hQODA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOd3NfbFBleDhZcE5oc1JBMmdVUEpsR09ORU1ZdTRyallMWS1Od21DN1p5a0dMME5HQ3FQMUpxMkJaYjBiejlQeVIzLXVYUUp1eGdxTWU2NFJoN2JUN2p2eVUtOVBjNWI4ekw3VEl1NkstcUUzNl9jbkxrWm41SjZTMjFFZzBQLXdNQmNHVXpTanZ6SUxMU0JJQTFfZ2hYMXkxRTAxNFJ3?oc=5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46117.55590277778</v>
+        <v>46118.73524305555</v>
       </c>
     </row>
     <row r="38">
@@ -2470,22 +2470,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>E17 versperd in Kruibeke richting Antwerpen door twee ongevallen: “Hinder is momenteel beperkt” - Nieuwsblad</t>
+          <t>Twee jaar na alle commotie haalt ‘Klopjacht’ het scherm, deelnemer Yahya dan toch niet geschrapt - Nieuwsblad</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>E17 blocked in Kruibeke towards Antwerp due to two accidents: “Inconvenience is currently limited” - Nieuwsblad</t>
+          <t>Two years after all the commotion, 'Manhunt' makes it to the screen, participant Yahya is not deleted after all - Nieuwsblad</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 14:30:00 GMT</t>
+          <t>Mon, 06 Apr 2026 16:15:54 GMT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxQUTJfbTV0ek81RFJxeXdGTXFhX2lENUNMZVhxTFRHX0FpR0lGdGhta1dHTVVvRVJkR3dDNnFMUW5QUHQzZnduem04U2lkY2pnS1NiVENZNk9sNmZ2ZnFpR2ozN3oyQkZzVC02MjdTV3Y3UXFsZ0dOTmxUWDBPNGRyc29LWk9uSERuMXhwNjZTZzYtUDA1UkNJUnVzUUQ1ZUtqY3hyaWxVYUo5NWZpMGRVUFlqc2xZdGVJaTU2cEx4a2dfeVpjcDd0aUFlb1dYeV9pQ2lhU3VVaFptQm1lZF9hZXJMUF9LS21xZ0hQWkRtTWtnWWp1bHRuV2RyY0RHclV2M3JPekJEYkZjbTdybi1CTGlvY2hmUlYycEd3Uzln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPRXp1S1JuZ3FQZmJIZzJFeXUwcllxY21yR05pSW1Bd3BmMHRtMEl3VUI1b09QTGV5WXNYY0ozT242bGNZM0NSQy1tLVhNSllTRnVjQlRXWkF6SHlaS1RYb01aVlMyWG83c01zd283RlVydjMtX25TS0xPMUFVVzdzQmVXM0JaeVo5b2hVV25MSURwdHZFYnRHUklYRnpyejcyUkVkd0ZNSWdNNjVoMHU1eTdUc0NQYlctM0ZaT1EyM1RJTUlCalNEaGhMN0VfLWFBWlh0UXV3TDlqdWhuOWszV0hCSXRDUnRSTXdXdExDZG40b3ctdmc?oc=5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46118.60416666666</v>
+        <v>46118.67770833334</v>
       </c>
     </row>
     <row r="39">
@@ -2525,22 +2525,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Controle verdachte bromfietser leidt tot cocaïnelab in appartement - Nieuwsblad</t>
+          <t>Pro-Iraanse beweging Hayi zet video explosie Nederlands Israëlcentrum online - HLN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Check on suspected moped rider leads to cocaine lab in apartment - Nieuwsblad</t>
+          <t>Pro-Iranian movement Hayi puts video explosion Dutch Israel Center online - HLN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 17:16:00 GMT</t>
+          <t>Sun, 05 Apr 2026 13:20:30 GMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNZFBXMWlDY0pwMmNndlNTOWdSeU5Dbi1LeEtUUlNtVFE2dWI0bDZrcEtZTTJreXVvRHZ2eWkwWmZCMHNBQkZDNUg3Y3E5MGtrMUVsZzFCaWF2TGFOSkJ3MkhGRzl1bjcyVWhySXE5eWQ1LS11VXZwS1ZFdThNNmd4Uy1ORzJFRUFLNGd0LUFGdll2ajVUTXJmUkY5OWZJQWI2cW5uQkRsOVRvZm43RTRKMlVuV2x3c0dJYlVwT1hBc3N1U2lXXzZBSVNtWXdLemZuZHNrM2RqSDYtaks3Q2lqQmNoa3p6N1pEUjlPQVRZSkJfalU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNZklTVXFTd3hHRXlDZ1c0SU9aanFUNk9TRS01RDN2NmNPUlpZTVVGTnpJZGVEbXQybTI3S3JHN01JRVdmeUhqNFNrQ2NPN2N6aEh5Q0QyLVFubzc1OEp3MnVVQnRyQWI1Sk5QM0xMOW9NY0JuWTdRS0xjQjVVcTFSR1R6Umhhckg2aFQwWXFEOVlTdU9nMnVVLUtsYnNWVDRmZFRUekJwelNSM08wZGRCNjdWR2hQODA?oc=5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46117.71944444445</v>
+        <v>46117.55590277778</v>
       </c>
     </row>
     <row r="40">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dodelijk ongeval met werfvoertuig op E40 in Soumagne - GVA</t>
+          <t>E17 versperd in Kruibeke richting Antwerpen door twee ongevallen: “Hinder is momenteel beperkt” - Nieuwsblad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fatal accident with construction site vehicle on E40 in Soumagne - GVA</t>
+          <t>E17 blocked in Kruibeke towards Antwerp due to two accidents: “Inconvenience is currently limited” - Nieuwsblad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 09:59:52 GMT</t>
+          <t>Mon, 06 Apr 2026 14:30:00 GMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNlQxekt5WnJWUmdUOTBubzhYRFhOdTJfeUllWkt0UFBpRGdya2tWVVh4VXdXdWFZZ3lJdXNLQ2VINjNKMm5lVUk4UUY1NF9nMng3LTBiY3JUbHhlRlZBQlYzbE5ISWMzTWZ5NHZ2QlhLRmJjR1JWQWpPTHczZ0ZsRmVoVWFBeE5oTVdCYnQ1RFpGRWF0dmNhY3M4VUhWUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxQUTJfbTV0ek81RFJxeXdGTXFhX2lENUNMZVhxTFRHX0FpR0lGdGhta1dHTVVvRVJkR3dDNnFMUW5QUHQzZnduem04U2lkY2pnS1NiVENZNk9sNmZ2ZnFpR2ozN3oyQkZzVC02MjdTV3Y3UXFsZ0dOTmxUWDBPNGRyc29LWk9uSERuMXhwNjZTZzYtUDA1UkNJUnVzUUQ1ZUtqY3hyaWxVYUo5NWZpMGRVUFlqc2xZdGVJaTU2cEx4a2dfeVpjcDd0aUFlb1dYeV9pQ2lhU3VVaFptQm1lZF9hZXJMUF9LS21xZ0hQWkRtTWtnWWp1bHRuV2RyY0RHclV2M3JPekJEYkZjbTdybi1CTGlvY2hmUlYycEd3Uzln?oc=5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46118.41657407407</v>
+        <v>46118.60416666666</v>
       </c>
     </row>
     <row r="41">
@@ -2635,22 +2635,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Auto blokkeert verkeer voor trouwstoet in Borgerhout: bestuurder test positief op drugs - Nieuwsblad</t>
+          <t>Koets zonder paard verdeelt Antwerpen: “Je glijdt door de stad, maar het hoefgetrappel ontbreekt” - Nieuwsblad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Car blocks traffic for wedding procession in Borgerhout: driver tests positive for drugs - Nieuwsblad</t>
+          <t>Horseless carriage divides Antwerp: “You glide through the city, but the hooves are missing” - Nieuwsblad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 22:16:55 GMT</t>
+          <t>Mon, 06 Apr 2026 17:26:37 GMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQdXd4dmZoQnhoTzZQb195U05HbkFSbVBiOEtwbkpQZGttN20xQjNwaTNoUTdjYmFVaDBKdmtLRG5RNDVNUGw5dTZwNXc3WTlHTjFORzJDV0YwX1RCWlR1Z0xfMl9sZkRiQjFZaGtQajZoTjdZc2NiWlg2QUdTQTlONVpTR2t3cFdwVTVLVUw2eVZnM1ZxR0U3MldjRDdsQVNETThlS0lEbC1IOFgtWVNidjMtNDZHbTlVckZhVngya3pRMzRJSjJOUHNIRmJqSEtPQlVKbVZDQXRhR1d6YjBKd3k2dUtSZDZ6V2Q4dmV1bTl5bW9pTF9WcGFiWi1tdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQMDYxMXdpbHFnUF8yaERkU2hQMjB6aXBEWThhZ3dUR3BwMFRrLUFxc1R0Z2ZDTnJ4NUlZQnRZdzZRSEc3azloMUw2c1lFeXpvOVFrUWxOX1RxWHFaMWVnc2Zzam5qdnZRejV5Y1hVYlNCcV9ETC1KN0pGM1BodlNVRjZFSkRHbGtoYmlLbU51bVVNbzRTZTk4WmVGUU43eURaM3EyZTlrMlZlOXJNRU85dVhscVU5Z05tY29ESTE5UkNWQm5UVkFqUWYyNk9MX1R6eUlwR3RYc2QwMWRvS2dVaDlNV0FsWHlTV1hwSjYtUEIzNVV4MnBGTHdwaU5ucUNUc3RuUWFvZw?oc=5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46117.92841435185</v>
+        <v>46118.72681712963</v>
       </c>
     </row>
     <row r="42">
@@ -2690,22 +2690,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vierde verdachte opgepakt in Londense rechtbank in onderzoek naar brandstichting bij Joodse ambulances - Nieuwsblad</t>
+          <t>Dodelijk ongeval met werfvoertuig op E40 in Soumagne - GVA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fourth suspect arrested in London court in investigation into arson of Jewish ambulances - Nieuwsblad</t>
+          <t>Fatal accident with construction site vehicle on E40 in Soumagne - GVA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 11:02:00 GMT</t>
+          <t>Mon, 06 Apr 2026 09:59:52 GMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQYzRGcWl2a2h4YWFQMGR2X3lBQ21MNkNfbzJBd0c0ZkZhRzVkWHd2MTRucldRNS1mMEd6LVN4eXJBeEotYjFIVHJUdDJnYmxybjNHc1hlN2ZfVUZlMW5MeVE0MC11b1ZYemhUSkstNDJNUGl2LWR4aHM3ckp0UC1fSkY2ank4T1BpMnd4VXNud1VNTi1oMG9MYkpKZnI0TUZJTzBSRldxcWFPNm5hWm40OGNleG5OM2pObmthVGVFTTVDdUNocmlWZWZNZlJEbFZ3cEFrS0hqRS05d1ZaWjdvVDNGN2Q1dU90QVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNlQxekt5WnJWUmdUOTBubzhYRFhOdTJfeUllWkt0UFBpRGdya2tWVVh4VXdXdWFZZ3lJdXNLQ2VINjNKMm5lVUk4UUY1NF9nMng3LTBiY3JUbHhlRlZBQlYzbE5ISWMzTWZ5NHZ2QlhLRmJjR1JWQWpPTHczZ0ZsRmVoVWFBeE5oTVdCYnQ1RFpGRWF0dmNhY3M4VUhWUQ?oc=5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46117.45972222222</v>
+        <v>46118.41657407407</v>
       </c>
     </row>
     <row r="43">
@@ -2745,22 +2745,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boekenjacht op Paasmaandag: bib Brecht verkoopt afgevoerde materialen uit tijdens Pasenmarkt - Nieuwsblad</t>
+          <t>Controle verdachte bromfietser leidt tot cocaïnelab in appartement - Nieuwsblad</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Book hunt on Easter Monday: Brecht library sells removed materials during the Easter market - Nieuwsblad</t>
+          <t>Check on suspected moped rider leads to cocaine lab in apartment - Nieuwsblad</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 12:00:00 GMT</t>
+          <t>Sun, 05 Apr 2026 17:16:00 GMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxPRVBjSFAxLXVFNTViVENHOTBwUVRERFJTeGxJVVpqTF9NbmN2TElaYnJGVi1qZ2t4WE5aVENHM0RQNE55OFRyUHNzT1JpMmRUcVpXeEZwUEJqNFZJdndIZEZ1RkJUTzBoTWhaR3gxdWxLTXNxdk52dkwxQ0d1TWtvSXR6SnN1c18xUXFHQl9hbmJMdkFFcTRLYnh6RlFoYkc2MHlwT0Y1ODVHcDByeTJ1RU9Ja0tKU2JxRzlGc2RUVEp3emZvemhFS2UtT1hlM3hIOFhKT1ZRbU5rb1dYS2IxeXUzN1JleXgwNUhuMzlSbUtNRTVwZTJRU3hVaVpaR3k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNZFBXMWlDY0pwMmNndlNTOWdSeU5Dbi1LeEtUUlNtVFE2dWI0bDZrcEtZTTJreXVvRHZ2eWkwWmZCMHNBQkZDNUg3Y3E5MGtrMUVsZzFCaWF2TGFOSkJ3MkhGRzl1bjcyVWhySXE5eWQ1LS11VXZwS1ZFdThNNmd4Uy1ORzJFRUFLNGd0LUFGdll2ajVUTXJmUkY5OWZJQWI2cW5uQkRsOVRvZm43RTRKMlVuV2x3c0dJYlVwT1hBc3N1U2lXXzZBSVNtWXdLemZuZHNrM2RqSDYtaks3Q2lqQmNoa3p6N1pEUjlPQVRZSkJfalU?oc=5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46118.5</v>
+        <v>46117.71944444445</v>
       </c>
     </row>
     <row r="44">
@@ -2800,22 +2800,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>“Dit nauwe en voor velen onooglijke gangetje in Antwerpen is er al sinds 1427” - Nieuwsblad</t>
+          <t>Auto blokkeert verkeer voor trouwstoet in Borgerhout: bestuurder test positief op drugs - Nieuwsblad</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>“This narrow and, for many, unsightly corridor in Antwerp has been there since 1427” - Nieuwsblad</t>
+          <t>Car blocks traffic for wedding procession in Borgerhout: driver tests positive for drugs - Nieuwsblad</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 16:00:00 GMT</t>
+          <t>Sun, 05 Apr 2026 22:16:55 GMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQOHBVYVJjN0N3ZmxTTWlwbkZQR1E2SXBZaUkxeDFhMGRvYUNSR2g4U0J1NWlub2NrbXlRbGN1RkxRZUFfX0hZMmJiQ1VzcWw4bkgxM19HY044RVEzdmNaRG5IaXFPM3Q2X1U1d1NXNTZNZVFSdGpLRFBxTm1ROWpxUmR2NmNxMHY2cjZURjJtMHJtWlRudXFKcnA5M2h5YnNCUHhWODRCNy1GOG1XRXFvcjJfNVhxbXpUZTcwdkNEamJBbFg0ZTRuNGxVZlJnc3RJYWJWQUN1cXFZZUU2Y1h2WEp0enV5d1hUZ1NrYUtEMXU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQdXd4dmZoQnhoTzZQb195U05HbkFSbVBiOEtwbkpQZGttN20xQjNwaTNoUTdjYmFVaDBKdmtLRG5RNDVNUGw5dTZwNXc3WTlHTjFORzJDV0YwX1RCWlR1Z0xfMl9sZkRiQjFZaGtQajZoTjdZc2NiWlg2QUdTQTlONVpTR2t3cFdwVTVLVUw2eVZnM1ZxR0U3MldjRDdsQVNETThlS0lEbC1IOFgtWVNidjMtNDZHbTlVckZhVngya3pRMzRJSjJOUHNIRmJqSEtPQlVKbVZDQXRhR1d6YjBKd3k2dUtSZDZ6V2Q4dmV1bTl5bW9pTF9WcGFiWi1tdw?oc=5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46117.66666666666</v>
+        <v>46117.92841435185</v>
       </c>
     </row>
     <row r="45">
@@ -2855,22 +2855,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eindelijk startdatum voor langverwachte heraanleg Ropstraat - Nieuwsblad</t>
+          <t>Boekenjacht op Paasmaandag: bib Brecht verkoopt afgevoerde materialen uit tijdens Pasenmarkt - Nieuwsblad</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Finally start date for long-awaited reconstruction of Ropstraat - Nieuwsblad</t>
+          <t>Book hunt on Easter Monday: Brecht library sells removed materials during the Easter market - Nieuwsblad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 22:00:00 GMT</t>
+          <t>Mon, 06 Apr 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQTGVrR1RsNU9jYWxYYmYwVVRMSWtuMTBhN0dPLXRlZGRGMDlwaUc2VkFFUHNQYXR3OS1sTG1hYUJZaXFZaWx5WWlZSmJybl9MRWxOU3AtcTdSckNfa19pM3NtS2VpaV9xNktSMkM1S3VZWnBCREpDRVdQZHdEX0JJc2stYzdSTFE1UC1mZFlEbEJRVW1TOXFFWlhCTEk5QkM4MHlFZ3FDTnVYanlETTlHS201NFpiS2J6LXFydFFCeUZRdFVvbkY2UEZBX1BadnM1Z1lqZkdKWk9aQU03ZkhqaEVqT01MX3g4NlJfZ1RVNVdHUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxPRVBjSFAxLXVFNTViVENHOTBwUVRERFJTeGxJVVpqTF9NbmN2TElaYnJGVi1qZ2t4WE5aVENHM0RQNE55OFRyUHNzT1JpMmRUcVpXeEZwUEJqNFZJdndIZEZ1RkJUTzBoTWhaR3gxdWxLTXNxdk52dkwxQ0d1TWtvSXR6SnN1c18xUXFHQl9hbmJMdkFFcTRLYnh6RlFoYkc2MHlwT0Y1ODVHcDByeTJ1RU9Ja0tKU2JxRzlGc2RUVEp3emZvemhFS2UtT1hlM3hIOFhKT1ZRbU5rb1dYS2IxeXUzN1JleXgwNUhuMzlSbUtNRTVwZTJRU3hVaVpaR3k0?oc=5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46117.91666666666</v>
+        <v>46118.5</v>
       </c>
     </row>
     <row r="46">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Politieactie op Battelsesteenweg in Mechelen na schietincident: “Man aangetroffen met schotwonde” - Nieuwsblad</t>
+          <t>Vierde verdachte opgepakt in Londense rechtbank in onderzoek naar brandstichting bij Joodse ambulances - Nieuwsblad</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Police action on Battelsesteenweg in Mechelen after shooting incident: “Man found with gunshot wound” - Nieuwsblad</t>
+          <t>Fourth suspect arrested in London court in investigation into arson of Jewish ambulances - Nieuwsblad</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 16:19:46 GMT</t>
+          <t>Sun, 05 Apr 2026 11:02:00 GMT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQenFDcGs2Q0U5ZUp2VDJudmNvVjZNV19iTGdfWjI4bmtGSjdXaGU4QTdobm1MQzNHU2Y4ak5vSEFRcjctVVY1YTlMQ3Q2bk8tMGpOZ3psTUVZNGZ3VTRMVGVza1FwT2NxaUhuVlFlS01YMlMzZmtOS2VxaV9SSEFSTVRjLWlEdWw0cmZkSk55U3RieF9rZnlpSS1pSk5xNlY4WjZuSmdYdWg2QXAyd1ljS1NaYUFwMTMxcVMyOVh2VWo0OXdQZGlITk1xRUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQYzRGcWl2a2h4YWFQMGR2X3lBQ21MNkNfbzJBd0c0ZkZhRzVkWHd2MTRucldRNS1mMEd6LVN4eXJBeEotYjFIVHJUdDJnYmxybjNHc1hlN2ZfVUZlMW5MeVE0MC11b1ZYemhUSkstNDJNUGl2LWR4aHM3ckp0UC1fSkY2ank4T1BpMnd4VXNud1VNTi1oMG9MYkpKZnI0TUZJTzBSRldxcWFPNm5hWm40OGNleG5OM2pObmthVGVFTTVDdUNocmlWZWZNZlJEbFZ3cEFrS0hqRS05d1ZaWjdvVDNGN2Q1dU90QVE?oc=5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2949,38 +2949,38 @@
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46117.68039351852</v>
+        <v>46117.45972222222</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EU warns Trump against ‘illegal’ bombing of Iran’s power stations - politico.eu</t>
+          <t>“Dit nauwe en voor velen onooglijke gangetje in Antwerpen is er al sinds 1427” - Nieuwsblad</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EU warns Trump against ‘illegal’ bombing of Iran’s power stations - politico.eu</t>
+          <t>“This narrow and, for many, unsightly corridor in Antwerp has been there since 1427” - Nieuwsblad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 13:14:00 GMT</t>
+          <t>Sun, 05 Apr 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOSFpzR2dkRklrU183Ukp1clhFVWI1Qml3UENtd2RydGw3RmdqQkx2OGhkRTZrNml4bVQ3U1IwVUZvMWdiQ3FDbktpeWZBeVVjX2dWVGhxMU1nLW5XWW9fNFp1d3RKNjlpbjFZSVJEVU1KRkpXX0c4QjZma3BKeC1XNlRDb3R4ekZXVE1YYkFHazNaNEdWR0F2N0lwUFJNRTJXWE5yQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQOHBVYVJjN0N3ZmxTTWlwbkZQR1E2SXBZaUkxeDFhMGRvYUNSR2g4U0J1NWlub2NrbXlRbGN1RkxRZUFfX0hZMmJiQ1VzcWw4bkgxM19HY044RVEzdmNaRG5IaXFPM3Q2X1U1d1NXNTZNZVFSdGpLRFBxTm1ROWpxUmR2NmNxMHY2cjZURjJtMHJtWlRudXFKcnA5M2h5YnNCUHhWODRCNy1GOG1XRXFvcjJfNVhxbXpUZTcwdkNEamJBbFg0ZTRuNGxVZlJnc3RJYWJWQUN1cXFZZUU2Y1h2WEp0enV5d1hUZ1NrYUtEMXU?oc=5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3000,42 +3000,42 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46118.55138888889</v>
+        <v>46117.66666666666</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Athletics: Diamond League to cut meetings, disciplines by 2020 - AOL.com</t>
+          <t>Eindelijk startdatum voor langverwachte heraanleg Ropstraat - Nieuwsblad</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Athletics: Diamond League to cut meetings, disciplines by 2020 - AOL.com</t>
+          <t>Finally start date for long-awaited reconstruction of Ropstraat - Nieuwsblad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 22:11:26 GMT</t>
+          <t>Sun, 05 Apr 2026 22:00:00 GMT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOVTFyREpOZzFZeFdsSFdKakxjb296SVJLT2FvMU9jd01NMGV2VXF0ZFhYQ2FFTjB4NFZpWGk5VWxxeTdkenJ2bGUyOFlyQ3VjNHFHZWhVMzU0UUFEUmtsTVlKVzBuYS1wSHdXQURSazBoNUxJcUpwblRBSk9vZWs3YmVNa1NLcTQ2ZDV3b09ucVdBZmg5ajBlYURn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQTGVrR1RsNU9jYWxYYmYwVVRMSWtuMTBhN0dPLXRlZGRGMDlwaUc2VkFFUHNQYXR3OS1sTG1hYUJZaXFZaWx5WWlZSmJybl9MRWxOU3AtcTdSckNfa19pM3NtS2VpaV9xNktSMkM1S3VZWnBCREpDRVdQZHdEX0JJc2stYzdSTFE1UC1mZFlEbEJRVW1TOXFFWlhCTEk5QkM4MHlFZ3FDTnVYanlETTlHS201NFpiS2J6LXFydFFCeUZRdFVvbkY2UEZBX1BadnM1Z1lqZkdKWk9aQU03ZkhqaEVqT01MX3g4NlJfZ1RVNVdHUQ?oc=5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3055,42 +3055,42 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46118.92460648148</v>
+        <v>46117.91666666666</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Travel demand holds as Middle East war reshapes holiday choices - Travel Tomorrow</t>
+          <t>Politieactie op Battelsesteenweg in Mechelen na schietincident: “Man aangetroffen met schotwonde” - Nieuwsblad</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Travel demand holds as Middle East war reshapes holiday choices - Travel Tomorrow</t>
+          <t>Police action on Battelsesteenweg in Mechelen after shooting incident: “Man found with gunshot wound” - Nieuwsblad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 14:45:36 GMT</t>
+          <t>Sun, 05 Apr 2026 16:19:46 GMT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPTExyVXJZNHdtWEdBeHNMUHpLc0VuOUpRSFhOdmYxVzUtbV9OOW1vU2NOU196bmppMXF0X2RLU3hIaW8ySEdyd1RJY2pNbnp3SE5Cdk9HdG93Z05idHA0WnQtUDVvZmd3Y2I1NzFsd05BRko1UU11SXFVempOWXhuWTJpcWdjU2V0Yy1SWWpwRXNEOUNsbWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQenFDcGs2Q0U5ZUp2VDJudmNvVjZNV19iTGdfWjI4bmtGSjdXaGU4QTdobm1MQzNHU2Y4ak5vSEFRcjctVVY1YTlMQ3Q2bk8tMGpOZ3psTUVZNGZ3VTRMVGVza1FwT2NxaUhuVlFlS01YMlMzZmtOS2VxaV9SSEFSTVRjLWlEdWw0cmZkSk55U3RieF9rZnlpSS1pSk5xNlY4WjZuSmdYdWg2QXAyd1ljS1NaYUFwMTMxcVMyOVh2VWo0OXdQZGlITk1xRUU?oc=5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3110,42 +3110,42 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46118.615</v>
+        <v>46117.68039351852</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - The 'Sunburnt Car' made of synthetic 'human skin' - 9Now</t>
+          <t>Liveblog: FC Emmen ontvangt MVV Maastricht - StadIndex</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - The 'Sunburnt Car' made of synthetic 'human skin' - 9Now</t>
+          <t>Live blog: FC Emmen receives MVV Maastricht - StadIndex</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 04:15:23 GMT</t>
+          <t>Mon, 06 Apr 2026 14:42:19 GMT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQU3pCWDd5SFpVTGJyQkM1SUJYclRFQnhpVFhfZlpRamxGcDZlcUlrckFhNzNYRzF4eU04SWFLVUg1SVFNbTJfbHNZVEZZWjIwci14Q0FsejAxcXRIeUxMME0yMEItNklmZzlONmlvc1FmYjFxODZZX3FaQ3VQY0hPWXRJanhfanloVnhiUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPaEdzc3FTUFBKNnZmbkxwbEJBcUZ5QVp4c0FneFU4Y05zbG5XTmVhTXduNmprUkplYTFjZl8ya0VOd2xhOVNFSVJGWHVYS05TY1dfVGNjTF9DamFlaTFEbld1Z2FpMlA0ZzhlbVRFeGIxZU5vdnBjRnRRc1lOZGV6cm1ITnJFZDRES0tjVkZ0ZmNxYmZjYUpxSWNvbHE3LXlCZmJwVFdpRnlPNlBZQ256M3c1d19WTzJSRFpiWkp1LW1tUQ?oc=5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3165,11 +3165,11 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46119.17734953704</v>
+        <v>46118.61271990741</v>
       </c>
     </row>
     <row r="51">
@@ -3185,22 +3185,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia cautions citizens over travel risks linked to US sanctions - Travel Tomorrow</t>
+          <t>EU warns Trump against ‘illegal’ bombing of Iran’s power stations - politico.eu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Russia cautions citizens over travel risks linked to US sanctions - Travel Tomorrow</t>
+          <t>EU warns Trump against ‘illegal’ bombing of Iran’s power stations - politico.eu</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 15:28:18 GMT</t>
+          <t>Mon, 06 Apr 2026 13:14:00 GMT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPQTBLSThUSC1OUDcybDhJRzRUNHdVVzh5ZW1hbkRTQjNvVW1Qbl9qem8yVGtsbC1LTFR5UGxnZzlRcWhmMjBvSmlja0hIa0h4QUhiaFRTQm0yY0EyOFI0UzBVRlZkZThXNDR3Y1k2TmR3Qk5qVl9FUmZRaWlmajBhb19sX3BFUm1LTnhBSjE0ckRxa0JSTlhtXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOSFpzR2dkRklrU183Ukp1clhFVWI1Qml3UENtd2RydGw3RmdqQkx2OGhkRTZrNml4bVQ3U1IwVUZvMWdiQ3FDbktpeWZBeVVjX2dWVGhxMU1nLW5XWW9fNFp1d3RKNjlpbjFZSVJEVU1KRkpXX0c4QjZma3BKeC1XNlRDb3R4ekZXVE1YYkFHazNaNEdWR0F2N0lwUFJNRTJXWE5yQw?oc=5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46118.64465277778</v>
+        <v>46118.55138888889</v>
       </c>
     </row>
     <row r="52">
@@ -3240,22 +3240,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Meta and Google found guilty of building addictive platforms - 9Now</t>
+          <t>Athletics: Diamond League to cut meetings, disciplines by 2020 - AOL.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Meta and Google found guilty of building addictive platforms - 9Now</t>
+          <t>Athletics: Diamond League to cut meetings, disciplines by 2020 - AOL.com</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 02:10:26 GMT</t>
+          <t>Mon, 06 Apr 2026 22:11:26 GMT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPT2Rzc3VMZEh3WTNVZUhPMllSRFpnREtPMDhmNDNaeWtQQXVPSzdlWGJkSTlsRDlEblgzZVFSUFJYWTdURG4xMWVBZ2U2ZUNCcXhtdFYxWk9ZWV9EM0w5RFAzakp3Rk9jRnEtbnNVXzFVTTNLU0l5MUJmTXBkOGZYRG8tVzVrUjZjVUJDeQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOVTFyREpOZzFZeFdsSFdKakxjb296SVJLT2FvMU9jd01NMGV2VXF0ZFhYQ2FFTjB4NFZpWGk5VWxxeTdkenJ2bGUyOFlyQ3VjNHFHZWhVMzU0UUFEUmtsTVlKVzBuYS1wSHdXQURSazBoNUxJcUpwblRBSk9vZWs3YmVNa1NLcTQ2ZDV3b09ucVdBZmg5ajBlYURn?oc=5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46119.0905787037</v>
+        <v>46118.92460648148</v>
       </c>
     </row>
     <row r="53">
@@ -3295,22 +3295,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fuel limits hit Italian airports as Middle East conflict strains supply - Travel Tomorrow</t>
+          <t>Travel demand holds as Middle East war reshapes holiday choices - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fuel limits hit Italian airports as Middle East conflict strains supply - Travel Tomorrow</t>
+          <t>Travel demand holds as Middle East war reshapes holiday choices - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 12:27:37 GMT</t>
+          <t>Mon, 06 Apr 2026 14:45:36 GMT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPcHFsRDdieTFISDJ1Z0dxbWEwUjAtXzVHelVZb09xNmY3M1pXcW1LOGpIU3NRZGlkVFZCVE1KekFoRENpN3RsX0g1SXFXWk4wM2lKN1kzVHRCblJNUUNweWJzSWRTbnJxVTNscHBncUlWTG9RQXRvdXZBVjBMdDZJazY2dFZ4MWZGNWtqdHU3VEM3Z1dHdk80T0hLdzNkTXBw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPTExyVXJZNHdtWEdBeHNMUHpLc0VuOUpRSFhOdmYxVzUtbV9OOW1vU2NOU196bmppMXF0X2RLU3hIaW8ySEdyd1RJY2pNbnp3SE5Cdk9HdG93Z05idHA0WnQtUDVvZmd3Y2I1NzFsd05BRko1UU11SXFVempOWXhuWTJpcWdjU2V0Yy1SWWpwRXNEOUNsbWc?oc=5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46118.51917824074</v>
+        <v>46118.615</v>
       </c>
     </row>
     <row r="54">
@@ -3350,22 +3350,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Everest fraud scandal exposes fake rescues and broken oversight - Travel Tomorrow</t>
+          <t>Watch 9News Latest Stories - Season 2026 - The 'Sunburnt Car' made of synthetic 'human skin' - 9Now</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Everest fraud scandal exposes fake rescues and broken oversight - Travel Tomorrow</t>
+          <t>Watch 9News Latest Stories - Season 2026 - The 'Sunburnt Car' made of synthetic 'human skin' - 9Now</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 11:33:41 GMT</t>
+          <t>Tue, 07 Apr 2026 04:15:23 GMT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPa0hPd1NpQ0daWDZoWVVKX0xJVXBpQml6cHpnalFHSmJEYVFXTk5uUDlaZ3c5MjlBb1NVN1AwSnFvLVI3ZkxQTWRteS1mQ2dnd2xlalA1Y0d2cV90SF9jLTZsRzhwT2ZtcjFEcmtQUmdTMkJHTHhyb2o0aFJrcVlPb00wT2NHemxlajFYV0Z2LWMzdjdOYnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQU3pCWDd5SFpVTGJyQkM1SUJYclRFQnhpVFhfZlpRamxGcDZlcUlrckFhNzNYRzF4eU04SWFLVUg1SVFNbTJfbHNZVEZZWjIwci14Q0FsejAxcXRIeUxMME0yMEItNklmZzlONmlvc1FmYjFxODZZX3FaQ3VQY0hPWXRJanhfanloVnhiUw?oc=5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46118.48172453704</v>
+        <v>46119.17734953704</v>
       </c>
     </row>
     <row r="55">
@@ -3405,22 +3405,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Orbán Suggests Ukrainians Responsible for Attempted Pipeline Terror Attack Days Ahead of Election - breitbart.com</t>
+          <t>Russia cautions citizens over travel risks linked to US sanctions - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Orbán Suggests Ukrainians Responsible for Attempted Pipeline Terror Attack Days Ahead of Election - breitbart.com</t>
+          <t>Russia cautions citizens over travel risks linked to US sanctions - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 09:18:37 GMT</t>
+          <t>Mon, 06 Apr 2026 15:28:18 GMT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOVTBjalV3TnZ4azVSb0JUNG9BbV9oQUdjWS1nMlRZaG1Ga2dpa0ZmQVdxOExBb1RSTEJDYXBUVDd3eDdSdF9ZYXR1ZXVia0I3aXF5MjRid2ZPb1FpV0JfdE5mOGVBaHJMdnJiNEFtZ1hzeDRqMEZyMlZvVGZDQWR5OHZTNHkya2pIc00tTjRBQktERk4yYjI4UDF6ZzI3bnZEeFBsTjNOTUNRTi1oam5YRVlteWJwZjFaaW5iZXc2X2dIYUpnVnFpcHhzampKeUlvMDVxbkJNaUxHcTRDTkZn0gHfAUFVX3lxTE5VMGNqVXdOdnhrNVJvQlQ0b0FtX2hBR2NZLWcyVFlobUZrZ2lrRmZBV3E4TEFvVFJMQkNhcFRUN3d4N1J0X1lhdHVldWJrQjdpcXkyNGJ3Zk9vUWlXQl90TmY4ZUFockx2cmI0QW1nWHN4NGowRnIyVm9UZkNBZHk4dlM0eTJrakhzTS1ONEFCS0RGTjJiMjhQMXpnMjdudkR4UGxOM05NQ1FOLWhqblhFWW15YnBmMVppbmJldzZfZ0hhSmdWcWlweHNqakp5SW8wNXFuQk1pTEdxNENORmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPQTBLSThUSC1OUDcybDhJRzRUNHdVVzh5ZW1hbkRTQjNvVW1Qbl9qem8yVGtsbC1LTFR5UGxnZzlRcWhmMjBvSmlja0hIa0h4QUhiaFRTQm0yY0EyOFI0UzBVRlZkZThXNDR3Y1k2TmR3Qk5qVl9FUmZRaWlmajBhb19sX3BFUm1LTnhBSjE0ckRxa0JSTlhtXw?oc=5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3444,38 +3444,38 @@
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46118.38792824074</v>
+        <v>46118.64465277778</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Un adolescent de 14 ans poignardé lors d’une soirée étudiante, un suspect recherché - BruxellesToday</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Meta and Google found guilty of building addictive platforms - 9Now</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A 14-year-old teenager stabbed during a student party, a suspect sought - BruxellesToday</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Meta and Google found guilty of building addictive platforms - 9Now</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 14:01:00 GMT</t>
+          <t>Tue, 07 Apr 2026 02:10:26 GMT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMWRYQVU2Tk1GZExGLVBkYjB0MTNqZzRTeW5pcGcwa0h3TW9ha2hVYnBQZ0lTOXROSnlndXZkekNSZndYTGRaa1k2aVJPUlA5eC1ucWs1MzF3dExBT0pGVzZuXzE3Qmdrakc5d1R0Sk1zdi1RUl9CeWhsV3B2R3N3WW94N09oaHh0LWM3Y0xmN0pGa3hyUEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPT2Rzc3VMZEh3WTNVZUhPMllSRFpnREtPMDhmNDNaeWtQQXVPSzdlWGJkSTlsRDlEblgzZVFSUFJYWTdURG4xMWVBZ2U2ZUNCcXhtdFYxWk9ZWV9EM0w5RFAzakp3Rk9jRnEtbnNVXzFVTTNLU0l5MUJmTXBkOGZYRG8tVzVrUjZjVUJDeQ?oc=5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3495,42 +3495,42 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46117.58402777778</v>
+        <v>46119.0905787037</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Un homme de 35 ans blessé par balle à la jambe, une enquête ouverte - BruxellesToday</t>
+          <t>Fuel limits hit Italian airports as Middle East conflict strains supply - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A 35-year-old man shot in the leg, an investigation opened - BruxellesToday</t>
+          <t>Fuel limits hit Italian airports as Middle East conflict strains supply - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 08:41:00 GMT</t>
+          <t>Mon, 06 Apr 2026 12:27:37 GMT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPOFZXazRPOEVlOHFHdDJyS2VRYmJ5UzlVakVWUDhUU2ltd3d4Mm10NktCNUJjbVpRT1FkUnNmUk85SGhHYWVPU2V6NGpOWTRQQ2UwOHI2RDhkZThodDJPSndFWTQxcHRYR1hWMjNZSjkwX2x1blR2MV9ZWkFmdUJ6ZEFDbzcyM0pDcUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPcHFsRDdieTFISDJ1Z0dxbWEwUjAtXzVHelVZb09xNmY3M1pXcW1LOGpIU3NRZGlkVFZCVE1KekFoRENpN3RsX0g1SXFXWk4wM2lKN1kzVHRCblJNUUNweWJzSWRTbnJxVTNscHBncUlWTG9RQXRvdXZBVjBMdDZJazY2dFZ4MWZGNWtqdHU3VEM3Z1dHdk80T0hLdzNkTXBw?oc=5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3550,42 +3550,42 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46117.36180555556</v>
+        <v>46118.51917824074</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Assises à Anvers - Said Cherkaoui condamné à la prison à perpétuité pour l'assassinat de Davy Veraghtert - msn.com</t>
+          <t>Everest fraud scandal exposes fake rescues and broken oversight - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Assizes in Antwerp - Said Cherkaoui sentenced to life imprisonment for the assassination of Davy Veraghtert - msn.com</t>
+          <t>Everest fraud scandal exposes fake rescues and broken oversight - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 01:30:05 GMT</t>
+          <t>Mon, 06 Apr 2026 11:33:41 GMT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNalRwbEdHandrVGRmbG85aTNPa2lnMUN5dWo2WC1pMDBhTlkwLWRUR1o2Z0JSOFZXVHM3cWRkWEZVOU94OUtQNEhEX092S040bF9ueGcxUV9rZVF5R2dncVF5Q0lxaFFlOUUwYS0tbV9ZbnVHUVFWY0RZZmRTTS1EWWtCT1pBaE1NbHB1YlhSb3NENWZuZ01zMk9SeUQyNGVDcjFfU2tZOHBLU3BBSHdtckpkX1FIQmRFU2hBVVhaNllhU1JxQm9GM1Exb3FETjRPSWM3YmxFYXdFWnhscTJZMnBuNXBTT2FMaERvYUdXYzhZQTFsZUU4MzB1X2JORmJaYlNfdUVyR0lydElNSjR2NnZzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPa0hPd1NpQ0daWDZoWVVKX0xJVXBpQml6cHpnalFHSmJEYVFXTk5uUDlaZ3c5MjlBb1NVN1AwSnFvLVI3ZkxQTWRteS1mQ2dnd2xlalA1Y0d2cV90SF9jLTZsRzhwT2ZtcjFEcmtQUmdTMkJHTHhyb2o0aFJrcVlPb00wT2NHemxlajFYV0Z2LWMzdjdOYnc?oc=5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3605,42 +3605,42 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46119.06255787037</v>
+        <v>46118.48172453704</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Une femme dans le coma après des violences, son compagnon arrêté - BruxellesToday</t>
+          <t>Orbán Suggests Ukrainians Responsible for Attempted Pipeline Terror Attack Days Ahead of Election - breitbart.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>A woman in a coma after violence, her partner arrested - BruxellesToday</t>
+          <t>Orbán Suggests Ukrainians Responsible for Attempted Pipeline Terror Attack Days Ahead of Election - breitbart.com</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 14:31:00 GMT</t>
+          <t>Mon, 06 Apr 2026 09:18:37 GMT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1V5TzF6UHBmOFd4VUZwSnpOeXR3THZJV1hCSFhaRDRhSGNWdjZ6TkZFS3JRZ0JZWkNud2pBOVhBQmpSQkNUM3M5Ylc2NHdfRDh6QnFVZjRKWEItdzNqLU5sOFFYamJ1bmlla3pSMTdIVnFoZ00yT2d5R2FiUjVIdHF1Q0tCUTFveEdKcFpjYVp1aWpsNzZwNTlneEYzUzdhbUktdDd4UG1KeXRDblVnVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOVTBjalV3TnZ4azVSb0JUNG9BbV9oQUdjWS1nMlRZaG1Ga2dpa0ZmQVdxOExBb1RSTEJDYXBUVDd3eDdSdF9ZYXR1ZXVia0I3aXF5MjRid2ZPb1FpV0JfdE5mOGVBaHJMdnJiNEFtZ1hzeDRqMEZyMlZvVGZDQWR5OHZTNHkya2pIc00tTjRBQktERk4yYjI4UDF6ZzI3bnZEeFBsTjNOTUNRTi1oam5YRVlteWJwZjFaaW5iZXc2X2dIYUpnVnFpcHhzampKeUlvMDVxbkJNaUxHcTRDTkZn0gHfAUFVX3lxTE5VMGNqVXdOdnhrNVJvQlQ0b0FtX2hBR2NZLWcyVFlobUZrZ2lrRmZBV3E4TEFvVFJMQkNhcFRUN3d4N1J0X1lhdHVldWJrQjdpcXkyNGJ3Zk9vUWlXQl90TmY4ZUFockx2cmI0QW1nWHN4NGowRnIyVm9UZkNBZHk4dlM0eTJrakhzTS1ONEFCS0RGTjJiMjhQMXpnMjdudkR4UGxOM05NQ1FOLWhqblhFWW15YnBmMVppbmJldzZfZ0hhSmdWcWlweHNqakp5SW8wNXFuQk1pTEdxNENORmc?oc=5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3660,42 +3660,42 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46117.60486111111</v>
+        <v>46118.38792824074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen Dutch</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Man (34) slaat stiefvader (58) met hamer op hoofd in Lanaken en verwondt moeder, slachtoffers uit ziekenhuis - VRT</t>
+          <t>Un adolescent de 14 ans poignardé lors d’une soirée étudiante, un suspect recherché - BruxellesToday</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Man (34) hits stepfather (58) on the head with a hammer in Lanaken and injures mother, victims from hospital - VRT</t>
+          <t>A 14-year-old teenager stabbed during a student party, a suspect sought - BruxellesToday</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 09:27:51 GMT</t>
+          <t>Sun, 05 Apr 2026 14:01:00 GMT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPMkpIV29SOU5HQXhnREx4VGptSlJXa1NRMkowMjU3M20xRGdSTVllcm9zWmJ3YXJmaEFBc1pRY3ozUnhaaXN2em1BYXA4REJaNzVMVUk5amliWUFzMEdCUlVfang3SExIYnNNOFNpaWRpSWEyM083ZHZvWDI1eDFnQXNFWjl2OGMyTXhEV2NRNmZlSmRE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOMWRYQVU2Tk1GZExGLVBkYjB0MTNqZzRTeW5pcGcwa0h3TW9ha2hVYnBQZ0lTOXROSnlndXZkekNSZndYTGRaa1k2aVJPUlA5eC1ucWs1MzF3dExBT0pGVzZuXzE3Qmdrakc5d1R0Sk1zdi1RUl9CeWhsV3B2R3N3WW94N09oaHh0LWM3Y0xmN0pGa3hyUEE?oc=5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3715,42 +3715,42 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46118.39434027778</v>
+        <v>46117.58402777778</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen Dutch</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>16-jarige uit Genk lichtgewond bij kop-staartaanrijding op Kempische Steenweg in Hasselt | Foto - HLN</t>
+          <t>Un homme de 35 ans blessé par balle à la jambe, une enquête ouverte - BruxellesToday</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>16-year-old from Genk slightly injured in rear-end collision on Kempische Steenweg in Hasselt | Photo - HLN</t>
+          <t>A 35-year-old man shot in the leg, an investigation opened - BruxellesToday</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 13:13:33 GMT</t>
+          <t>Sun, 05 Apr 2026 08:41:00 GMT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNNW9MT3JtSFJlVWp4QlFBUXlrVXlMdDByN1V1LWpSUmVUM3UxTUdJbmNNREVFcFc5TkRaZWhmUF8yRzBrNm4tMWtGMFQxWkVNU2dpN0tqVVg2REhLMXpJN2pFUDJCQVJ6cmR4ckdMc1NkWGllRlR6QzNCR1dmYmJ1ZHFXZHdwRmhQZ19zekU5T2lZNFU0NjJHQldYeXdSMkxFbFRMaFFITVgzaklQVXBFXzBkS2FMQmV3WXRvU1p6aGlDdW9fdmRLaUw3bGlPYk5P?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPOFZXazRPOEVlOHFHdDJyS2VRYmJ5UzlVakVWUDhUU2ltd3d4Mm10NktCNUJjbVpRT1FkUnNmUk85SGhHYWVPU2V6NGpOWTRQQ2UwOHI2RDhkZThodDJPSndFWTQxcHRYR1hWMjNZSjkwX2x1blR2MV9ZWkFmdUJ6ZEFDbzcyM0pDcUE?oc=5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3770,42 +3770,42 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46118.55107638889</v>
+        <v>46117.36180555556</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen Dutch</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vader en dochter raken ernstig gewond bij ongeval in Hasselt: Luikersteenweg afgesloten - VRT</t>
+          <t>Assises à Anvers - Said Cherkaoui condamné à la prison à perpétuité pour l'assassinat de Davy Veraghtert - MSN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Father and daughter seriously injured in accident in Hasselt: Luikersteenweg closed - VRT</t>
+          <t>Assizes in Antwerp - Said Cherkaoui sentenced to life imprisonment for the assassination of Davy Veraghtert - MSN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 17:13:20 GMT</t>
+          <t>Tue, 07 Apr 2026 01:30:05 GMT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcWZGTmNiZkN1Snd6RU5wSnVRMEp0M3V2RldxV1pIUzRoTVhLRnMxaERLcFF1YXAyekZzSzg1LURhV1lyeWhwblAzcXQtUzZFWjFkVWdQajhxSUlWZC1YSWc1UVZMbDdzV19lNGVWQVB6eFA2bnRLcmYyU0gta0RBdlZoZTAxNmxIQVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNalRwbEdHandrVGRmbG85aTNPa2lnMUN5dWo2WC1pMDBhTlkwLWRUR1o2Z0JSOFZXVHM3cWRkWEZVOU94OUtQNEhEX092S040bF9ueGcxUV9rZVF5R2dncVF5Q0lxaFFlOUUwYS0tbV9ZbnVHUVFWY0RZZmRTTS1EWWtCT1pBaE1NbHB1YlhSb3NENWZuZ01zMk9SeUQyNGVDcjFfU2tZOHBLU3BBSHdtckpkX1FIQmRFU2hBVVhaNllhU1JxQm9GM1Exb3FETjRPSWM3YmxFYXdFWnhscTJZMnBuNXBTT2FMaERvYUdXYzhZQTFsZUU4MzB1X2JORmJaYlNfdUVyR0lydElNSjR2NnZzQQ?oc=5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3825,42 +3825,42 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46117.71759259259</v>
+        <v>46119.06255787037</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>La fête de Pâques en famille a dégénéré à Lanaken : le beau-père s’est pris un coup de marteau dans le crâne - Sudinfo</t>
+          <t>Une femme dans le coma après des violences, son compagnon arrêté - BruxellesToday</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>The family Easter celebration degenerated in Lanaken: the father-in-law was hit in the head with a hammer - Sudinfo</t>
+          <t>A woman in a coma after violence, her partner arrested - BruxellesToday</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 09:33:09 GMT</t>
+          <t>Sun, 05 Apr 2026 14:31:00 GMT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPQ2p2eHh1YWNvRFhSZjlHeVNFMlV0YXZuQkNaYlIwSEtXcTFjWVRDSU5lTjI4UFg3d1kxTlBrVVU5QTlqYkRJelpkYk53Ykg3RjVYRnpDdWg4OEYxUnpJZFI4RUo4SS1tY1FudDhLRGUzMGhtcmZ6d3dYM3dRamFPRWlZRXNHRHVsaExCUFZESWpVY09UMDYySVlPcUpvWmpZZ3I1YkVvejZyZFhHTGJrcEtra2ZvWkpxSjVVLUZMS0xRdXB1RklxWERMVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1V5TzF6UHBmOFd4VUZwSnpOeXR3THZJV1hCSFhaRDRhSGNWdjZ6TkZFS3JRZ0JZWkNud2pBOVhBQmpSQkNUM3M5Ylc2NHdfRDh6QnFVZjRKWEItdzNqLU5sOFFYamJ1bmlla3pSMTdIVnFoZ00yT2d5R2FiUjVIdHF1Q0tCUTFveEdKcFpjYVp1aWpsNzZwNTlneEYzUzdhbUktdDd4UG1KeXRDblVnVw?oc=5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3884,38 +3884,38 @@
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46118.39802083333</v>
+        <v>46117.60486111111</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prix des carburants: Binet (CGT) demande un "prix maximum à la pompe de 1,70 euro" - France 24</t>
+          <t>Man (34) slaat stiefvader (58) met hamer op hoofd in Lanaken en verwondt moeder, slachtoffers uit ziekenhuis - VRT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fuel prices: Binet (CGT) calls for a “maximum pump price of 1.70 euros” - France 24</t>
+          <t>Man (34) hits stepfather (58) on the head with a hammer in Lanaken and injures mother, victims from hospital - VRT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:33:11 GMT</t>
+          <t>Mon, 06 Apr 2026 09:27:51 GMT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdk85MC0zOHJlU0U4WEJfU3M2Tm91a3RicDkzNDVGWnhPNHdRY3gteE00Vkl2MFNCRldyN3ctMGxwSzFrellKVXhuSi14UEw1aVJTWnVkeXBxdzNLMXNrYVJaY2IxWGdkakhhRFBxaWVGcXNTUnpvcHZZTFpVRmNEZDhtR1RWZDV5TDNKcmpmM1RBcTZXZWFESWFVU0pJX2k4T2xSWU4wZ3FjNnR1ZlZrekJGMG1qUkhIdFVteWZJZDY2NkNfbGZnNWpOZmZiN213?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPMkpIV29SOU5HQXhnREx4VGptSlJXa1NRMkowMjU3M20xRGdSTVllcm9zWmJ3YXJmaEFBc1pRY3ozUnhaaXN2em1BYXA4REJaNzVMVUk5amliWUFzMEdCUlVfang3SExIYnNNOFNpaWRpSWEyM083ZHZvWDI1eDFnQXNFWjl2OGMyTXhEV2NRNmZlSmRE?oc=5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3935,42 +3935,42 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46118.68971064815</v>
+        <v>46118.39434027778</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bomb OR explosion OR shooting OR stabbing OR evacuation OR police OR arrest OR threat) AND -sport AND -football</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ASTRID Delegation Visits Hasselt's CIC Limburg, Showcasing Multidisciplinary Emergency Dispatching - The Critical Communications Review</t>
+          <t>16-jarige uit Genk lichtgewond bij kop-staartaanrijding op Kempische Steenweg in Hasselt | Foto - HLN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ASTRID Delegation Visits Hasselt's CIC Limburg, Showcasing Multidisciplinary Emergency Dispatching - The Critical Communications Review</t>
+          <t>16-year-old from Genk slightly injured in rear-end collision on Kempische Steenweg in Hasselt | Photo - HLN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 09:50:23 GMT</t>
+          <t>Mon, 06 Apr 2026 13:13:33 GMT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxObXdSaUgyQ3lLRFpJSXRJTHpaVGJEeHZYQVMtVWRoWmdjNWZFa1VFZkFCaGp6OW1mZER2bTJIY2RaenJtVHlKeUItamFqNzhLZFNwRzNCYkZ0ZEUyYWZ0aXBKR3FqRUs5ZVRIaGVIaUpFMXFtdm5ubm9DbFg0TWd0WG0wQzZ2cENjdXNDSmw3VV9jM0g1WkZKNDNtTTVQS01PNjVDSTRiZXR5aHdRcHJWUFBMWnNJUFFlMXY0R0RzeEZ0Nkp1QXlmRjR5Q1JsRnlJT29IcTc1dVpVd3BnVmxYMjFhWUYtVEJPZEdQNTliaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNNW9MT3JtSFJlVWp4QlFBUXlrVXlMdDByN1V1LWpSUmVUM3UxTUdJbmNNREVFcFc5TkRaZWhmUF8yRzBrNm4tMWtGMFQxWkVNU2dpN0tqVVg2REhLMXpJN2pFUDJCQVJ6cmR4ckdMc1NkWGllRlR6QzNCR1dmYmJ1ZHFXZHdwRmhQZ19zekU5T2lZNFU0NjJHQldYeXdSMkxFbFRMaFFITVgzaklQVXBFXzBkS2FMQmV3WXRvU1p6aGlDdW9fdmRLaUw3bGlPYk5P?oc=5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3980,52 +3980,52 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46118.40998842593</v>
+        <v>46118.55107638889</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bomb OR explosion OR shooting OR stabbing OR evacuation OR police OR arrest OR threat) AND -sport AND -football</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Young man hits stepfather on head with hammer in Flanders - The Brussels Times</t>
+          <t>Vader en dochter zwaargewond na botsing met auto tegen boom in Hasselt - msn.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Young man hits stepfather on head with hammer in Flanders - The Brussels Times</t>
+          <t>Father and daughter seriously injured after car crashes into tree in Hasselt - msn.com</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:00:00 GMT</t>
+          <t>Mon, 06 Apr 2026 15:53:07 GMT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPYmk5WURvSWRnZUZtV3gtQUNWRU5jdktQM0JVaEVvQ2lSbnc0cm1MSGFNN3BmaW9TQnQ2ZnV1S1JUdDEzRllQWUdyMVhsdjJZLTI5bmZtaVBfell3X1RJWHo2ZEJ0V2hKSEM1SXJmSlRGODZlZE9FbE5oVW43ZUZZRnk2YnA1UnF6RFcwRmRqNUQ5LWk1UURkdV92OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gJBVV95cUxNcmdKNGtyZGMxNTQxX2tPVXJacXpMWlJvcHgzbGN2dGhpTi0yb0d2VFhEcU1TcDNVSEx0Rkt4eU5JY1A1OEdPcjBBbkd2enRZdW5SenhESnFjQlprdE5MVjhjRTh6d0k1Sk1zUHh4NEIxRGR3QjdUVHJUNU1QWnhzX3lQRlplRkdlZUhwZlpmYmluMzBrdE9YcG5SemVTdU01X25ROGJwcDNtRVhrTGtMSGFFeFNXeG14Zm9lT2cwMHJNbzVId1drckFMYWhGR3BXZ3ltejh4aVZrS3ZFemJfNUV6VHMzdzBSak1ET1ZudEdXeGNvR24wZk0yOE5BcGZwMUdRaFZoWkdIQ2QzV0FPOE9Ualg3NXRBbzItVDVkV0REeUhBajY4UlhMakNyMW15Vkl6bkRaUHNoVUNQNndlU3BGd1hhM3NqOU44WnM0bUpDdnJ0cVFuTTNn?oc=5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4035,52 +4035,52 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46118.75</v>
+        <v>46118.66188657407</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FSU Herbert Wertheim College of Business honors faculty and staff, adds two to its Faculty Hall of Fame - Florida State University News</t>
+          <t>Vader en dochter raken ernstig gewond bij ongeval in Hasselt: Luikersteenweg afgesloten - VRT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FSU Herbert Wertheim College of Business honors faculty and staff, adds two to its Faculty Hall of Fame - Florida State University News</t>
+          <t>Father and daughter seriously injured in accident in Hasselt: Luikersteenweg closed - VRT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 17:00:35 GMT</t>
+          <t>Sun, 05 Apr 2026 17:13:20 GMT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPQV9RZHNIOVRKMGUzenUzd1dCOUY4MFVVd1ZfY1k5NEJIRExCYnVQNVF4M29JT0lkdmFkMkw1WVZLWEF3blBhNGxraXY1cGVYcjFPTFpqWFBsNktfaWowbmxEcWdKamQ5cFpZNzlWVFVUN01rQXpYajU0UzlIRDZ1bVNXMlZxZ1ZraU1aeGJfUjlfY0ZsNzNwVTJsR01tZUN6RW52TVhuLWpZMUg3QmdEdTA1b054VTZRVWZzQVUyd3pKUXBnMWNRU3Q0cUFvNnNhT1dndjZxUlBDd1YwUGd0S0RTRm5OVXprMzRLaTduLVpVUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcWZGTmNiZkN1Snd6RU5wSnVRMEp0M3V2RldxV1pIUzRoTVhLRnMxaERLcFF1YXAyekZzSzg1LURhV1lyeWhwblAzcXQtUzZFWjFkVWdQajhxSUlWZC1YSWc1UVZMbDdzV19lNGVWQVB6eFA2bnRLcmYyU0gta0RBdlZoZTAxNmxIQVE?oc=5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4090,52 +4090,52 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46118.70873842593</v>
+        <v>46117.71759259259</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Herbie Wertheim throws his red hat into congressional race - Stet News</t>
+          <t>Parket Limburg onderzoekt home-invasion in Hamont-Achel - msn.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Herbie Wertheim throws his red hat into congressional race - Stet News</t>
+          <t>Limburg Public Prosecutor's Office investigates home invasion in Hamont-Achel - msn.com</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 14:33:51 GMT</t>
+          <t>Sun, 05 Apr 2026 14:35:14 GMT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQWENFQ09yRGowSG9rMEpwdzBpcjQ2Y3M0NmM0RV9zbmhYRnhkcW05VXo5Y0VmeGFxdS0teGtLNGFzRXJlWUdjZVl6ZEwzampENHlja0hRRFpLUE5mTHZYeEs3cXNFbi1aRVNZU19FMkc2OGtIQ0NVeFlCWEUzSTZfR0JjcmxCcHdSdmhUMTlEUUY3Q01UbWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgJBVV95cUxQajAzZFM5QU0zTVRVaEMxN2ZiMGdoWGI0VGYxbFFwUUR5bVlrajhXOWttcG15elh1R3BmcEMtWTZ0Y0tqcC1UdjVQMUZheElMOWFYMHJYejJUOWE4WUhpdzM4UldfWXFKUldRWklSWTVCYUJnT3B5dERlSE9fZGdDZlR5cHVZVE91cWRuY1NEVllWbVY3dllHcjM0eDV0dTJRU3Ytclg2XzRoSGZOaF9lVUdyZ1J4bTdjVFh0WWtuVGkwS3dqZjh5clR1ZVZYRXBIbmFTekNNX0kzZ1Z2Z1h4N0N0Z2Z1Y2pLVkZoQnNtRWg2NDdnUFVQZ01acTV4X0E0eDdGV3libVJ1T0xvTk1SX2tGd3Q2ZXE4X2VzNm5meldaMGszdTNpYWVrQW10T2dJM2xwZ1lSTHdDdG1KNmlyZEJJTUlHQQ?oc=5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4145,52 +4145,52 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46118.60684027777</v>
+        <v>46117.60780092593</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Suffolk County police rescue teen stuck in mud at Wertheim National Wildlife Refuge - Yahoo</t>
+          <t>La fête de Pâques en famille a dégénéré à Lanaken : le beau-père s’est pris un coup de marteau dans le crâne - Sudinfo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Suffolk County police rescue teen stuck in mud at Wertheim National Wildlife Refuge - Yahoo</t>
+          <t>The family Easter celebration degenerated in Lanaken: the father-in-law was hit in the head with a hammer - Sudinfo</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 23:24:58 GMT</t>
+          <t>Mon, 06 Apr 2026 09:33:09 GMT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQLTRHcHRXZGJzQ2UtWkNuQmFXX1FGODMwR0FXUzZVa19BQThPTmtSYnBCdHhkemswb1I4RGkzS21qYUdJWHhfbTRscVlUOTZIRVEzYW9JVkRETE5xdTRnM3pWZGE1dHozOVlvRk1NRGNtdHBhamRXOG9UbGlkSXJtXzlfSEEwQXNicElYaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPQ2p2eHh1YWNvRFhSZjlHeVNFMlV0YXZuQkNaYlIwSEtXcTFjWVRDSU5lTjI4UFg3d1kxTlBrVVU5QTlqYkRJelpkYk53Ykg3RjVYRnpDdWg4OEYxUnpJZFI4RUo4SS1tY1FudDhLRGUzMGhtcmZ6d3dYM3dRamFPRWlZRXNHRHVsaExCUFZESWpVY09UMDYySVlPcUpvWmpZZ3I1YkVvejZyZFhHTGJrcEtra2ZvWkpxSjVVLUZMS0xRdXB1RklxWERMVQ?oc=5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4200,52 +4200,52 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46118.9756712963</v>
+        <v>46118.39802083333</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Stony Brook Medicine Leadership Advances Federal Priorities in Washington Meetings with New York Delegation - Stony Brook Medicine</t>
+          <t>Prix des carburants: Binet (CGT) demande un "prix maximum à la pompe de 1,70 euro" - France 24</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Stony Brook Medicine Leadership Advances Federal Priorities in Washington Meetings with New York Delegation - Stony Brook Medicine</t>
+          <t>Fuel prices: Binet (CGT) calls for a “maximum pump price of 1.70 euros” - France 24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:01:12 GMT</t>
+          <t>Mon, 06 Apr 2026 16:33:11 GMT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPZWkxcE84MzVrZFRXZFUydnBwTkN4VWNhcTR5bEpkQThuNmFiWHEtTWxwMkNHcnF5TEtNX3J3Y19VaURfanlpQ1k5Vnhscy0tR2ZwU0Y4RXp6ZEJVREFFNlNCU0ZrV3VqRkl2TzZma09hZ214Z0JfV1NIWjhpVnZqd3RYSjhhcm1VTjVJMFhSZ1JFX0NIcDhxTE1tVjQ3SlBWTWRiMjVtLVdBbFRXdDdHajhqQlhSZ0dEemktOG1NYXhBS1I2TmpHalpWb0RZb2Nkam5yRm4tVUJ1VV9jS0ZWVHNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQdk85MC0zOHJlU0U4WEJfU3M2Tm91a3RicDkzNDVGWnhPNHdRY3gteE00Vkl2MFNCRldyN3ctMGxwSzFrellKVXhuSi14UEw1aVJTWnVkeXBxdzNLMXNrYVJaY2IxWGdkakhhRFBxaWVGcXNTUnpvcHZZTFpVRmNEZDhtR1RWZDV5TDNKcmpmM1RBcTZXZWFESWFVU0pJX2k4T2xSWU4wZ3FjNnR1ZlZrekJGMG1qUkhIdFVteWZJZDY2NkNfbGZnNWpOZmZiN213?oc=5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4255,52 +4255,52 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46118.75083333333</v>
+        <v>46118.68971064815</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Maasmechelen English</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bomb OR explosion OR shooting OR stabbing OR evacuation OR police OR arrest OR threat) AND -sport AND -football</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UF earns top marks in latest U.S. News graduate program rankings - Gainesville Sun</t>
+          <t>ASTRID Delegation Visits Hasselt's CIC Limburg, Showcasing Multidisciplinary Emergency Dispatching - The Critical Communications Review</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UF earns top marks in latest U.S. News graduate program rankings - Gainesville Sun</t>
+          <t>ASTRID Delegation Visits Hasselt's CIC Limburg, Showcasing Multidisciplinary Emergency Dispatching - The Critical Communications Review</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 04:01:00 GMT</t>
+          <t>Mon, 06 Apr 2026 09:50:23 GMT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQZFk1UWUzbnZPUk5wYmlCbThwNlR5WGprSDU1Vi1sa05vdUVyWk5XWGM3eVRVYS1JRmJraTE2aHU5cnB4bUJzN01hTEpRMDZrT2tJQkplVk0xWXVQOERySF9XUFZ2eVFPbmJSOWFKVDZjX2lscnZoQzU1TDV1eDJKYXFQdFBBRF9IZkdxRndYeHNGTC1uUXhiTTM3emJUNWpMVEkxQ1pDRng2T205WWwtdXR3UW9TZmtUdjBVQ2hTVFljMXp2OUFjVGd6NmswX3EtZzhHMjNtZnNVQW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxObXdSaUgyQ3lLRFpJSXRJTHpaVGJEeHZYQVMtVWRoWmdjNWZFa1VFZkFCaGp6OW1mZER2bTJIY2RaenJtVHlKeUItamFqNzhLZFNwRzNCYkZ0ZEUyYWZ0aXBKR3FqRUs5ZVRIaGVIaUpFMXFtdm5ubm9DbFg0TWd0WG0wQzZ2cENjdXNDSmw3VV9jM0g1WkZKNDNtTTVQS01PNjVDSTRiZXR5aHdRcHJWUFBMWnNJUFFlMXY0R0RzeEZ0Nkp1QXlmRjR5Q1JsRnlJT29IcTc1dVpVd3BnVmxYMjFhWUYtVEJPZEdQNTliaw?oc=5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4324,38 +4324,38 @@
         </is>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46119.16736111111</v>
+        <v>46118.40998842593</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Maasmechelen English</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bomb OR explosion OR shooting OR stabbing OR evacuation OR police OR arrest OR threat) AND -sport AND -football</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>The Herald-Mail Media Events - Water Marbling with Acrylics on Hanging Glass Baubles (AM) with Peggy Wertheim - The Herald-Mail</t>
+          <t>Young man hits stepfather on head with hammer in Flanders - The Brussels Times</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>The Herald-Mail Media Events - Water Marbling with Acrylics on Hanging Glass Baubles (AM) with Peggy Wertheim - The Herald-Mail</t>
+          <t>Young man hits stepfather on head with hammer in Flanders - The Brussels Times</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 09:00:15 GMT</t>
+          <t>Mon, 06 Apr 2026 18:00:00 GMT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNTWVLTE9uelVHUGZ0Qlg2eDR0eGxqdkoyaVZib3drN3BpS3EzZ2VicXVHTVFJdGMyVHdONzlsSVNFWUt1M2VjQ0xuSFZoZTRvOFdrenVrQjRnZnM1ZmZyYkZpbGN3bEtLc3lpTnpDZ1daRUdYeXRRLXkwbkN1d0p3a05lTzkyMUwwZTJzVGhCMFhUYTg4cDd2eF9Ib2VHTTB6eVp1aGZOVlJGdDA5VElmWTc0cExwTm5uTGlQeWV1RzIyam5iX1ltSk54SnZ2UkJZM0t5T1BRVFFwMXJ4TDZKZkdVSVVmclI4MDhuYWdOZ0dQOVk3ZUQ3aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPYmk5WURvSWRnZUZtV3gtQUNWRU5jdktQM0JVaEVvQ2lSbnc0cm1MSGFNN3BmaW9TQnQ2ZnV1S1JUdDEzRllQWUdyMVhsdjJZLTI5bmZtaVBfell3X1RJWHo2ZEJ0V2hKSEM1SXJmSlRGODZlZE9FbE5oVW43ZUZZRnk2YnA1UnF6RFcwRmRqNUQ5LWk1UURkdV92OA?oc=5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46118.37517361111</v>
+        <v>46118.75</v>
       </c>
     </row>
     <row r="73">
@@ -4395,22 +4395,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>86-Year-Old Billionaire Launches Congressional Campaign With His Own $2.5 Million Donation - Yahoo</t>
+          <t>FSU Herbert Wertheim College of Business honors faculty and staff, adds two to its Faculty Hall of Fame - Florida State University News</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>86-Year-Old Billionaire Launches Congressional Campaign With His Own $2.5 Million Donation - Yahoo</t>
+          <t>FSU Herbert Wertheim College of Business honors faculty and staff, adds two to its Faculty Hall of Fame - Florida State University News</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 19:20:11 GMT</t>
+          <t>Mon, 06 Apr 2026 17:00:35 GMT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQRVlCSGQ2cnd1U0JSb2N0VWNwVTZXUWtoXzNYYzdLRl9fc2k1dkxqbXdXYmFRUUVRMkRJVTc2TzBoYTctTXdZUHI2cmFZdEp4MDNFT3hGT2JLU1hVYllieDgzQkItTkdESWxvTGt1VldsY1AzajFaSzJfVGppYzRNb2FGMUNOYUZqaFJ4MHFnYWNodU5vZlJr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPQV9RZHNIOVRKMGUzenUzd1dCOUY4MFVVd1ZfY1k5NEJIRExCYnVQNVF4M29JT0lkdmFkMkw1WVZLWEF3blBhNGxraXY1cGVYcjFPTFpqWFBsNktfaWowbmxEcWdKamQ5cFpZNzlWVFVUN01rQXpYajU0UzlIRDZ1bVNXMlZxZ1ZraU1aeGJfUjlfY0ZsNzNwVTJsR01tZUN6RW52TVhuLWpZMUg3QmdEdTA1b054VTZRVWZzQVUyd3pKUXBnMWNRU3Q0cUFvNnNhT1dndjZxUlBDd1YwUGd0S0RTRm5OVXprMzRLaTduLVpVUQ?oc=5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46118.80568287037</v>
+        <v>46118.70873842593</v>
       </c>
     </row>
     <row r="74">
@@ -4450,22 +4450,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Other countries have 200 mph passenger trains. Why has high-speed rail not tracked here? - CBS News</t>
+          <t>Herbie Wertheim throws his red hat into congressional race - Stet News</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Other countries have 200 mph passenger trains. Why has high-speed rail not tracked here? - CBS News</t>
+          <t>Herbie Wertheim throws his red hat into congressional race - Stet News</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 23:00:17 GMT</t>
+          <t>Mon, 06 Apr 2026 14:33:51 GMT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPT3NJOVphM2pvY3lrWVBWQTh6alpYXzJXaUJnQ0I4WGVBbzJfbUQxQjVnVDFlRHJPSWpNZFhXS3hBcG5uQVdLSWFGR095TVBycXFjTzJhclU2MDNPeU4talAyVWFjNVZJbTMxaDU4Y3NSRGNWekd3dG9BTENTNVpHdFBxeVhURFJRQThWNHZjZ2RuZEnSAZgBQVVfeXFMUDd1VDdKOU5FMlFTa0hvd1VYVWJ2VGNOS05UVWRlU09ndmFJRm5VS1hLZHJUS0d5WkllOUFvek5EY0F2bm1lb21makFXN0J3MTQxZDZ3VW5jWXA1NmVmUnVCOV9LNUxnRE83d2dCUHVUMWdibjZ2V0VsWVJ6QkV4MTIwYTFjQkdwck9BMlc3UWJtODlFWmp4S18?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQWENFQ09yRGowSG9rMEpwdzBpcjQ2Y3M0NmM0RV9zbmhYRnhkcW05VXo5Y0VmeGFxdS0teGtLNGFzRXJlWUdjZVl6ZEwzampENHlja0hRRFpLUE5mTHZYeEs3cXNFbi1aRVNZU19FMkc2OGtIQ0NVeFlCWEUzSTZfR0JjcmxCcHdSdmhUMTlEUUY3Q01UbWc?oc=5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46117.95853009259</v>
+        <v>46118.60684027777</v>
       </c>
     </row>
     <row r="75">
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York teen trapped in sinking mud uses flashlight to signal for help - MSN</t>
+          <t>Suffolk County police rescue teen stuck in mud at Wertheim National Wildlife Refuge - Yahoo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>New York teen trapped in sinking mud uses flashlight to signal for help - MSN</t>
+          <t>Suffolk County police rescue teen stuck in mud at Wertheim National Wildlife Refuge - Yahoo</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 14:53:14 GMT</t>
+          <t>Mon, 06 Apr 2026 23:24:58 GMT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxQZjhVbW9yZ3BjZU1ITVNTZDZRQW9adkNaeDBGZ2szNWtMQTFSM0FzSTJ6MGljN0R4aFRiWFFISi1teEg1M3o2aFk3UTdzZWZuODZXLS1EeTVqNDY3cVhJbHNOc2VGVXc2ZzRMcHpfZXc1ZXFocHF0WlVhbHpkTkczdmN2YVNHMS1LQVBDTFBzcnhEOE1KaWN3ejkxSlRUOW5OX2thNmxuTkZaU2JBRWlpalNYRzFzejdSZUxPTXRhekUybmN2clhHMGJrYV82V3F0TF85NGlXYnc2NnBJbTV1WWNCRFNpWWN1MFpzaWZCenNWYmVETnpBMG0zMGhWMFVvNDNXbVdxQmJrcHF4eDBqQm5DRk1xa3ByQ3FGUmdVazdkQTk4amdSMU5pU2hJLWVpTE8tSXpPSEhZWG5taUhmWTZVSXNVZ3p4cHQxZGJ0TzEydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQLTRHcHRXZGJzQ2UtWkNuQmFXX1FGODMwR0FXUzZVa19BQThPTmtSYnBCdHhkemswb1I4RGkzS21qYUdJWHhfbTRscVlUOTZIRVEzYW9JVkRETE5xdTRnM3pWZGE1dHozOVlvRk1NRGNtdHBhamRXOG9UbGlkSXJtXzlfSEEwQXNicElYaw?oc=5</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46118.62030092593</v>
+        <v>46118.9756712963</v>
       </c>
     </row>
     <row r="76">
@@ -4560,22 +4560,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>60 Minutes CBS “Return to Ram, Ghost Train, The Mardi Gras Indians” April 5 2026 - IMDb</t>
+          <t>Stony Brook Medicine Leadership Advances Federal Priorities in Washington Meetings with New York Delegation - Stony Brook Medicine</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>60 Minutes CBS “Return to Ram, Ghost Train, The Mardi Gras Indians” April 5 2026 - IMDb</t>
+          <t>Stony Brook Medicine Leadership Advances Federal Priorities in Washington Meetings with New York Delegation - Stony Brook Medicine</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 04:08:44 GMT</t>
+          <t>Mon, 06 Apr 2026 18:01:12 GMT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE11ZE05T3JkLUFjY1d5YklaT3RnTUltSnFlQVVzSzY3TjBhMEJRWHpQQ0NEaTNaOTdtaUdlOUVXNm5xZGhXR0ZsbW8wVVZIVnFCMGM3UnZJb19tZ3ExcUszbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPZWkxcE84MzVrZFRXZFUydnBwTkN4VWNhcTR5bEpkQThuNmFiWHEtTWxwMkNHcnF5TEtNX3J3Y19VaURfanlpQ1k5Vnhscy0tR2ZwU0Y4RXp6ZEJVREFFNlNCU0ZrV3VqRkl2TzZma09hZ214Z0JfV1NIWjhpVnZqd3RYSjhhcm1VTjVJMFhSZ1JFX0NIcDhxTE1tVjQ3SlBWTWRiMjVtLVdBbFRXdDdHajhqQlhSZ0dEemktOG1NYXhBS1I2TmpHalpWb0RZb2Nkam5yRm4tVUJ1VV9jS0ZWVHNR?oc=5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46118.17273148148</v>
+        <v>46118.75083333333</v>
       </c>
     </row>
     <row r="77">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Transportation Secretary Sean Duffy's statement for 60 Minutes' "Ghost Train" report - CBS News</t>
+          <t>UF earns top marks in latest U.S. News graduate program rankings - Gainesville Sun</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Transportation Secretary Sean Duffy's statement for 60 Minutes' "Ghost Train" report - CBS News</t>
+          <t>UF earns top marks in latest U.S. News graduate program rankings - Gainesville Sun</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 23:00:21 GMT</t>
+          <t>Tue, 07 Apr 2026 04:01:00 GMT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPN0pEMEl3Z3l1TTdsTEJ6Q0R3ajdrVW5scFJLYUVLTnlvMzlHSXlWbldyUzhRSFJ3VjFxSGRmZ0Jvd1lmWElqem5pbFlyamFPZEt3clQtS1E2U2Y0ZlFVd2J5Q2Fvcm9wRnE1NnJCSU11MmpqZnNWeTBUbGNEUTNDdU9MbzExTTBm0gGIAUFVX3lxTE83SkQwSXdneXVNN2xMQnpDRHdqN2tVbmxwUkthRUtOeW8zOUdJeVZuV3JTOFFIUndWMXFIZGZnQm93WWZYSWp6bmlsWXJqYU9kS3dyVC1LUTZTZjRmUVV3YnlDYW9yb3BGcTU2ckJJTXUyampmc1Z5MFRsY0RRM0N1T0xvMTFNMGY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQZFk1UWUzbnZPUk5wYmlCbThwNlR5WGprSDU1Vi1sa05vdUVyWk5XWGM3eVRVYS1JRmJraTE2aHU5cnB4bUJzN01hTEpRMDZrT2tJQkplVk0xWXVQOERySF9XUFZ2eVFPbmJSOWFKVDZjX2lscnZoQzU1TDV1eDJKYXFQdFBBRF9IZkdxRndYeHNGTC1uUXhiTTM3emJUNWpMVEkxQ1pDRng2T205WWwtdXR3UW9TZmtUdjBVQ2hTVFljMXp2OUFjVGd6NmswX3EtZzhHMjNtZnNVQW8?oc=5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4654,38 +4654,38 @@
         </is>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46117.95857638889</v>
+        <v>46119.16736111111</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irre Verfolgungsjagd in Ingolstadt - HITRADIO RT1</t>
+          <t>86-Year-Old Billionaire Launches Congressional Campaign With His Own $2.5 Million Donation - Yahoo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Crazy chase in Ingolstadt - HITRADIO RT1</t>
+          <t>86-Year-Old Billionaire Launches Congressional Campaign With His Own $2.5 Million Donation - Yahoo</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 04:15:00 GMT</t>
+          <t>Mon, 06 Apr 2026 19:20:11 GMT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBqWmR5NERtOTlvSnRtYlJUdXc4T1NWN0sxQzVVYVVBSnV5SE8xWDA2V2t0WnZkckJ1Und2TnVlODY0YVd3ZWJmQy1iVEd6MXJIR01UYWhyVWh3N3EyV19ZYS1JS3NHMnY5dXlaWnNHTVNKUko5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQRVlCSGQ2cnd1U0JSb2N0VWNwVTZXUWtoXzNYYzdLRl9fc2k1dkxqbXdXYmFRUUVRMkRJVTc2TzBoYTctTXdZUHI2cmFZdEp4MDNFT3hGT2JLU1hVYllieDgzQkItTkdESWxvTGt1VldsY1AzajFaSzJfVGppYzRNb2FGMUNOYUZqaFJ4MHFnYWNodU5vZlJr?oc=5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4695,52 +4695,52 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K78" s="1" t="n">
-        <v>46119.17708333334</v>
+        <v>46118.80568287037</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Notarzteinsatz am Bahnhof Allersberg – Strecke ab Nürnberg war in der Nacht gesperrt - NN.de</t>
+          <t>Other countries have 200 mph passenger trains. Why has high-speed rail not tracked here? - CBS News</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Emergency medical intervention at Allersberg train station – route from Nuremberg was closed at night - NN.de</t>
+          <t>Other countries have 200 mph passenger trains. Why has high-speed rail not tracked here? - CBS News</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 09:06:15 GMT</t>
+          <t>Sun, 05 Apr 2026 23:00:17 GMT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQTWREOW5GNzRuSmhnREtRM3BNZXN3ckswLW1heGxFNkRCak5nbEwtQnhPNE9NbnFiVVo2Z09vbVE5clBPUWRJa0VWWmRLRVE0bTRBRkdVWjZNd2pNTGZWOEJLVlMzRnFGS2R4S0JZTHgxVnZ3Q1AzSHRYOGVoRl9FclVVemxnME5XNF9RTlh1RUFlSC1IaUhjc3V0TFlCNF9FYXZxVXlOcHVoVGRYMk90TE1lYWZDbExoQUZSQlVwTFpBYWFkX1Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPT3NJOVphM2pvY3lrWVBWQTh6alpYXzJXaUJnQ0I4WGVBbzJfbUQxQjVnVDFlRHJPSWpNZFhXS3hBcG5uQVdLSWFGR095TVBycXFjTzJhclU2MDNPeU4talAyVWFjNVZJbTMxaDU4Y3NSRGNWekd3dG9BTENTNVpHdFBxeVhURFJRQThWNHZjZ2RuZEnSAZgBQVVfeXFMUDd1VDdKOU5FMlFTa0hvd1VYVWJ2VGNOS05UVWRlU09ndmFJRm5VS1hLZHJUS0d5WkllOUFvek5EY0F2bm1lb21makFXN0J3MTQxZDZ3VW5jWXA1NmVmUnVCOV9LNUxnRE83d2dCUHVUMWdibjZ2V0VsWVJ6QkV4MTIwYTFjQkdwck9BMlc3UWJtODlFWmp4S18?oc=5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4750,52 +4750,52 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K79" s="1" t="n">
-        <v>46117.37934027778</v>
+        <v>46117.95853009259</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Holders versus record winners: Bayern vs. Wolfsburg in cup final - FC Bayern Munich</t>
+          <t>The Herald-Mail Media Events - Water Marbling with Acrylics on Hanging Glass Baubles (AM) with Peggy Wertheim - The Herald-Mail</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Holders versus record winners: Bayern vs. Wolfsburg in cup final - FC Bayern Munich</t>
+          <t>The Herald-Mail Media Events - Water Marbling with Acrylics on Hanging Glass Baubles (AM) with Peggy Wertheim - The Herald-Mail</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 17:23:00 GMT</t>
+          <t>Mon, 06 Apr 2026 09:00:15 GMT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOQzZSdDJYRjh6c1Q4S3NQTWJKdGZPYlZEcjB5c3hjLUlPMldEYlhDZnY5akROdzJIX040SDZpUUQtekJVcTZ0YmZSWEQwaEVNbEdHczRCX3Q0YVNuc1hHT01VZTRoQnJxR0hXZWNBclhMQXpLdUFJYWd3dnM3b2VadlNXaERIc0VuNFl5c25CR09uTWhaRVptbnN5SWF4dm14NDJVamJxd0Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNTWVLTE9uelVHUGZ0Qlg2eDR0eGxqdkoyaVZib3drN3BpS3EzZ2VicXVHTVFJdGMyVHdONzlsSVNFWUt1M2VjQ0xuSFZoZTRvOFdrenVrQjRnZnM1ZmZyYkZpbGN3bEtLc3lpTnpDZ1daRUdYeXRRLXkwbkN1d0p3a05lTzkyMUwwZTJzVGhCMFhUYTg4cDd2eF9Ib2VHTTB6eVp1aGZOVlJGdDA5VElmWTc0cExwTm5uTGlQeWV1RzIyam5iX1ltSk54SnZ2UkJZM0t5T1BRVFFwMXJ4TDZKZkdVSVVmclI4MDhuYWdOZ0dQOVk3ZUQ3aA?oc=5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4819,38 +4819,38 @@
         </is>
       </c>
       <c r="K80" s="1" t="n">
-        <v>46118.72430555556</v>
+        <v>46118.37517361111</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Audi CEO says diesel crisis not over and vows to stay on: report - AOL.com</t>
+          <t>Statement to 60 Minutes for "Ghost Train" - MSN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Audi CEO says diesel crisis not over and vows to stay on: report - AOL.com</t>
+          <t>Statement to 60 Minutes for "Ghost Train" - MSN</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 04:36:32 GMT</t>
+          <t>Mon, 06 Apr 2026 06:59:51 GMT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSWtjRGNLRks5MlRmM2JVc0hDLVZ0cVlKbUJUNWlaVm9WN29HMHl6bGlOblhEc1lsZ3lvWnhlb2RleGpXMTJRU2lwRVdIR0swQlR1c0lEbXR1cUtnYVVLU0N4bGJCVzRIcHA5dTBmQzhXZldia1l5M0FEZkIyWFJHMVlqVVk3a2Q5c3pkekR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNUnFrZUtaQU44YjdUeXBNRk9mRzBqYVdEZTU5cVd1aHBrNjBMdlkwWDBsdGFobm5Vak1xbEo5VEY2Ni1nbjRuWjA4SFpLUUV4YkFfWXpJNnhuTWxNNlJvR2U4NDZraTRUS1dDVlhFWXlXcmlUeUd4VkVVb1ZrWHJYTkNJeFh3bHZ6cXNmOVlhalpiS0tONjFsMzJEZmxNVEExVkpxanB0VlNybGw5blZOeFFfeHFEQVRoUWR0TVA1NTlnWHdYamNBVFVzZDhzbVE?oc=5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4874,38 +4874,38 @@
         </is>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46119.19203703704</v>
+        <v>46118.2915625</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Village Bicester Kildare</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LATEST: Green light for new homes over shop in this Kildare village - Leinster Leader</t>
+          <t>New York teen trapped in sinking mud uses flashlight to signal for help - MSN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LATEST: Green light for new homes over shop in this Kildare village - Leinster Leader</t>
+          <t>New York teen trapped in sinking mud uses flashlight to signal for help - MSN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 10:07:09 GMT</t>
+          <t>Mon, 06 Apr 2026 14:53:14 GMT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQUldaWGNpVVNqcGp4b2d2T3Jvd1lKcEs2WGVYcGpxOXZxdWdpcVFldEp2YmxZX0JOQ3JpTTRRVXVKNXplcjVoZlpKTGNGVDI0UGtaMHVHNFhjWnM1M2VkT1U0dEU1WDdlNjJ2RkJwY0trN0hWVnVTMUFfZFNxX3VmbnhGTUpMSEI0RHdWbG9vQVYyblpiM3JDdVZKNGd0VWJrd1ROd2IzTms0Q1FBcUNPdVZwakQ5ZnJDZjNaUmVPUTRVNW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxQZjhVbW9yZ3BjZU1ITVNTZDZRQW9adkNaeDBGZ2szNWtMQTFSM0FzSTJ6MGljN0R4aFRiWFFISi1teEg1M3o2aFk3UTdzZWZuODZXLS1EeTVqNDY3cVhJbHNOc2VGVXc2ZzRMcHpfZXc1ZXFocHF0WlVhbHpkTkczdmN2YVNHMS1LQVBDTFBzcnhEOE1KaWN3ejkxSlRUOW5OX2thNmxuTkZaU2JBRWlpalNYRzFzejdSZUxPTXRhekUybmN2clhHMGJrYV82V3F0TF85NGlXYnc2NnBJbTV1WWNCRFNpWWN1MFpzaWZCenNWYmVETnpBMG0zMGhWMFVvNDNXbVdxQmJrcHF4eDBqQm5DRk1xa3ByQ3FGUmdVazdkQTk4amdSMU5pU2hJLWVpTE8tSXpPSEhZWG5taUhmWTZVSXNVZ3p4cHQxZGJ0TzEydw?oc=5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4929,38 +4929,38 @@
         </is>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46118.42163194445</v>
+        <v>46118.62030092593</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Four men arrested on suspicion of murder after stabbing in south London - The Guardian</t>
+          <t>60 Minutes CBS “Return to Ram, Ghost Train, The Mardi Gras Indians” April 5 2026 - IMDb</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Four men arrested on suspicion of murder after stabbing in south London - The Guardian</t>
+          <t>60 Minutes CBS “Return to Ram, Ghost Train, The Mardi Gras Indians” April 5 2026 - IMDb</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:29:00 GMT</t>
+          <t>Mon, 06 Apr 2026 04:08:44 GMT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOMnRoN2Fnd0EyNTQtUnpnenVvLWEyUmlVR21HdVV0eU15VUlGRHFiNnBMUjhtSnl3ZTB3R3VEMElZamluQ3g0RDFEY0pKN2tOb1RUeGhIakh1VjhJSFFoVVVYYlVuYXdlNDktYzhLNXRJdXZfeXFxSmtiZ3BYelNVY19fajM1QWJYUWVoLUcxcjhmakt4SVFFYjdyMlc4Ym9WY1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE11ZE05T3JkLUFjY1d5YklaT3RnTUltSnFlQVVzSzY3TjBhMEJRWHpQQ0NEaTNaOTdtaUdlOUVXNm5xZGhXR0ZsbW8wVVZIVnFCMGM3UnZJb19tZ3ExcUszbg?oc=5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4984,38 +4984,38 @@
         </is>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46118.68680555555</v>
+        <v>46118.17273148148</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Two men fighting for their lives after triple stabbing in south east London - Yahoo News UK</t>
+          <t>Irre Verfolgungsjagd in Ingolstadt - HITRADIO RT1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Two men fighting for their lives after triple stabbing in south east London - Yahoo News UK</t>
+          <t>Crazy chase in Ingolstadt - HITRADIO RT1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 15:38:05 GMT</t>
+          <t>Tue, 07 Apr 2026 04:15:00 GMT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE82YWlYQk1mdi1MTkJVNFV6Wk1MVG9FVXh5amo4enAway1jaTNucUhxUXMyLVhuempFT0FHdFNLSWJMbmVyeXQ3cG1aNmVFU0tkRkszdTBzODE4LXFsQjJHbnJWWEFyRHAybURIcjBudUo4MEF1b0JJVkJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBqWmR5NERtOTlvSnRtYlJUdXc4T1NWN0sxQzVVYVVBSnV5SE8xWDA2V2t0WnZkckJ1Und2TnVlODY0YVd3ZWJmQy1iVEd6MXJIR01UYWhyVWh3N3EyV19ZYS1JS3NHMnY5dXlaWnNHTVNKUko5?oc=5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5025,52 +5025,52 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46118.65144675926</v>
+        <v>46119.17708333334</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Woolwich shooting: Further arrests after Eghosa Ogbebor shot dead - BBC</t>
+          <t>Notarzteinsatz am Bahnhof Allersberg – Strecke ab Nürnberg war in der Nacht gesperrt - NN.de</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Woolwich shooting: Further arrests after Eghosa Ogbebor shot dead - BBC</t>
+          <t>Emergency medical intervention at Allersberg train station – route from Nuremberg was closed at night - NN.de</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 11:36:50 GMT</t>
+          <t>Sun, 05 Apr 2026 09:06:15 GMT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5CZUhMRFBuNHJjb0VGSlZfV280UEd3N0hwRUROeVByTnhGSDM2N3k2bXVpOVp0Y0xNSDM2OFd3bDlmYXJCejF4X0ZMSDFoZXJncDJpYnRiSFhmZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQTWREOW5GNzRuSmhnREtRM3BNZXN3ckswLW1heGxFNkRCak5nbEwtQnhPNE9NbnFiVVo2Z09vbVE5clBPUWRJa0VWWmRLRVE0bTRBRkdVWjZNd2pNTGZWOEJLVlMzRnFGS2R4S0JZTHgxVnZ3Q1AzSHRYOGVoRl9FclVVemxnME5XNF9RTlh1RUFlSC1IaUhjc3V0TFlCNF9FYXZxVXlOcHVoVGRYMk90TE1lYWZDbExoQUZSQlVwTFpBYWFkX1Mw?oc=5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5080,52 +5080,52 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K85" s="1" t="n">
-        <v>46117.48391203704</v>
+        <v>46117.37934027778</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Man remanded in custody accused of stabbing twin teenage sisters and passerby in Dublin - The Irish Times</t>
+          <t>Holders versus record winners: Bayern vs. Wolfsburg in cup final - FC Bayern Munich</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Man remanded in custody accused of stabbing twin teenage sisters and passerby in Dublin - The Irish Times</t>
+          <t>Holders versus record winners: Bayern vs. Wolfsburg in cup final - FC Bayern Munich</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 15:27:58 GMT</t>
+          <t>Mon, 06 Apr 2026 17:23:00 GMT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOR3ltVEZSNzNtVUo0TmZLRTNZc2Q5bkdNZmNSQXRlOWxBZTQ5SW1OZlFFNU1ZMmxMTjRUdU5HQkQ2aHIyQlJRQk5jVThydXRkXzFkUmhFSUc0YnU1UFFUX25hZ1VFR1UzeHZiVkdXa0lkZmdGZDBDNHpFMzAwOHJRMGlocEFjU0xraDVRYXZDUWZxb2NlaUIxRzltaU5EMGp0QUJVN25UNXlqZlN1Q3llZ3UzeFpzTVYwTTRiaXNfODlmODYyWnFlT0Q1QkZQTm9qNWpFSlozM1BuZFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOQzZSdDJYRjh6c1Q4S3NQTWJKdGZPYlZEcjB5c3hjLUlPMldEYlhDZnY5akROdzJIX040SDZpUUQtekJVcTZ0YmZSWEQwaEVNbEdHczRCX3Q0YVNuc1hHT01VZTRoQnJxR0hXZWNBclhMQXpLdUFJYWd3dnM3b2VadlNXaERIc0VuNFl5c25CR09uTWhaRVptbnN5SWF4dm14NDJVamJxd0Y?oc=5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5149,38 +5149,38 @@
         </is>
       </c>
       <c r="K86" s="1" t="n">
-        <v>46118.6444212963</v>
+        <v>46118.72430555556</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Student detained after bomb threat note found at New London High School - WQAD</t>
+          <t>Audi CEO says diesel crisis not over and vows to stay on: report - AOL.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Student detained after bomb threat note found at New London High School - WQAD</t>
+          <t>Audi CEO says diesel crisis not over and vows to stay on: report - AOL.com</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:31:00 GMT</t>
+          <t>Tue, 07 Apr 2026 04:36:32 GMT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPbnVDajdYSC05S1ZtZDBkb29nOWFGajJhVDdrekZrc0d6MkU2X0tYVkQwdHAyR3FmcWY0OF9CZzd1YzY3NWdpLWFWd0J1M1RVSUJPLVZiN1Y3TWJ5WFE2VExaSm1DQjR2RnlpMllmRXAtZEZPZ1ZzZGVKbENNMXhZQTJNXzNOSGFaN0NpUkFyVk9mZjRrdFhWZzlmOVcwYzFJUUxRYkd2NkpHaUxZcklmRWFMeU5EYUVob1VjT2tmeEMwT3VYTmhOd2FFU3pTaFN0bk9VeXlvc19XMHRoWGZRYXF0MS0wZElJWmRxWlR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSWtjRGNLRks5MlRmM2JVc0hDLVZ0cVlKbUJUNWlaVm9WN29HMHl6bGlOblhEc1lsZ3lvWnhlb2RleGpXMTJRU2lwRVdIR0swQlR1c0lEbXR1cUtnYVVLU0N4bGJCVzRIcHA5dTBmQzhXZldia1l5M0FEZkIyWFJHMVlqVVk3a2Q5c3pkekR3?oc=5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5204,38 +5204,38 @@
         </is>
       </c>
       <c r="K87" s="1" t="n">
-        <v>46118.77152777778</v>
+        <v>46119.19203703704</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village Bicester Kildare</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Two more people arrested on suspicion of murder after 14-year-old boy shot dead in London - Sky News</t>
+          <t>LATEST: Green light for new homes over shop in this Kildare village - Leinster Leader</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Two more people arrested on suspicion of murder after 14-year-old boy shot dead in London - Sky News</t>
+          <t>LATEST: Green light for new homes over shop in this Kildare village - Leinster Leader</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 11:12:25 GMT</t>
+          <t>Mon, 06 Apr 2026 10:07:09 GMT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNWlYyM2p5RTk2T3dYOTdUaV84Zk5jQWQ2TzBRZUltUE03cVpwd2FKcG82UTFCX0xqMlFobmxUSkxMdEd5Q1piWFAxUzYxaXBMTTIxaGd1NG1FcUJQQ0JlV1Rnb1N6aG9iWXoxSWdaclMxeVVsYmNEZHFkbDJWREVYTjlnMUJNUGs5Y2szVWdQUmJzVWFEeUZLNndMTVNtSEtjdGpHQl8wd0d2eTVqQjk1dk1DaWdieFFaNFJrT3I3STF4dVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQUldaWGNpVVNqcGp4b2d2T3Jvd1lKcEs2WGVYcGpxOXZxdWdpcVFldEp2YmxZX0JOQ3JpTTRRVXVKNXplcjVoZlpKTGNGVDI0UGtaMHVHNFhjWnM1M2VkT1U0dEU1WDdlNjJ2RkJwY0trN0hWVnVTMUFfZFNxX3VmbnhGTUpMSEI0RHdWbG9vQVYyblpiM3JDdVZKNGd0VWJrd1ROd2IzTms0Q1FBcUNPdVZwakQ5ZnJDZjNaUmVPUTRVNW8?oc=5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="K88" s="1" t="n">
-        <v>46117.46695601852</v>
+        <v>46118.42163194445</v>
       </c>
     </row>
     <row r="89">
@@ -5275,22 +5275,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boy stabbed at huge annual Easter Travellers meeting outside Harrods - London Now</t>
+          <t>Four men arrested on suspicion of murder after stabbing in south London - The Guardian</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Boy stabbed at huge annual Easter Travellers meeting outside Harrods - London Now</t>
+          <t>Four men arrested on suspicion of murder after stabbing in south London - The Guardian</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 12:41:46 GMT</t>
+          <t>Mon, 06 Apr 2026 16:29:00 GMT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWlZ4a0RldlZVRm5EX01JUHZHYnViUDFPdUQ0SExrd3hOcFRIZk9lYW9TTHVHQzVDc2VhbHNGb0FhTmJvcERLOThwYThka0VIZlV3YmpDWklBVUJGT09jXzlVVmZKNWtwdEtuV1owVDliM0J3OHpianNEd3diU1RvZ1I0dW5saVJ6eGN2S3RvenhVTElZbWE1cFdvZF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOMnRoN2Fnd0EyNTQtUnpnenVvLWEyUmlVR21HdVV0eU15VUlGRHFiNnBMUjhtSnl3ZTB3R3VEMElZamluQ3g0RDFEY0pKN2tOb1RUeGhIakh1VjhJSFFoVVVYYlVuYXdlNDktYzhLNXRJdXZfeXFxSmtiZ3BYelNVY19fajM1QWJYUWVoLUcxcjhmakt4SVFFYjdyMlc4Ym9WY1E?oc=5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="K89" s="1" t="n">
-        <v>46117.52900462963</v>
+        <v>46118.68680555555</v>
       </c>
     </row>
     <row r="90">
@@ -5330,22 +5330,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Investing in America: 1937 New London Explosion - KETK.com</t>
+          <t>LIVE as man stabbed to death and two fighting for life after Peckham stabbing - London Now</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Investing in America: 1937 New London Explosion - KETK.com</t>
+          <t>LIVE as man stabbed to death and two fighting for life after Peckham stabbing - London Now</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 01:57:26 GMT</t>
+          <t>Tue, 07 Apr 2026 06:19:00 GMT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQbWpEaTUyTFdfNXd4MEZoWWNtRmtibHMxbXEydTl1NE9YUUY0MDV3b1J2QWxTUDQxU2JYcm50T1E1bEZCT3Itdkg3Xy1DNGRKQVFaSU91bVVsY3NLWHNQVldfa2E3R3J0M2FZZEJsWWYyTnY4dDkzV0loaUNiZHJzdDRpbTJZTWFHTXlfRdIBkgFBVV95cUxNajB5dEJJS3J4cTBQUTI2dUtHVS1MQTVCakZsQWZwcU5DcFh0UXFDU3JPZjZmcXAzMG9GY1ZsNnVRV1B3SjBLMFN5cTA5X0dnMTlja2hTZWhtcVEwbXQ0WjY4NFJjY0lkNEVRNUhNMU02WlF0SWVlNE9zbXZ3VUxlVERYYW5WeEtacDMwOTN5ckxndw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPdkNMVkFYRHlvdDZweFVnLVJfelZnOWtHTGhSWUE2OUZLTkI1M3pydzlJQ3BvZXBsbTB4N1FCNFMzczZ6bkkzLTNCN2V1ZmYwMExuYm8wVktuajhZdGpGY1RQN0tJc3hwMEYwMWNOMUhlWEVkSDduNHcwQUJGR1hLV2U1UWhXd0FrbGFhaGtldmJ6Z1dKX3lBU2hfM2NVWFlG?oc=5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="K90" s="1" t="n">
-        <v>46119.08155092593</v>
+        <v>46119.26319444444</v>
       </c>
     </row>
     <row r="91">
@@ -5385,22 +5385,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Update after teen arrested for 'stabbing' man under armpit - oxfordmail.co.uk</t>
+          <t>Woolwich shooting: Further arrests after Eghosa Ogbebor shot dead - BBC</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Update after teen arrested for 'stabbing' man under armpit - oxfordmail.co.uk</t>
+          <t>Woolwich shooting: Further arrests after Eghosa Ogbebor shot dead - BBC</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 12:01:28 GMT</t>
+          <t>Sun, 05 Apr 2026 11:36:50 GMT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOOHRPdXNGVHBPLVEyUHZlU1ExVll5a0cyLUlaa1dfSlIyWHJsM0ZLOUNBNk9PeE0xLVVmUmNpeEd5bDlEOS1hei1HMzA1bmNkdEZFT2xLaWVDVVFGZmczeEp6QWtxZzRRYy1qdUR5aVRHSGdEV3M3RkFOaU0yOEJ5bm9NY044N0RQTUdpRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5CZUhMRFBuNHJjb0VGSlZfV280UEd3N0hwRUROeVByTnhGSDM2N3k2bXVpOVp0Y0xNSDM2OFd3bDlmYXJCejF4X0ZMSDFoZXJncDJpYnRiSFhmZw?oc=5</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5424,7 +5424,7 @@
         </is>
       </c>
       <c r="K91" s="1" t="n">
-        <v>46117.50101851852</v>
+        <v>46117.48391203704</v>
       </c>
     </row>
     <row r="92">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Man in serious condition after Oxford shooting; suspect in custody - wral.com</t>
+          <t>Man remanded in custody accused of stabbing twin teenage sisters and passerby in Dublin - The Irish Times</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Man in serious condition after Oxford shooting; suspect in custody - wral.com</t>
+          <t>Man remanded in custody accused of stabbing twin teenage sisters and passerby in Dublin - The Irish Times</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 18:34:48 GMT</t>
+          <t>Mon, 06 Apr 2026 15:27:58 GMT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNS0JPNWJLVHNSeVBQWE1BZ1Ntcnp4S3JmM0hfTExNcFZ6VWN3RTFEVlVoM24xUUNUMDJKbk5hSkhSeExWaElwazJVbXpuT1p0ZTFNeGRpbUlRaldoQWJPREU2OGo4LWpUTFRHRnBNN0wzVThqMlFSaDJvUjZTeGxNVHlqWlJvUnhIU3hQSERzMXlRNklxWWxKUU44QjByREYwc09xeDU3OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOR3ltVEZSNzNtVUo0TmZLRTNZc2Q5bkdNZmNSQXRlOWxBZTQ5SW1OZlFFNU1ZMmxMTjRUdU5HQkQ2aHIyQlJRQk5jVThydXRkXzFkUmhFSUc0YnU1UFFUX25hZ1VFR1UzeHZiVkdXa0lkZmdGZDBDNHpFMzAwOHJRMGlocEFjU0xraDVRYXZDUWZxb2NlaUIxRzltaU5EMGp0QUJVN25UNXlqZlN1Q3llZ3UzeFpzTVYwTTRiaXNfODlmODYyWnFlT0Q1QkZQTm9qNWpFSlozM1BuZFU?oc=5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46117.77416666667</v>
+        <v>46118.6444212963</v>
       </c>
     </row>
     <row r="93">
@@ -5495,22 +5495,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>South London man arrested after 'targeted' stabbing in Suffolk - My London</t>
+          <t>Student detained after bomb threat note found at New London High School - WQAD</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>South London man arrested after 'targeted' stabbing in Suffolk - My London</t>
+          <t>Student detained after bomb threat note found at New London High School - WQAD</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 07:51:00 GMT</t>
+          <t>Mon, 06 Apr 2026 18:31:00 GMT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOb2FKcTVLR2ZzRm1EVXBPa0Q3THBieTZFY19WUGVZVzdQdUhiVlBmYUZFTHp4eVVscEVkWmVNSTM3MEFZcUpJek1PM2JiRHRpWFFxaDRueEM3YzJzeTBvLVJUejQ5YUozWkZocGpDeVBuckpobFlpTXNzWm5TSjU0R01MU1hkYkxMSHFISzdUdWJMeEXSAZgBQVVfeXFMTTUwMnllb2pJdFZsV083amNSNTZOR1A0YXNBcU5sblhnNUhTSTdLbzNMTHZPb3JheVBIckE2VXc5enZBTGl1endBYlJicVJpcWY1S0VGU20yckNPcUJrdzk2b29UcWZuVHpVekszSmRwYmR4TEk4eG1vRjl4Z01JbVpsZVF6MEdIUHU4NWN2NWU4a21ZNUFBdmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPbnVDajdYSC05S1ZtZDBkb29nOWFGajJhVDdrekZrc0d6MkU2X0tYVkQwdHAyR3FmcWY0OF9CZzd1YzY3NWdpLWFWd0J1M1RVSUJPLVZiN1Y3TWJ5WFE2VExaSm1DQjR2RnlpMllmRXAtZEZPZ1ZzZGVKbENNMXhZQTJNXzNOSGFaN0NpUkFyVk9mZjRrdFhWZzlmOVcwYzFJUUxRYkd2NkpHaUxZcklmRWFMeU5EYUVob1VjT2tmeEMwT3VYTmhOd2FFU3pTaFN0bk9VeXlvc19XMHRoWGZRYXF0MS0wZElJWmRxWlR3?oc=5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46117.32708333333</v>
+        <v>46118.77152777778</v>
       </c>
     </row>
     <row r="94">
@@ -5550,22 +5550,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Political leaders condemn 'terrifying and unprovoked' stabbing of garda in Dublin city centre - MSN</t>
+          <t>Investing in America: 1937 New London Explosion - KETK.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Political leaders condemn 'terrifying and unprovoked' stabbing of garda in Dublin city centre - MSN</t>
+          <t>Investing in America: 1937 New London Explosion - KETK.com</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 09:47:29 GMT</t>
+          <t>Tue, 07 Apr 2026 01:57:26 GMT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigNBVV95cUxPTkVfaFZSdnFMOUdEWTU3ZHgwR29kczRPN3ZkMktmZk8xOUdXdHU4N3FvTjhMcWxZRXhPU0ZlQWdEVHpGMWJ4OG5ZN1BTN1M1TTkzRWlveDhrT0U2LUZZaEFWV25XYzV1X3JwSmNURkFTMmMxRDdzSlRXZkJzVG9Wak9vNG0wN0FRNzBGM3dQeHZPSVZfNFBrMEw3WlY4dDRLZEJNYlhPeXJBc2w5YUZwZkNGZHVISGY1eHNFMHZxLUtRS3pqQjlfbGxtRTlsako2eVgySkhxdG9TTGZXdll0M3VkS0xRbDQwblhoX3FRaTItOV9Td3JfNW9CVmlRTGVUb0RWaGlhbzZFVk45WlVNQkdnVVdOSmZPdS1PYmFJNktGOEN1V2dhMGRiNkhfWnlEWWh1eENHc3ZjV0xmbXdYUnItdlFjS1FwQjdUSGVDWHoyV3ZQeWo5a2dIaXlqZHVyUVBVZ1h5dUc0N2h4aHkxOW5aaF9fWjk3d3Fqc09JV2tSZDlpTnJIZGVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQbWpEaTUyTFdfNXd4MEZoWWNtRmtibHMxbXEydTl1NE9YUUY0MDV3b1J2QWxTUDQxU2JYcm50T1E1bEZCT3Itdkg3Xy1DNGRKQVFaSU91bVVsY3NLWHNQVldfa2E3R3J0M2FZZEJsWWYyTnY4dDkzV0loaUNiZHJzdDRpbTJZTWFHTXlfRdIBkgFBVV95cUxNajB5dEJJS3J4cTBQUTI2dUtHVS1MQTVCakZsQWZwcU5DcFh0UXFDU3JPZjZmcXAzMG9GY1ZsNnVRV1B3SjBLMFN5cTA5X0dnMTlja2hTZWhtcVEwbXQ0WjY4NFJjY0lkNEVRNUhNMU02WlF0SWVlNE9zbXZ3VUxlVERYYW5WeEtacDMwOTN5ckxndw?oc=5</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46118.40797453704</v>
+        <v>46119.08155092593</v>
       </c>
     </row>
     <row r="95">
@@ -5605,22 +5605,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bomb threat discovered on note at New London High School | The Hawk Eye - Burlington, Iowa - Daily Gate City</t>
+          <t>Two more people arrested on suspicion of murder after 14-year-old boy shot dead in London - Sky News</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bomb threat discovered on note at New London High School | The Hawk Eye - Burlington, Iowa - Daily Gate City</t>
+          <t>Two more people arrested on suspicion of murder after 14-year-old boy shot dead in London - Sky News</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 02:05:00 GMT</t>
+          <t>Sun, 05 Apr 2026 11:12:25 GMT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPQ3EtSkQ3Z1NzcjZPWWtzTnhSbV9hMGt3bGRxbWNCSHVjR1FBQkdINVN5TURPMW9VM29wR0Q1WlRnNVh0aTk4Unh1cEY3bjgzR3E0NXNUWFdQQmpCdnl4Y3MyY2JaempwUlJqTE5MbmItUXJEaWV5cE9obUppTEE2SHBQR0ZMMTJ3THdTWjF5bXlBelhaSjNXX3FIcUhvZkRpSjU4RUd4Mk52X2NkcjlJbENCbkNKTHlmRDhpallqeDRnNzllbnFRTGwyUHM1REZZUEdMR3hZWDQ5c3JtcDYyXzl3cFJLQUpBTE44cURGRXRpRTVubWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNWlYyM2p5RTk2T3dYOTdUaV84Zk5jQWQ2TzBRZUltUE03cVpwd2FKcG82UTFCX0xqMlFobmxUSkxMdEd5Q1piWFAxUzYxaXBMTTIxaGd1NG1FcUJQQ0JlV1Rnb1N6aG9iWXoxSWdaclMxeVVsYmNEZHFkbDJWREVYTjlnMUJNUGs5Y2szVWdQUmJzVWFEeUZLNndMTVNtSEtjdGpHQl8wd0d2eTVqQjk1dk1DaWdieFFaNFJrT3I3STF4dVk?oc=5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46119.08680555555</v>
+        <v>46117.46695601852</v>
       </c>
     </row>
     <row r="96">
@@ -5660,22 +5660,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Woolwich shooting: Major police update issued after boy, 14, shot dead in London - Daily Express</t>
+          <t>Boy stabbed at huge annual Easter Travellers meeting outside Harrods - London Now</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Woolwich shooting: Major police update issued after boy, 14, shot dead in London - Daily Express</t>
+          <t>Boy stabbed at huge annual Easter Travellers meeting outside Harrods - London Now</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 11:49:00 GMT</t>
+          <t>Sun, 05 Apr 2026 12:41:46 GMT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOb0JtbzItc0I0bFBHUEpybFVXLUQ1ZDFSa2xKM2xWVjhqUF9QOVNFU3Q1NmY0VnRaLUNxd1EyeWloOUdwMzFmZFBnVFJLQkpHNGdXQkE4NW1uNS04YXlJVElxZGNFSi1IQ1ZoTGFYeFltMEo1dFhtbHFNek5UWVdhQ2wwNXBKM05a0gGOAUFVX3lxTE5XeV9OZEJLN1kxTncwZHhiUEFZQ01FWUJJVm95V21qYmlDLW1DMHpkMHdOV3UwNGUtNFlqYkxrTjRFUDFqOGtDaEp0VWJrc2xCRXZobWRVbGhMNG1qU25OSUltNjVENnhuRlZrdmNaVmtrdFVRd0lhWGtBQTg1TWRfZWR6NXlxV1JINXQ4bVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWlZ4a0RldlZVRm5EX01JUHZHYnViUDFPdUQ0SExrd3hOcFRIZk9lYW9TTHVHQzVDc2VhbHNGb0FhTmJvcERLOThwYThka0VIZlV3YmpDWklBVUJGT09jXzlVVmZKNWtwdEtuV1owVDliM0J3OHpianNEd3diU1RvZ1I0dW5saVJ6eGN2S3RvenhVTElZbWE1cFdvZF8?oc=5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46117.49236111111</v>
+        <v>46117.52900462963</v>
       </c>
     </row>
     <row r="97">
@@ -5715,22 +5715,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>One arrested in Oxford shooting - hendersondispatch.com</t>
+          <t>Update after teen arrested for 'stabbing' man under armpit - oxfordmail.co.uk</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>One arrested in Oxford shooting - hendersondispatch.com</t>
+          <t>Update after teen arrested for 'stabbing' man under armpit - oxfordmail.co.uk</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 13:44:38 GMT</t>
+          <t>Sun, 05 Apr 2026 12:01:28 GMT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNRTFFZ2xDSnpYUGVWM25QTVNrNVMxNkxocmZxYjJlTGZTTTZhZXRZX1VET0Jaa29QTWUtRzczUlE1bV8tZ09MT19vVi1UTjBiNEhGRlF6MTU3UEdYcmlMWC1QX1NCSTNUbmFtN25lNkNQNjNQdVA1eU5YampYQXR5OUhjWXdkSkpOdkg3SXphTWt3Ty12TDV6RW1rd25ITmg2OGtlTWVscF9sQzZJdUVfWkxxaUoyZ0JvdHlTLVluM0dodw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOOHRPdXNGVHBPLVEyUHZlU1ExVll5a0cyLUlaa1dfSlIyWHJsM0ZLOUNBNk9PeE0xLVVmUmNpeEd5bDlEOS1hei1HMzA1bmNkdEZFT2xLaWVDVVFGZmczeEp6QWtxZzRRYy1qdUR5aVRHSGdEV3M3RkFOaU0yOEJ5bm9NY044N0RQTUdpRQ?oc=5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="K97" s="1" t="n">
-        <v>46118.57266203704</v>
+        <v>46117.50101851852</v>
       </c>
     </row>
     <row r="98">
@@ -5770,22 +5770,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Victim dies six weeks after shooting outside Dublin hotel - wlrfm.com</t>
+          <t>Man in serious condition after Oxford shooting; suspect in custody - WRAL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Victim dies six weeks after shooting outside Dublin hotel - wlrfm.com</t>
+          <t>Man in serious condition after Oxford shooting; suspect in custody - WRAL</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 01:54:22 GMT</t>
+          <t>Sun, 05 Apr 2026 18:34:48 GMT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOanp2VEZWek1Nd0M5WHAzZ2hUU1B4NlkzNkdSNUR4NVM3UjcxTDlzOEZVXzFkRW9sWFc3SFl4c2hKaTJVRm9RczdXQTN4N3VBTjZ2UkdzVHBDYjBTTE9NMUc2VWVSX3NqWHo5UEdpZTJFeWVjZDJheVlBR3J3SEFDTXltQUtkUHNubzF0TUg4VktMZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNS0JPNWJLVHNSeVBQWE1BZ1Ntcnp4S3JmM0hfTExNcFZ6VWN3RTFEVlVoM24xUUNUMDJKbk5hSkhSeExWaElwazJVbXpuT1p0ZTFNeGRpbUlRaldoQWJPREU2OGo4LWpUTFRHRnBNN0wzVThqMlFSaDJvUjZTeGxNVHlqWlJvUnhIU3hQSERzMXlRNklxWWxKUU44QjByREYwc09xeDU3OA?oc=5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="K98" s="1" t="n">
-        <v>46118.07942129629</v>
+        <v>46117.77416666667</v>
       </c>
     </row>
     <row r="99">
@@ -5825,22 +5825,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oxford arrest made after Durham man shot 5 times; police seize cocaine, weapons and ammo - CBS17.com</t>
+          <t>South London man arrested after 'targeted' stabbing in Suffolk - My London</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Oxford arrest made after Durham man shot 5 times; police seize cocaine, weapons and ammo - CBS17.com</t>
+          <t>South London man arrested after 'targeted' stabbing in Suffolk - My London</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 18:31:26 GMT</t>
+          <t>Sun, 05 Apr 2026 07:51:00 GMT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYXIyTU9YUDhsdHJpaUtzODF2UzdraElic2RSY3FvTlhPOUFfeDI4dHcyS2ZWSUpIVEROTHBzdXlReWxrS3FzRDFLbUU3eWdBVlRGaW1hN2hNcy1tcHZjN0drd3BETG9kM2hlWGJrZ0xHeGdqX1dUNjVkRHhTMXZPUUZTVHV3MXgwaWh3c0dCNzVtaFM0OFFrNGF2WFZqUWVhX01zeldpWE5jZUdDeW9TeUF0ZEc1TXpjcklNclhTaWprLUHSAcgBQVVfeXFMTUZYUEtpcmhwemtkWTB0aFBiRnB4TjhYRGE2Qnp6bDVjRzBpS2hFc1dxQWNHd3RwT3JmV1BROGhzcUJpVVBzN2pRX19jazBUZGU1d1htMGxxTDdVU3pvSEZHZVA1amdaVTliRmhTOTZxQ3UzTVFZNXRsWktYM3RiS21XTHl3WS1mcTJLTXBzdGcyU2FGWEV1d1NvZ1RSZzBtemV3dTY4ajNRZUNMZkQzOV9xUkpEdERQNWhZYVozUy1rdEs0b3BwOFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOb2FKcTVLR2ZzRm1EVXBPa0Q3THBieTZFY19WUGVZVzdQdUhiVlBmYUZFTHp4eVVscEVkWmVNSTM3MEFZcUpJek1PM2JiRHRpWFFxaDRueEM3YzJzeTBvLVJUejQ5YUozWkZocGpDeVBuckpobFlpTXNzWm5TSjU0R01MU1hkYkxMSHFISzdUdWJMeEXSAZgBQVVfeXFMTTUwMnllb2pJdFZsV083amNSNTZOR1A0YXNBcU5sblhnNUhTSTdLbzNMTHZPb3JheVBIckE2VXc5enZBTGl1endBYlJicVJpcWY1S0VGU20yckNPcUJrdzk2b29UcWZuVHpVekszSmRwYmR4TEk4eG1vRjl4Z01JbVpsZVF6MEdIUHU4NWN2NWU4a21ZNUFBdmo?oc=5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5864,38 +5864,38 @@
         </is>
       </c>
       <c r="K99" s="1" t="n">
-        <v>46117.77182870371</v>
+        <v>46117.32708333333</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>High Level City France French</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>("Paris" OR "Île-de-France") AND ("alerte à la bombe" OR "colis suspect" OR "menace à la bombe" OR fusillade OR "attentat" OR "attaque au couteau" OR "opération de police" OR évacuation) AND -immobilier AND -"prix immobilier" AND -foot AND -transfert AND -Texas</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Attentats terroristes à Paris, attaques, état islamique, kamikaze, Bataclan, fusillade - 20 Minutes</t>
+          <t>Political leaders condemn 'terrifying and unprovoked' stabbing of garda in Dublin city centre - MSN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Terrorist attacks in Paris, attacks, Islamic State, suicide bomber, Bataclan, shooting - 20 Minutes</t>
+          <t>Political leaders condemn 'terrifying and unprovoked' stabbing of garda in Dublin city centre - MSN</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fri, 03 Apr 2026 07:00:00 GMT</t>
+          <t>Mon, 06 Apr 2026 09:47:29 GMT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE03N1A0aVhGOWtIb3JFRjdadmc0ZkNpVFRqWjAyTkxJSXExRU5fWGFRbzBHUm9TUjc4Z1ctQXBLQkdlRDB1NVpJRzlsY2szZVpvZ2RUcFNtaEVOYnFBd3g3bFV2d2hSa2JxOVZsdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigNBVV95cUxPTkVfaFZSdnFMOUdEWTU3ZHgwR29kczRPN3ZkMktmZk8xOUdXdHU4N3FvTjhMcWxZRXhPU0ZlQWdEVHpGMWJ4OG5ZN1BTN1M1TTkzRWlveDhrT0U2LUZZaEFWV25XYzV1X3JwSmNURkFTMmMxRDdzSlRXZkJzVG9Wak9vNG0wN0FRNzBGM3dQeHZPSVZfNFBrMEw3WlY4dDRLZEJNYlhPeXJBc2w5YUZwZkNGZHVISGY1eHNFMHZxLUtRS3pqQjlfbGxtRTlsako2eVgySkhxdG9TTGZXdll0M3VkS0xRbDQwblhoX3FRaTItOV9Td3JfNW9CVmlRTGVUb0RWaGlhbzZFVk45WlVNQkdnVVdOSmZPdS1PYmFJNktGOEN1V2dhMGRiNkhfWnlEWWh1eENHc3ZjV0xmbXdYUnItdlFjS1FwQjdUSGVDWHoyV3ZQeWo5a2dIaXlqZHVyUVBVZ1h5dUc0N2h4aHkxOW5aaF9fWjk3d3Fqc09JV2tSZDlpTnJIZGVR?oc=5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5905,52 +5905,52 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>FR:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46115.29166666666</v>
+        <v>46118.40797453704</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Aeroporti senza carburante, rischi rifornimenti cherosene: altri scali a secco - RaiNews</t>
+          <t>Bomb threat discovered on note at New London High School | The Hawk Eye - Burlington, Iowa - Daily Gate City</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Airports without fuel, risks of kerosene supplies: other dry airports - RaiNews</t>
+          <t>Bomb threat discovered on note at New London High School | The Hawk Eye - Burlington, Iowa - Daily Gate City</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 04:07:00 GMT</t>
+          <t>Tue, 07 Apr 2026 02:05:00 GMT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxQeER5VHlzVF91blQxOTE5YThOYzFXYVFlRWNncE9FN3MwVlNVZjF2NEFUN2Z1NDRuVUdObXQwcVNVamtvU1FtazkxSWdGNUcwTkNIMWZXY0ZvQ2xsRDlVOUJPdTNVZ1h1aVBhcV9GZ3oyVjdsVEdGZkl4aDBQSUU4ZTVNaGt6Q1gtMlZNZm5RRW5qWHkwRDJXR0s5a3M1MUkxR1BJS2gxbVpIVWJ5OGt4SUotSmV0ZjA1TG50clV5eEdzWlJ3NTdUeVRfQkdRTjRFajZLTXJUbksyWE1ubzA0NkhKU2NoQUtvZ1RHb2hzNEVKY2s3alFzV3MzX1dtN1VqVEo5Y0RuLUU1dGgwWXNCdm9Oa3dFVV9Wc3fSAZoCQVVfeXFMUHhEeVR5c1RfdW5UMTkxOWE4TmMxV2FRZUVjZ3BPRTdzMFZTVWYxdjRBVDdmdTQ0blVHTm10MHFTVWprb1NRbWs5MUlnRjVHME5DSDFmV2NGb0NsbEQ5VTlCT3UzVWdYdWlQYXFfRmd6MlY3bFRHRmZJeGgwUElFOGU1TWhrekNYLTJWTWZuUUVualh5MEQyV0dLOWtzNTFJMUdQSUtoMW1aSFVieThreElKLUpldGYwNUxudHJVeXhHc1pSdzU3VHlUX0JHUU40RWo2S01yVG5LMlhNbm8wNDZISlNjaEFLb2dUR29oczRFSmNrN2pRc1dzM19XbTdValRKOWNEbi1FNXRoMFlzQnZvTmt3RVVfVnN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPQ3EtSkQ3Z1NzcjZPWWtzTnhSbV9hMGt3bGRxbWNCSHVjR1FBQkdINVN5TURPMW9VM29wR0Q1WlRnNVh0aTk4Unh1cEY3bjgzR3E0NXNUWFdQQmpCdnl4Y3MyY2JaempwUlJqTE5MbmItUXJEaWV5cE9obUppTEE2SHBQR0ZMMTJ3THdTWjF5bXlBelhaSjNXX3FIcUhvZkRpSjU4RUd4Mk52X2NkcjlJbENCbkNKTHlmRDhpallqeDRnNzllbnFRTGwyUHM1REZZUEdMR3hZWDQ5c3JtcDYyXzl3cFJLQUpBTE44cURGRXRpRTVubWc?oc=5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5960,52 +5960,52 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K101" s="1" t="n">
-        <v>46119.17152777778</v>
+        <v>46119.08680555555</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Aprile mese degli scioperi. Dai trasporti alla stampa, dalla sanità alla logistica: tutti gli stop - TGLA7</t>
+          <t>Woolwich shooting: Major police update issued after boy, 14, shot dead in London - Daily Express</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>April month of strikes. From transport to the press, from healthcare to logistics: all the stops - TGLA7</t>
+          <t>Woolwich shooting: Major police update issued after boy, 14, shot dead in London - Daily Express</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 15:52:10 GMT</t>
+          <t>Sun, 05 Apr 2026 11:49:00 GMT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOMkp1XzgtdmxxVXRxSXU5Zk50SEhOaWFFd1k4Q1pSRHM2VGpkclFNajVmR1V3clFkX0x0THBpY2tKaGFXQWloUFpsZmh1bkhVMTA1WDVMbVNVX25ocUNBeEhNUDgtNzhnVnplWENGQ0xqbWJBUkQyOVpiMlR5enNKMG42NHF5YkhBVXBv0gGQAUFVX3lxTE0tSFNOSWZ3MW9oMFJCbUcyQWMwMTF2djR4MG4xcS1sajd5U3hKZzdkc0s2bnYtU2dDUk1HUnlEcXpKMWRCQldYQXc0RFhLbDBLaE02SzNUdjZCdy1pWmRDdHphY1JycERBRkF0U0dkWmRZZDg0aXR1cmcyU0RIVUF1a0hXY3ZHdUpoY2lOOFlWdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOb0JtbzItc0I0bFBHUEpybFVXLUQ1ZDFSa2xKM2xWVjhqUF9QOVNFU3Q1NmY0VnRaLUNxd1EyeWloOUdwMzFmZFBnVFJLQkpHNGdXQkE4NW1uNS04YXlJVElxZGNFSi1IQ1ZoTGFYeFltMEo1dFhtbHFNek5UWVdhQ2wwNXBKM05a0gGOAUFVX3lxTE5XeV9OZEJLN1kxTncwZHhiUEFZQ01FWUJJVm95V21qYmlDLW1DMHpkMHdOV3UwNGUtNFlqYkxrTjRFUDFqOGtDaEp0VWJrc2xCRXZobWRVbGhMNG1qU25OSUltNjVENnhuRlZrdmNaVmtrdFVRd0lhWGtBQTg1TWRfZWR6NXlxV1JINXQ4bVE?oc=5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6015,52 +6015,52 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K102" s="1" t="n">
-        <v>46118.66122685185</v>
+        <v>46117.49236111111</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sciopero dei trasporti aprile 2026: calendario e orari città per città - Virgilio</t>
+          <t>One arrested in Oxford shooting - hendersondispatch.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Transport strike April 2026: calendar and timetables city by city - Virgilio</t>
+          <t>One arrested in Oxford shooting - hendersondispatch.com</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:00:00 GMT</t>
+          <t>Mon, 06 Apr 2026 13:44:38 GMT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxORU5PTi0xQ2pNdkpYenBObHRvN0VILXdhOFg5UXg3cmNRWE1QNDFDaE1kYzZaLVRydEZaTjZXQnN6VDAxUmJQMU9xaWVJRWxoQ3FCaEV3Wk1uUDlGWjI1a0VpdzBlZ0ZKNFBjR05nYWRwMVdnTG01dGRjUDVmaUNyZ3VmMTVtQmpybDcxN3ROVGFYdXNiemdOM2xvLTRJXzJsZG1YM0Q5SWF5Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNRTFFZ2xDSnpYUGVWM25QTVNrNVMxNkxocmZxYjJlTGZTTTZhZXRZX1VET0Jaa29QTWUtRzczUlE1bV8tZ09MT19vVi1UTjBiNEhGRlF6MTU3UEdYcmlMWC1QX1NCSTNUbmFtN25lNkNQNjNQdVA1eU5YampYQXR5OUhjWXdkSkpOdkg3SXphTWt3Ty12TDV6RW1rd25ITmg2OGtlTWVscF9sQzZJdUVfWkxxaUoyZ0JvdHlTLVluM0dodw?oc=5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6070,52 +6070,52 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K103" s="1" t="n">
-        <v>46118.25</v>
+        <v>46118.57266203704</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Raccolta firme per la remigrazione. Sdegno del Coordinamento 25 aprile - ilgiorno.it</t>
+          <t>Victim dies six weeks after shooting outside Dublin hotel - wlrfm.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Collecting signatures for remigration. Outrage of the Coordination 25 April - ilgiorno.it</t>
+          <t>Victim dies six weeks after shooting outside Dublin hotel - wlrfm.com</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 03:35:56 GMT</t>
+          <t>Mon, 06 Apr 2026 01:54:22 GMT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPX0NOSWpVRk5EcUprUTlvYXZPaERiY3E3VDZaS1A5Mnl4TkxCcXlrbnhHdEt5V0ZFVkxWMDBOWTNoMmlTc003bU1JM2tmUXhRZnM3eGJyQmNtcVBaTXpPamUwNGQwVl81ck45NWJvd0tRa3VCWnNFRm5hclV2ZFMyY1lxVDQwU00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOanp2VEZWek1Nd0M5WHAzZ2hUU1B4NlkzNkdSNUR4NVM3UjcxTDlzOEZVXzFkRW9sWFc3SFl4c2hKaTJVRm9RczdXQTN4N3VBTjZ2UkdzVHBDYjBTTE9NMUc2VWVSX3NqWHo5UEdpZTJFeWVjZDJheVlBR3J3SEFDTXltQUtkUHNubzF0TUg4VktMZw?oc=5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6125,52 +6125,52 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K104" s="1" t="n">
-        <v>46119.1499537037</v>
+        <v>46118.07942129629</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sciopero aerei nel weekend, disagi in tutta Italia: chi aderisce, scali coinvolti e voli garantiti - Moveo by Telepass</t>
+          <t>Oxford arrest made after Durham man shot 5 times; police seize cocaine, weapons and ammo - CBS17.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Aircraft strike over the weekend, inconveniences throughout Italy: who is taking part, airports involved and flights guaranteed - Moveo by Telepass</t>
+          <t>Oxford arrest made after Durham man shot 5 times; police seize cocaine, weapons and ammo - CBS17.com</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:00:40 GMT</t>
+          <t>Sun, 05 Apr 2026 18:31:26 GMT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4xcEdDaWF4UV9zVnlseVRUY2ZpVHpwVllwX2NIMG9QYjV4RV9wN3czdUY1alMwcWszMG5ybGZlUWxsY0phNHFHWGRLcGlCeUxfT3l5MjRBeTJsamczd0o2eHFkbWZDMHNuYTJydGhmOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOYXIyTU9YUDhsdHJpaUtzODF2UzdraElic2RSY3FvTlhPOUFfeDI4dHcyS2ZWSUpIVEROTHBzdXlReWxrS3FzRDFLbUU3eWdBVlRGaW1hN2hNcy1tcHZjN0drd3BETG9kM2hlWGJrZ0xHeGdqX1dUNjVkRHhTMXZPUUZTVHV3MXgwaWh3c0dCNzVtaFM0OFFrNGF2WFZqUWVhX01zeldpWE5jZUdDeW9TeUF0ZEc1TXpjcklNclhTaWprLUHSAcgBQVVfeXFMTUZYUEtpcmhwemtkWTB0aFBiRnB4TjhYRGE2Qnp6bDVjRzBpS2hFc1dxQWNHd3RwT3JmV1BROGhzcUJpVVBzN2pRX19jazBUZGU1d1htMGxxTDdVU3pvSEZHZVA1amdaVTliRmhTOTZxQ3UzTVFZNXRsWktYM3RiS21XTHl3WS1mcTJLTXBzdGcyU2FGWEV1d1NvZ1RSZzBtemV3dTY4ajNRZUNMZkQzOV9xUkpEdERQNWhZYVozUy1rdEs0b3BwOFk?oc=5</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6180,52 +6180,52 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K105" s="1" t="n">
-        <v>46118.25046296296</v>
+        <v>46117.77182870371</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City France English</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Paris" OR "Île-de-France") AND "France" AND ("bomb threat" OR "suspicious package" OR "shooting" OR "stabbing" OR "terror attack" OR "police operation" OR evacuation) AND -Texas AND -"Paris, Texas" AND -film AND -movie AND -football AND -transfer</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Aprile mese duro per gli scioperi nei trasporti: dagli aerei ai tir ecco chi si ferma: E c'è una data, in particolare, da segnare in rosso - La Sicilia</t>
+          <t>Goldman Paris under police watch after bomb threat linked to Iran group - ایران اینترنشنال</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>April is a tough month for transport strikes: from planes to trucks, here's who's stopping: And there is one date, in particular, to be marked in red - Sicily</t>
+          <t>Goldman Paris under police watch after bomb threat linked to Iran group - ایران اینترنشنال</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 14:21:00 GMT</t>
+          <t>Thu, 02 Apr 2026 10:45:56 GMT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxONE9mN0tkZGRibXhORGdmeVdadG9wSTVTUmU1Mk16S0xfMWNBLXBBRlY1Y1l1aVZfQ3lTZjdRb0pubVRGMVNDemxhNlR6YjFreEt4OHJmSl8xQ29mQnRKNUZMZTZOR1RDZC1iaXd2bFpWRDFyVzJ6WDMxc3lPeUtVN0k2UmdTcFRqM0k4S3JqU2dsRkVOZ1F2R1dESGlwYUExYWNlQ1ZfQ1U0YmlkcUM4QUtPbThKNTVuLTRkZGw2VkprQ2RvdS1nSlB6QjVOOXplY3lrUGRMaFBfUkJHVzhqRzhfSGlBanRUOUplSUp5engxOEpveUdyTTYtWE5DTnlDbVJvd2RIQW9JZlYtOGJoV0FZbkxHYW5EcEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9WSlRZdlVqcmxROTV4WkcxRExFaTR1UnlXeFg2TlU3R0V1MVhKZ1lmZjBZYWYzajNjc0tEMzZuTGF2dkwxMk9QVk4tWTBfNllaZEE?oc=5</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6235,52 +6235,52 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>FR:en</t>
         </is>
       </c>
       <c r="K106" s="1" t="n">
-        <v>46118.59791666667</v>
+        <v>46114.44856481482</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City France English</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Paris" OR "Île-de-France") AND "France" AND ("bomb threat" OR "suspicious package" OR "shooting" OR "stabbing" OR "terror attack" OR "police operation" OR evacuation) AND -Texas AND -"Paris, Texas" AND -film AND -movie AND -football AND -transfer</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scarseggia il carburante, primi guai per i voli aerei - RaiNews</t>
+          <t>Goldman Sachs (GS.US) Paris HQ Receives Bomb Threat; France Tightens Security at US Banks - AASTOCKS.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Fuel is running short, first problems for airline flights - RaiNews</t>
+          <t>Goldman Sachs (GS.US) Paris HQ Receives Bomb Threat; France Tightens Security at US Banks - AASTOCKS.com</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 00:04:07 GMT</t>
+          <t>Thu, 02 Apr 2026 15:53:00 GMT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOX0sxejY2M2FfNHNkUWtWdkt2QjdaRkFNdjNZM3dYc0RSQmJtMnlNbmliVldKaHVuZm1QakZ3akh2b1NJeFBKenoyM3hfYzRQdTNKSE9BakkwblVWcC01anRTRUFBUUZlenA4MUNReUFxUzhDS09rd3BTSFRPMDJTc1NWTVhyN29vQmZqN2UwOHhGLXEtR0RoSW5lT0tSS0k1WS1NcWR5eGM1UzZiQ3FhbzNKUkVqLUtVWi1lSTcwT2pGX0Q1ZnN2b2ZGQTlqcDlxTXBXWWVlR05od0RTRnpLOVdBUXl5WVpkSGfSAe8BQVVfeXFMUGg3Sk5PSFgzcmpDVHFjUlMxMkFQczJwVUlSMVlsT3d1S25Pal82TjdXT2FMSnZHUXp5N3JnTXc0QnpGdHJjYXpmcGY4T05ibktaV1ZkMDBqc2d2TFRqcC1zY0tqUUdtNFRYZlBHSlZvTUtleVAwdDJrVzN6OWhJV2VHOTYxSVQ5WEstek44dF9QeXBpMXpXd0o5R1FUZG43MnRHazlITlAxUWpCbnU3WDVOXy01WkpCOUFJODlCOVpPXzBwaGV6T0R1Q3RYOWtuNmp5TWg0OU1xQTJZQ2hxaVpjbmNDYnZJc3E1RGtNNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNMWlxVG9mU25Ia1o2cnJ2VXc3VmcwTThEZmF5d0Vta003WUExUTVQTXByVEM2TTJSbzFmVHNTLXZlLXVXQ1lINURmLW9RQnVMNGcwSHB0MmRSdEtZYzc3dERNcEZxYjMxbDZ5NUpyVVNRYmhSdmpaeHpKbFZnYmRtMDNZWkhPZEFoOXc?oc=5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6290,52 +6290,52 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>FR:en</t>
         </is>
       </c>
       <c r="K107" s="1" t="n">
-        <v>46119.0028587963</v>
+        <v>46114.66180555556</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City France French</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Paris" OR "Île-de-France") AND ("alerte à la bombe" OR "colis suspect" OR "menace à la bombe" OR fusillade OR "attentat" OR "attaque au couteau" OR "opération de police" OR évacuation) AND -immobilier AND -"prix immobilier" AND -foot AND -transfert AND -Texas</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Da Como una Harley “pirata” per Johnny Depp: corteo di biker verso il concerto della star - QuiComo</t>
+          <t>"Le but est de raviver la psychose du terrorisme" : derrière l'attentat déjoué contre la Bank of America à Paris, la riposte graduée de l'Iran - France Info</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>From Como a "pirate" Harley for Johnny Depp: procession of bikers towards the star's concert - QuiComo</t>
+          <t>"The goal is to revive the psychosis of terrorism": behind the foiled attack against the Bank of America in Paris, Iran's graduated response - France Info</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 06:48:48 GMT</t>
+          <t>Fri, 03 Apr 2026 03:52:06 GMT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNbUxVV2ZZcHJEaFMtbEFTbHNRcDFCUEpCWW5IYU05SVA2TnpEXzRNd19rczdwdHZGVXRDeTl2U2hNUXVwLVAyRjZESnVLZ3BWWFpINEhrMXdsdGtoN2pUQlNoaGxmQ3VYNU8xbTIwT1hxTXNZaUU5eXVfVzNmWGRWLWI3OUlLT3RJekt1WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxNT3MzeEF3eTU4WkMxUmFvakk4RjVkMVRPVTRFUFMySk9aZlEtMWNseUVOWGY5dzc3cnJydm05dEVnYWhSME43VjBKdkVtODNqMnEwR2JQVW9iTFJtazNrbUU3Z1ROVnZxY2l1cmtyaWkxOWFSU190NFRFdElpUjZkblJZdTE1djZXN0dVOHpPN1hIWnNadjZEUVEtYXBQa0F3dUljZy1RamYtSDZmc3N4eUZFR1d2aFZiNng1Yll1d01SMmpLeU9WbnJfMjVjbXRiOGF4N2xZNWExcmN1LTN1SnRLeERKT05xWDZKX21MZkVhNVY4MkRpbDFYMkhOWGRYa3E1bktCLWdrVmZ5NTN4NFVmOWpkZ0UtaF9vaGVpcGhHM3NMTmxVenJmcEFXdGdtc1RkNVBSQ0ttamJyd09ibXFYNk9WeUZJbXB6dmg3ZFdtZw?oc=5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6345,52 +6345,52 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>FR:fr</t>
         </is>
       </c>
       <c r="K108" s="1" t="n">
-        <v>46118.28388888889</v>
+        <v>46115.16118055556</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City France French</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Paris" OR "Île-de-France") AND ("alerte à la bombe" OR "colis suspect" OR "menace à la bombe" OR fusillade OR "attentat" OR "attaque au couteau" OR "opération de police" OR évacuation) AND -immobilier AND -"prix immobilier" AND -foot AND -transfert AND -Texas</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Il messaggio di Pasqua di Zuppi: “Dobbiamo credere nella forza dell’amore” - Il Resto del Carlino</t>
+          <t>Attentats terroristes à Paris, attaques, état islamique, kamikaze, Bataclan, fusillade - 20 Minutes</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Zuppi's Easter message: "We must believe in the power of love" - ​​Il Resto del Carlino</t>
+          <t>Terrorist attacks in Paris, attacks, Islamic State, suicide bomber, Bataclan, shooting - 20 Minutes</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 17:12:17 GMT</t>
+          <t>Fri, 03 Apr 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQYXNNZDR6NnNEQVozMmQ1RExXUmw0T2wwbk5TdWRnTTF2NnhkakoyR1NQbGxiSmZLZDEzTm1nMlE1TUVZd2RLZjFwMnN3UjNWTUthNENNR0p4ZXRoam54TUtFTTgtcDFheU9PR2FVX3ozZmxNT0hHVVpYOW55eHlqcFlQM0loUGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE03N1A0aVhGOWtIb3JFRjdadmc0ZkNpVFRqWjAyTkxJSXExRU5fWGFRbzBHUm9TUjc4Z1ctQXBLQkdlRDB1NVpJRzlsY2szZVpvZ2RUcFNtaEVOYnFBd3g3bFV2d2hSa2JxOVZsdA?oc=5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6400,52 +6400,52 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>FR:fr</t>
         </is>
       </c>
       <c r="K109" s="1" t="n">
-        <v>46117.71686342593</v>
+        <v>46115.29166666666</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City France French</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Paris" OR "Île-de-France") AND ("alerte à la bombe" OR "colis suspect" OR "menace à la bombe" OR fusillade OR "attentat" OR "attaque au couteau" OR "opération de police" OR évacuation) AND -immobilier AND -"prix immobilier" AND -foot AND -transfert AND -Texas</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Zvrzi firma Manifestazione, una ballad civile nata dalla strada - Mescalina.it</t>
+          <t>Télétravail et sécurité renforcée à Paris après l'attentat déjoué contre Bank of America - France 24</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Zvrzi signs Manifestazione, a civil ballad born from the street - Mescalina.it</t>
+          <t>Teleworking and reinforced security in Paris after the foiled attack against Bank of America - France 24</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 18:16:22 GMT</t>
+          <t>Thu, 02 Apr 2026 13:40:34 GMT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPREppeWV0c2dvSlpUT0J6YnZLUG8xSXUtMGZMa0dNUUg2QTJySE15cnZXWmhScHJwdVpRZWpGZDBUVi1hR2JGdWxuMENNcTA4WUc0NTBzSTRYZFhET0k0S0xzWGlYVkZfT1NPSVJpbTlKb2Y0cEkxdjlqeUFObm5hS1k3SXFQdll2aFQ3WVVleE1ZZWZERG96MmNRUXprTHVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNTWIydHBDM3V3eGxvcDQ4WHVjZEo0R0hxVmZpTWU2Z1gxdTNhWm1aT05XUlN1bFFDZF8wajJDZnozb293N3ZuWjlxWFFfSDZMcDJXQU85RTk4eFg1NGJ3ZXdTM1hXdEwtclRBMFNmTy1RQmdJXy1hQXN1N2FEY1RYUm9XVjZqVmhLdldkTWFlRGZrU283VXhHZHJERHluX0N6NG4wejlRUTRncE5SbXpwNF93VmxUYk9JRk1EVGowZUM5dVh5MEtjejV4ZTI0TWVlclMycDZZNkxRR2FQcEVib1U3ZEFfVUFadk5oVTVQV0U4cmVnVEVlaWVfVjl5NjJzYjlSQlU5UEE?oc=5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6455,21 +6455,21 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>FR:fr</t>
         </is>
       </c>
       <c r="K110" s="1" t="n">
-        <v>46117.76136574074</v>
+        <v>46114.56983796296</v>
       </c>
     </row>
     <row r="111">
@@ -6485,22 +6485,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Scioperi dal 6 al 12 aprile, ma venerdì 10 giornata critica per aerei e trasporti mentre sabato 11 stop ai treni - Torino Cronaca</t>
+          <t>Aeroporti senza carburante, rischi rifornimenti cherosene: altri scali a secco - RaiNews</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Strikes from 6 to 12 April, but Friday the 10th is a critical day for planes and transport while on Saturday the 11th there will be a stop to trains - Turin News</t>
+          <t>Airports without fuel, risks of kerosene supplies: other dry airports - RaiNews</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 20:45:00 GMT</t>
+          <t>Tue, 07 Apr 2026 04:07:00 GMT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOMWI5YWZmWUN3TVJqOHJBU2Y3MG80ZGluWGdnaGRmMmRPQ1JESWlKR1k5LW5PUDRYTVYzMlAzU3lUb01TSFpaaFI2N3ViejAzSW81Tzg3ZGNaaGVQUjhnSDIyOEFETlJVQTFZeE9mS3h6ZGpObUVtWUFtZzBXX0FMeG50cU5DMjBJUVNzMUZEaUFvb0VIZmpQWkFabExDWFJjdzZObWRoTURldGJfeUNRMWxSLW4tMmx4SEhzR0d2QmxkVlRFd2pqajhsZTdqZ3QtMWhraHdnc2NZLUo3c0xhSUVVZHhTTHZQQkFNdS1PMVFjRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxQeER5VHlzVF91blQxOTE5YThOYzFXYVFlRWNncE9FN3MwVlNVZjF2NEFUN2Z1NDRuVUdObXQwcVNVamtvU1FtazkxSWdGNUcwTkNIMWZXY0ZvQ2xsRDlVOUJPdTNVZ1h1aVBhcV9GZ3oyVjdsVEdGZkl4aDBQSUU4ZTVNaGt6Q1gtMlZNZm5RRW5qWHkwRDJXR0s5a3M1MUkxR1BJS2gxbVpIVWJ5OGt4SUotSmV0ZjA1TG50clV5eEdzWlJ3NTdUeVRfQkdRTjRFajZLTXJUbksyWE1ubzA0NkhKU2NoQUtvZ1RHb2hzNEVKY2s3alFzV3MzX1dtN1VqVEo5Y0RuLUU1dGgwWXNCdm9Oa3dFVV9Wc3fSAZoCQVVfeXFMUHhEeVR5c1RfdW5UMTkxOWE4TmMxV2FRZUVjZ3BPRTdzMFZTVWYxdjRBVDdmdTQ0blVHTm10MHFTVWprb1NRbWs5MUlnRjVHME5DSDFmV2NGb0NsbEQ5VTlCT3UzVWdYdWlQYXFfRmd6MlY3bFRHRmZJeGgwUElFOGU1TWhrekNYLTJWTWZuUUVualh5MEQyV0dLOWtzNTFJMUdQSUtoMW1aSFVieThreElKLUpldGYwNUxudHJVeXhHc1pSdzU3VHlUX0JHUU40RWo2S01yVG5LMlhNbm8wNDZISlNjaEFLb2dUR29oczRFSmNrN2pRc1dzM19XbTdValRKOWNEbi1FNXRoMFlzQnZvTmt3RVVfVnN3?oc=5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="K111" s="1" t="n">
-        <v>46117.86458333334</v>
+        <v>46119.17152777778</v>
       </c>
     </row>
     <row r="112">
@@ -6540,22 +6540,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jet fuel, limiti a Linate e in altri scali italiani - guidaviaggi.it</t>
+          <t>Aprile mese degli scioperi. Dai trasporti alla stampa, dalla sanità alla logistica: tutti gli stop - TGLA7</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Jet fuel, limits at Linate and other Italian airports -guidaviaggi.it</t>
+          <t>April month of strikes. From transport to the press, from healthcare to logistics: all the stops - TGLA7</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 07:34:48 GMT</t>
+          <t>Mon, 06 Apr 2026 16:39:18 GMT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOYTJmemVWWnlQWnU5dnNLTHBCYnFwb21LWUxsVjUzdnFvQ3MyNXBPMEtBNXhQblNqMnY1R3hzMTItMk5fWHh4TTBoekl0LTNoOGhDOU5Fd2JNX3VOY0ZwV2dwTTREb3FhNHJhcE1kWlZSZFRiMW5fWTJsT3ZGZHFTOGMwTVJEd0RSZ2REd2N2ckFVb0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNLUhTTklmdzFvaDBSQm1HMkFjMDExdnY0eDBuMXEtbGo3eVN4Smc3ZHNLNm52LVNnQ1JNR1J5RHF6SjFkQkJXWEF3NERYS2wwS2hNNkszVHY2QnctaVpkQ3R6YWNScnBEQUZBdFNHZFpkWWQ4NGl0dXJnMlNESFVBdWtIV2N2R3VKaGNpTjhZVnfSAZABQVVfeXFMTS1IU05JZncxb2gwUkJtRzJBYzAxMXZ2NHgwbjFxLWxqN3lTeEpnN2RzSzZudi1TZ0NSTUdSeURxekoxZEJCV1hBdzREWEtsMEtoTTZLM1R2NkJ3LWlaZEN0emFjUnJwREFGQXRTR2RaZFlkODRpdHVyZzJTREhVQXVrSFdjdkd1SmhjaU44WVZ3?oc=5</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="K112" s="1" t="n">
-        <v>46118.31583333333</v>
+        <v>46118.69395833334</v>
       </c>
     </row>
     <row r="113">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Corteo propal a Milano, nel mirino la condizione dei detenuti palestinesi - stream24.ilsole24ore.com</t>
+          <t>Sciopero dei trasporti aprile 2026: calendario e orari città per città - Virgilio</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Propal procession in Milan, the condition of Palestinian prisoners in the crosshairs - stream24.ilsole24ore.com</t>
+          <t>Transport strike April 2026: calendar and timetables city by city - Virgilio</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 07:38:50 GMT</t>
+          <t>Mon, 06 Apr 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1CM2plNzhrb3hYMzBCMUdZVS0zdjUwWXUzMW5qUVg1NHIxXzNPemlGS2EySW5sTWZsa0xoeTdrTnhLbnI1RU5mTVJnbW1aWXJSVWRSdE0yX0NpTUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxORU5PTi0xQ2pNdkpYenBObHRvN0VILXdhOFg5UXg3cmNRWE1QNDFDaE1kYzZaLVRydEZaTjZXQnN6VDAxUmJQMU9xaWVJRWxoQ3FCaEV3Wk1uUDlGWjI1a0VpdzBlZ0ZKNFBjR05nYWRwMVdnTG01dGRjUDVmaUNyZ3VmMTVtQmpybDcxN3ROVGFYdXNiemdOM2xvLTRJXzJsZG1YM0Q5SWF5Zw?oc=5</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="K113" s="1" t="n">
-        <v>46117.31863425926</v>
+        <v>46118.25</v>
       </c>
     </row>
     <row r="114">
@@ -6650,22 +6650,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cherosene razionato, ora sono sei gli aeroporti in difficoltà: estate a rischio - PPN ADI - Agenzia delle Infrastrutture - primapaginanews.it</t>
+          <t>Raccolta firme per la remigrazione. Sdegno del Coordinamento 25 aprile - Il Giorno</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Kerosene rationed, now six airports are in difficulty: summer at risk - PPN ADI - Infrastructure Agency - primapaginanews.it</t>
+          <t>Collecting signatures for remigration. Outrage of the Coordination 25 April - The Day</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 18:14:52 GMT</t>
+          <t>Tue, 07 Apr 2026 03:35:56 GMT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNVlVRVy1wcTJUTG5pb1NfZGV4X01SQldYejZaSmhUbm5hYWFIVWJtVG5EbDRlM1FaZzdVeFBrc1JINjJETTJQNVhhZXlTN0xHa2NMRG9XcnV1YW5EX0Z1bDRCbklnaDBWVFNxZlZheElraW9MSUttWUhzTFg5UmZYTkhGb1JrUHdRcXpfYnZxTWZhLVdpZjhDOHZyQmxQUVBYTHlVdkRJSWxuWWg3c0xSRXBWSTFNWDRKMHN0OC10X1ZJRU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPX0NOSWpVRk5EcUprUTlvYXZPaERiY3E3VDZaS1A5Mnl4TkxCcXlrbnhHdEt5V0ZFVkxWMDBOWTNoMmlTc003bU1JM2tmUXhRZnM3eGJyQmNtcVBaTXpPamUwNGQwVl81ck45NWJvd0tRa3VCWnNFRm5hclV2ZFMyY1lxVDQwU00?oc=5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="K114" s="1" t="n">
-        <v>46118.76032407407</v>
+        <v>46119.1499537037</v>
       </c>
     </row>
     <row r="115">
@@ -6705,22 +6705,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Carburanti, Pichetto Fratin: "Siamo pronti al razionamento, se necessario" - RaiNews</t>
+          <t>Sciopero aerei nel weekend, disagi in tutta Italia: chi aderisce, scali coinvolti e voli garantiti - Moveo by Telepass</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Fuels, Pichetto Fratin: "We are ready for rationing, if necessary" - RaiNews</t>
+          <t>Aircraft strike over the weekend, inconveniences throughout Italy: who is taking part, airports involved and flights guaranteed - Moveo by Telepass</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 11:46:44 GMT</t>
+          <t>Mon, 06 Apr 2026 06:00:40 GMT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQN2RYenZEeFJlS2ttN1Bjbl85bVNmUlJ2ZmlUZ0M0M3Vkak9xd05EbUNubXFwU25lVXVHN29Scld5MXRXbFV4TTcyOWNkc2hGY2ZrRVFsV09Sbk9tdVVPNlI5T0YyTGtGNDg0Z0pqN3U0UWFoa0FxZ3BKT3NYZ2NLbkRZZlFtV25DZjl5NGNFdEpMX0MyVEpScVhvaHdyZXZIdzJEajRpSk5WNXJXM3dEQ3FiSTNBQ1Y2bU12dVZSVWE4Tm1sVWxlWmZrTWhSZXk3aEkxb0NZT2NFRjlVX2U2NGJn0gHnAUFVX3lxTE1JbU1lbS16Yld2VUlGRmhwc3pQNXFfdkNVQWVXWU15eTdXRXptOTZ3TU0zYi00RVAwV21wV1hNZWFqeUhsaHd4RzBPWUZRSks1UnRGUHZrdUxQckhwV1lLVzR0WUVscWdwaFJBeHpUMXNjV0NxVnVHSzRwTE5JOWlKcno3U0pJVTJTNUV4TThoQVgySXdKOEs4RjFPbGtyZzJaUGd3YjdsSGhIbVFMdDRyNlRrcF8tX1RqdTdQNl9OUFhfV0hraGRxajNxY0dKdE5NbEtHNFhiRUtxbXFtcDVCYnc2Z2VMVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4xcEdDaWF4UV9zVnlseVRUY2ZpVHpwVllwX2NIMG9QYjV4RV9wN3czdUY1alMwcWszMG5ybGZlUWxsY0phNHFHWGRLcGlCeUxfT3l5MjRBeTJsamczd0o2eHFkbWZDMHNuYTJydGhmOA?oc=5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6744,7 +6744,7 @@
         </is>
       </c>
       <c r="K115" s="1" t="n">
-        <v>46117.49078703704</v>
+        <v>46118.25046296296</v>
       </c>
     </row>
     <row r="116">
@@ -6760,22 +6760,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Emmelibri, sciopero e sit-in: "Promesse non mantenute, diritti degli operai calpestati" - MSN</t>
+          <t>Aprile mese duro per gli scioperi nei trasporti: dagli aerei ai tir ecco chi si ferma: E c'è una data, in particolare, da segnare in rosso - La Sicilia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Emmelibri, strike and sit-in: "Promises not kept, workers' rights trampled on" - MSN</t>
+          <t>April is a tough month for transport strikes: from planes to trucks, here's who's stopping: And there is one date, in particular, to be marked in red - Sicily</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 10:16:04 GMT</t>
+          <t>Mon, 06 Apr 2026 14:21:00 GMT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPVExPemFIZ0RRMUpRTW5ZdFZ1c2F3eTd4V3lOSUxUVGhqdWw1cDFhY3F2U1JuZ2dIUEhRZVRYZHVDeGVsTW8zbURrZHBhNHgyTDA5RzM2Qk4wdWRrM0VTR1lCYVQ1STFqdkx5NEVDZW5wbkFBbFBDVnl0RmlHUnNYV0hwbE90OGk5S19TeXRLTnQ4ZkJvUG00SnlkMUo5bWRLdmFTTjltQU05OF92RXo2M1cxemt6VklOaDFwTHdPUVBZano0LVR0aUp0QkIyMmZH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxONE9mN0tkZGRibXhORGdmeVdadG9wSTVTUmU1Mk16S0xfMWNBLXBBRlY1Y1l1aVZfQ3lTZjdRb0pubVRGMVNDemxhNlR6YjFreEt4OHJmSl8xQ29mQnRKNUZMZTZOR1RDZC1iaXd2bFpWRDFyVzJ6WDMxc3lPeUtVN0k2UmdTcFRqM0k4S3JqU2dsRkVOZ1F2R1dESGlwYUExYWNlQ1ZfQ1U0YmlkcUM4QUtPbThKNTVuLTRkZGw2VkprQ2RvdS1nSlB6QjVOOXplY3lrUGRMaFBfUkJHVzhqRzhfSGlBanRUOUplSUp5engxOEpveUdyTTYtWE5DTnlDbVJvd2RIQW9JZlYtOGJoV0FZbkxHYW5EcEE?oc=5</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="K116" s="1" t="n">
-        <v>46118.42782407408</v>
+        <v>46118.59791666667</v>
       </c>
     </row>
     <row r="117">
@@ -6815,22 +6815,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Restrizioni energetiche in quattro aeroporti italiani: primo caso in Europa - triestenews</t>
+          <t>Scarseggia il carburante, primi guai per i voli aerei - RaiNews</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Energy restrictions in four Italian airports: first case in Europe - triestenews</t>
+          <t>Fuel is running short, first problems for airline flights - RaiNews</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 11:30:29 GMT</t>
+          <t>Tue, 07 Apr 2026 00:04:07 GMT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOMXFrd2daczZGa3U4SjY2eTh1SDQtWEo0VERFS0RwQjJmWVB6Zk1OODNGZWF0RW1fLW1GYTZPMzZYeDlfdVdZM3JGbFllamxrbi1MN1djN1h1d3hLVGw3WENhcVNVWnhXRXBTU0p3aUZyejVwVjE0RU00NE52RklPbVloai1vV0EtMTFfaVpkV0R4U2R5UTYtRU1Mb2EyN2FMUW56b1BKaks0dzhPYlo1R0cxTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOX0sxejY2M2FfNHNkUWtWdkt2QjdaRkFNdjNZM3dYc0RSQmJtMnlNbmliVldKaHVuZm1QakZ3akh2b1NJeFBKenoyM3hfYzRQdTNKSE9BakkwblVWcC01anRTRUFBUUZlenA4MUNReUFxUzhDS09rd3BTSFRPMDJTc1NWTVhyN29vQmZqN2UwOHhGLXEtR0RoSW5lT0tSS0k1WS1NcWR5eGM1UzZiQ3FhbzNKUkVqLUtVWi1lSTcwT2pGX0Q1ZnN2b2ZGQTlqcDlxTXBXWWVlR05od0RTRnpLOVdBUXl5WVpkSGfSAe8BQVVfeXFMUGg3Sk5PSFgzcmpDVHFjUlMxMkFQczJwVUlSMVlsT3d1S25Pal82TjdXT2FMSnZHUXp5N3JnTXc0QnpGdHJjYXpmcGY4T05ibktaV1ZkMDBqc2d2TFRqcC1zY0tqUUdtNFRYZlBHSlZvTUtleVAwdDJrVzN6OWhJV2VHOTYxSVQ5WEstek44dF9QeXBpMXpXd0o5R1FUZG43MnRHazlITlAxUWpCbnU3WDVOXy01WkpCOUFJODlCOVpPXzBwaGV6T0R1Q3RYOWtuNmp5TWg0OU1xQTJZQ2hxaVpjbmNDYnZJc3E1RGtNNms?oc=5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="K117" s="1" t="n">
-        <v>46117.47950231482</v>
+        <v>46119.0028587963</v>
       </c>
     </row>
     <row r="118">
@@ -6870,22 +6870,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>La protesta contro la guerra, la NATO e le armi nucleari nella giornata del 4 aprile a Ghedi - Pressenza - International Press Agency</t>
+          <t>Da Como una Harley “pirata” per Johnny Depp: corteo di biker verso il concerto della star - QuiComo</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>The protest against war, NATO and nuclear weapons on April 4th in Ghedi - Pressenza - International Press Agency</t>
+          <t>From Como a "pirate" Harley for Johnny Depp: procession of bikers towards the star's concert - QuiComo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 09:55:39 GMT</t>
+          <t>Mon, 06 Apr 2026 06:48:48 GMT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPeVQ3enNBelZoVXhxNXJmMTV1N25FNW9xUmx0OE16TE9UVDAzUm5mU0xwaTNXenFoZFZqd2pJQUFQRHZuaVZJbmRBbVNyN3lOc3V6UnI2REtHSHBkMF9RYXRQSk9TZmUzLVFGU1M0MnpXbVJrOGhfUThiNVdUelUybW5R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNbUxVV2ZZcHJEaFMtbEFTbHNRcDFCUEpCWW5IYU05SVA2TnpEXzRNd19rczdwdHZGVXRDeTl2U2hNUXVwLVAyRjZESnVLZ3BWWFpINEhrMXdsdGtoN2pUQlNoaGxmQ3VYNU8xbTIwT1hxTXNZaUU5eXVfVzNmWGRWLWI3OUlLT3RJekt1WQ?oc=5</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="K118" s="1" t="n">
-        <v>46117.41364583333</v>
+        <v>46118.28388888889</v>
       </c>
     </row>
     <row r="119">
@@ -6925,22 +6925,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Carburante sos rifornimenti, voli a rischio. Vasile: «Si naviga a vista». Problemi per bus e treni - quotidianodipuglia.it</t>
+          <t>Il messaggio di Pasqua di Zuppi: “Dobbiamo credere nella forza dell’amore” - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SOS fuel supplies, flights at risk. Vasile: «We navigate by sight». Problems for buses and trains - cielodipuglia.it</t>
+          <t>Zuppi's Easter message: "We must believe in the power of love" - ​​Il Resto del Carlino</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 07:40:38 GMT</t>
+          <t>Sun, 05 Apr 2026 17:12:17 GMT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOQTkzMjlFaDJJZmF6c2I4THZ2Tjh1WnpHN2NKd1c5dUVoaVRIcEVzQ05oQXYyaXBadlU5eUFHR0lJdmpsUTBmRnVGVkNDeXJVRkxTeDNxcVZhYVZ1U1ZWSjNxbmdxbGlDUU1lbkg4MDhvOUpZMXFLNndJSnFoVF9zZzN2Mmo1a0Rhdk41OTdZUXYyTU9XQkFmRUI4Y3FSZUtsaG9tbDdIT1VuQ3ZhdF9YWkdxeVFTalNGdkNqUNIBwgFBVV95cUxNSUd5aEhuakVuYTBUaVhhQXZFOTQwNmZZcXpIMTJteVJuS1E3Y0p4cWF1QWNVREV2WkxJMGxvN19wVF81dXZDbU5CRnY0ZlB4dURCN0t5ZzhBM214Ujh2cXlRV2c4WFRoSlVFWjk1c04xLUxhQ3UyYjd6VFZ6YUdwcjVxNkxiWjEyV1hGeUMxbENlRk5vOElsRnBtcXA1NWp4TGZyTnpTZVUtbjk0eGx2a3pfLXZJQmJZNmRJS3luNXY2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQYXNNZDR6NnNEQVozMmQ1RExXUmw0T2wwbk5TdWRnTTF2NnhkakoyR1NQbGxiSmZLZDEzTm1nMlE1TUVZd2RLZjFwMnN3UjNWTUthNENNR0p4ZXRoam54TUtFTTgtcDFheU9PR2FVX3ozZmxNT0hHVVpYOW55eHlqcFlQM0loUGs?oc=5</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="K119" s="1" t="n">
-        <v>46118.31988425926</v>
+        <v>46117.71686342593</v>
       </c>
     </row>
     <row r="120">
@@ -6980,22 +6980,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Il pentito e la foto con Meloni “Si accreditò per conto di FDI” - PressReader</t>
+          <t>Zvrzi firma Manifestazione, una ballad civile nata dalla strada - Mescalina.it</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>The repentant and the photo with Meloni “He was accredited on behalf of FDI” - PressReader</t>
+          <t>Zvrzi signs Manifestazione, a civil ballad born from the street - Mescalina.it</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tue, 07 Apr 2026 00:21:24 GMT</t>
+          <t>Sun, 05 Apr 2026 18:16:22 GMT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOWVlwS2Q2dElhSE1ONUx5aE13TmhfWEJqdlBwWTR4XzdEWXp5UjJwT2VUblpQYkNMa1J4aG9XRnJ5OHNhM2pRUW1rY2lya3JkNXNnMWtWQS1kN2I4ZlM4S0Jvbm04aWl3WWc1WWdwT3dHeFVPOC05cEMwS1NKZVZocmJNX0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPREppeWV0c2dvSlpUT0J6YnZLUG8xSXUtMGZMa0dNUUg2QTJySE15cnZXWmhScHJwdVpRZWpGZDBUVi1hR2JGdWxuMENNcTA4WUc0NTBzSTRYZFhET0k0S0xzWGlYVkZfT1NPSVJpbTlKb2Y0cEkxdjlqeUFObm5hS1k3SXFQdll2aFQ3WVVleE1ZZWZERG96MmNRUXprTHVI?oc=5</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="K120" s="1" t="n">
-        <v>46119.01486111111</v>
+        <v>46117.76136574074</v>
       </c>
     </row>
     <row r="121">
@@ -7035,22 +7035,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Milano uova al consolato iraniano | l’urlo contro i massacri - zazoom.it</t>
+          <t>Jet fuel, limiti a Linate e in altri scali italiani - guidaviaggi.it</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Milan eggs at the Iranian consulate | the cry against the massacres - zazoom.it</t>
+          <t>Jet fuel, limits at Linate and other Italian airports -guidaviaggi.it</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 16:27:57 GMT</t>
+          <t>Mon, 06 Apr 2026 07:34:48 GMT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPb05CWnQ3OUVCSkJ1SFlkZHhjSUlzQ2ZSOWNna0Q2MzVXR2kwQVZuVl9KVXl5aGJYU1BnWGxqNVBQVlpVcDhmcURvS2N4elNLMlpWME1LMWhKVVgwVi13d04wWENZUUg4NlFyVi1CcjFGOFJ2U2wwS2NLRWlwbFlBbWdRMEttVUpNSC13VHlpRXZWcnp4bmNqY3NwVjNIRTVSb2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOYTJmemVWWnlQWnU5dnNLTHBCYnFwb21LWUxsVjUzdnFvQ3MyNXBPMEtBNXhQblNqMnY1R3hzMTItMk5fWHh4TTBoekl0LTNoOGhDOU5Fd2JNX3VOY0ZwV2dwTTREb3FhNHJhcE1kWlZSZFRiMW5fWTJsT3ZGZHFTOGMwTVJEd0RSZ2REd2N2ckFVb0U?oc=5</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7074,7 +7074,7 @@
         </is>
       </c>
       <c r="K121" s="1" t="n">
-        <v>46118.68607638889</v>
+        <v>46118.31583333333</v>
       </c>
     </row>
     <row r="122">
@@ -7090,22 +7090,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Polistena, le scuole unite nella “Passeggiata contro la violenza” per sensibilizzare i giovani - Telemia</t>
+          <t>Scioperi dal 6 al 12 aprile, ma venerdì 10 giornata critica per aerei e trasporti mentre sabato 11 stop ai treni - Torino Cronaca</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Polistena, the schools united in the "Walk against violence" to raise awareness among young people - Telemia</t>
+          <t>Strikes from 6 to 12 April, but Friday the 10th is a critical day for planes and transport while on Saturday the 11th there will be a stop to trains - Turin News</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sun, 05 Apr 2026 07:00:00 GMT</t>
+          <t>Sun, 05 Apr 2026 20:45:00 GMT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQczgtVWllNXhuTjQ2VVgwbVlTSEE0c3J3Zm1nNVNnWnk5d3RXd1I5bkNaUFNwSkN2QkVRSXlJV1FUeDVYTzRJWDQ3R250aDliUmRWelVkcnJTRHBNTHNiSUpZY2tHOEdSSUJQTWl3Tl80RDE1QUxGRzAweGhxNE83b2tFTGQ0dk9jSm9ZMjA1Q0VhVGd0eUVseWdjZnlNaFlKbUlFYkdna2RQdHVZLVRNLUFPbkZGUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOMWI5YWZmWUN3TVJqOHJBU2Y3MG80ZGluWGdnaGRmMmRPQ1JESWlKR1k5LW5PUDRYTVYzMlAzU3lUb01TSFpaaFI2N3ViejAzSW81Tzg3ZGNaaGVQUjhnSDIyOEFETlJVQTFZeE9mS3h6ZGpObUVtWUFtZzBXX0FMeG50cU5DMjBJUVNzMUZEaUFvb0VIZmpQWkFabExDWFJjdzZObWRoTURldGJfeUNRMWxSLW4tMmx4SEhzR0d2QmxkVlRFd2pqajhsZTdqZ3QtMWhraHdnc2NZLUo3c0xhSUVVZHhTTHZQQkFNdS1PMVFjRWc?oc=5</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7129,7 +7129,502 @@
         </is>
       </c>
       <c r="K122" s="1" t="n">
-        <v>46117.29166666666</v>
+        <v>46117.86458333334</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Corteo propal a Milano, nel mirino la condizione dei detenuti palestinesi - stream24.ilsole24ore.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Propal procession in Milan, the condition of Palestinian prisoners in the crosshairs - stream24.ilsole24ore.com</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Sun, 05 Apr 2026 07:38:50 GMT</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1CM2plNzhrb3hYMzBCMUdZVS0zdjUwWXUzMW5qUVg1NHIxXzNPemlGS2EySW5sTWZsa0xoeTdrTnhLbnI1RU5mTVJnbW1aWXJSVWRSdE0yX0NpTUk?oc=5</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K123" s="1" t="n">
+        <v>46117.31863425926</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Cherosene razionato, ora sono sei gli aeroporti in difficoltà: estate a rischio - PPN ADI - Agenzia delle Infrastrutture - primapaginanews.it</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Kerosene rationed, now six airports are in difficulty: summer at risk - PPN ADI - Infrastructure Agency - primapaginanews.it</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 18:14:52 GMT</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNVlVRVy1wcTJUTG5pb1NfZGV4X01SQldYejZaSmhUbm5hYWFIVWJtVG5EbDRlM1FaZzdVeFBrc1JINjJETTJQNVhhZXlTN0xHa2NMRG9XcnV1YW5EX0Z1bDRCbklnaDBWVFNxZlZheElraW9MSUttWUhzTFg5UmZYTkhGb1JrUHdRcXpfYnZxTWZhLVdpZjhDOHZyQmxQUVBYTHlVdkRJSWxuWWg3c0xSRXBWSTFNWDRKMHN0OC10X1ZJRU0?oc=5</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K124" s="1" t="n">
+        <v>46118.76032407407</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>La foto di Giorgia Meloni con l'uomo del Clan Senese. Il caso Amico arriva a Report - TP24.it</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>The photo of Giorgia Meloni with the man from the Senese Clan. The Amico case reaches Report - TP24.it</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Tue, 07 Apr 2026 07:13:15 GMT</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOenROa0stdHA2LUI3cEltM2VJM3RCdXJ3cDQzTmNIc1ZudjZBNXhXYy04V2ZGVkE1TUJ1OTZvejRwS3UzR3B2bU5kLTVuLTNIOFdqdTJaSDl4bVBGaC14NlF0UTV0cEhrNy1HSlprbGc0MGhUWGtlNW55TlRVUkNVYmFQZGhhQm5UN01ZcnEweHMzN182LWZTOHpaU0hVUlFISUZHd0JRLW5PNVVQNlJ0OWhueEkxRzhPcEFPUnhrbnA2U05tcUJKQXpB?oc=5</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K125" s="1" t="n">
+        <v>46119.30086805556</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Restrizioni energetiche in quattro aeroporti italiani: primo caso in Europa - triestenews</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Energy restrictions in four Italian airports: first case in Europe - triestenews</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Sun, 05 Apr 2026 11:30:29 GMT</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOMXFrd2daczZGa3U4SjY2eTh1SDQtWEo0VERFS0RwQjJmWVB6Zk1OODNGZWF0RW1fLW1GYTZPMzZYeDlfdVdZM3JGbFllamxrbi1MN1djN1h1d3hLVGw3WENhcVNVWnhXRXBTU0p3aUZyejVwVjE0RU00NE52RklPbVloai1vV0EtMTFfaVpkV0R4U2R5UTYtRU1Mb2EyN2FMUW56b1BKaks0dzhPYlo1R0cxTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K126" s="1" t="n">
+        <v>46117.47950231482</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Carburante sos rifornimenti, voli a rischio. Vasile: «Si naviga a vista». Problemi per bus e treni - Quotidiano Di Puglia</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SOS fuel supplies, flights at risk. Vasile: «We navigate by sight». Problems for buses and trains - Quotidiano Di Puglia</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 07:40:38 GMT</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOQTkzMjlFaDJJZmF6c2I4THZ2Tjh1WnpHN2NKd1c5dUVoaVRIcEVzQ05oQXYyaXBadlU5eUFHR0lJdmpsUTBmRnVGVkNDeXJVRkxTeDNxcVZhYVZ1U1ZWSjNxbmdxbGlDUU1lbkg4MDhvOUpZMXFLNndJSnFoVF9zZzN2Mmo1a0Rhdk41OTdZUXYyTU9XQkFmRUI4Y3FSZUtsaG9tbDdIT1VuQ3ZhdF9YWkdxeVFTalNGdkNqUNIBwgFBVV95cUxNSUd5aEhuakVuYTBUaVhhQXZFOTQwNmZZcXpIMTJteVJuS1E3Y0p4cWF1QWNVREV2WkxJMGxvN19wVF81dXZDbU5CRnY0ZlB4dURCN0t5ZzhBM214Ujh2cXlRV2c4WFRoSlVFWjk1c04xLUxhQ3UyYjd6VFZ6YUdwcjVxNkxiWjEyV1hGeUMxbENlRk5vOElsRnBtcXA1NWp4TGZyTnpTZVUtbjk0eGx2a3pfLXZJQmJZNmRJS3luNXY2QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K127" s="1" t="n">
+        <v>46118.31988425926</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Carburanti, Pichetto Fratin: "Siamo pronti al razionamento, se necessario" - RaiNews</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Fuels, Pichetto Fratin: "We are ready for rationing, if necessary" - RaiNews</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Sun, 05 Apr 2026 11:46:44 GMT</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQN2RYenZEeFJlS2ttN1Bjbl85bVNmUlJ2ZmlUZ0M0M3Vkak9xd05EbUNubXFwU25lVXVHN29Scld5MXRXbFV4TTcyOWNkc2hGY2ZrRVFsV09Sbk9tdVVPNlI5T0YyTGtGNDg0Z0pqN3U0UWFoa0FxZ3BKT3NYZ2NLbkRZZlFtV25DZjl5NGNFdEpMX0MyVEpScVhvaHdyZXZIdzJEajRpSk5WNXJXM3dEQ3FiSTNBQ1Y2bU12dVZSVWE4Tm1sVWxlWmZrTWhSZXk3aEkxb0NZT2NFRjlVX2U2NGJn0gHnAUFVX3lxTE1JbU1lbS16Yld2VUlGRmhwc3pQNXFfdkNVQWVXWU15eTdXRXptOTZ3TU0zYi00RVAwV21wV1hNZWFqeUhsaHd4RzBPWUZRSks1UnRGUHZrdUxQckhwV1lLVzR0WUVscWdwaFJBeHpUMXNjV0NxVnVHSzRwTE5JOWlKcno3U0pJVTJTNUV4TThoQVgySXdKOEs4RjFPbGtyZzJaUGd3YjdsSGhIbVFMdDRyNlRrcF8tX1RqdTdQNl9OUFhfV0hraGRxajNxY0dKdE5NbEtHNFhiRUtxbXFtcDVCYnc2Z2VMVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K128" s="1" t="n">
+        <v>46117.49078703704</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Scoppio del carro a Firenze, vola bene la 'colombina' - Corriere delle Alpi</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Explosion of the wagon in Florence, the 'colombina' flies well - Corriere delle Alpi</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Sun, 05 Apr 2026 09:18:19 GMT</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPTUhUZ29pZmlfZy1CVnFoNWZSNEpxV0p2TndNWHIySV83TG9UWWJOQ2dkTm4tRV9VNFJheC1jQ1h1akZKbXYwR3ZvMzh1UzBDU2VabmZhdldUYUUzNWp0WFVVWGtsNUF0S2FnMDc3dG5QLXdkaHFWamM3Q3hNOXlEdFBveVhuSkFWTjJuVjBYOFh1X1ZWcUxiVk1n?oc=5</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K129" s="1" t="n">
+        <v>46117.3877199074</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Il pentito e la foto con Meloni “Si accreditò per conto di FDI” - PressReader</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>The repentant and the photo with Meloni “He was accredited on behalf of FDI” - PressReader</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Tue, 07 Apr 2026 00:21:24 GMT</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOWVlwS2Q2dElhSE1ONUx5aE13TmhfWEJqdlBwWTR4XzdEWXp5UjJwT2VUblpQYkNMa1J4aG9XRnJ5OHNhM2pRUW1rY2lya3JkNXNnMWtWQS1kN2I4ZlM4S0Jvbm04aWl3WWc1WWdwT3dHeFVPOC05cEMwS1NKZVZocmJNX0U?oc=5</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K130" s="1" t="n">
+        <v>46119.01486111111</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Milano uova al consolato iraniano | l’urlo contro i massacri - zazoom.it</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Milan eggs at the Iranian consulate | the cry against the massacres - zazoom.it</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 16:27:57 GMT</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPb05CWnQ3OUVCSkJ1SFlkZHhjSUlzQ2ZSOWNna0Q2MzVXR2kwQVZuVl9KVXl5aGJYU1BnWGxqNVBQVlpVcDhmcURvS2N4elNLMlpWME1LMWhKVVgwVi13d04wWENZUUg4NlFyVi1CcjFGOFJ2U2wwS2NLRWlwbFlBbWdRMEttVUpNSC13VHlpRXZWcnp4bmNqY3NwVjNIRTVSb2c?oc=5</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K131" s="1" t="n">
+        <v>46118.68607638889</v>
       </c>
     </row>
   </sheetData>
